--- a/Rezultatai.xlsx
+++ b/Rezultatai.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,6 +31,10 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font/>
   </fonts>
   <fills count="2">
     <fill>
@@ -40,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,15 +52,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,51 +437,254 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="D5:D30"/>
+  <dimension ref="A2:AH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
+    <col width="15" customWidth="1" min="30" max="30"/>
+    <col width="15" customWidth="1" min="31" max="31"/>
+    <col width="15" customWidth="1" min="32" max="32"/>
+    <col width="15" customWidth="1" min="33" max="33"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
+  </cols>
   <sheetData>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Debitas pagal matuotą diferencinį slėgį</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="130" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Matavimo data</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Ėminių registracijos Nr. T-107-2026-E-</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Objekto pavadinimas, adresas, taršos šaltinio Nr.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Matavimo taškai ortakyje nuo vidinės sienelės, cm</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 1 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 2 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 3 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 4 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 5 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Pito vamzdelio koeficientas, K</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Temperatūra ortakyje t, oC</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Atmosferinis slėgis P, hPa</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Statinis slėgis ortakyje ± ΔP, hPa</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Dujų slėgis kamine Pk= P+ ΔP, hPa</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Dujų mol. masė Ms= qn *22.4, kg/</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Dujų srauto greitis matavimo taškuose, 1 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>Dujų srauto greitis matavimo taškuose, 2 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>Dujų srauto greitis matavimo taškuose, 3 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>Dujų srauto greitis matavimo taškuose, 4 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>Dujų srauto greitis matavimo taškuose, 5 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>Vidutinis dujų srauto greitis ortakyje w, m/s</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>Ortakio diametras, matmenys, m</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>Ortakio skerspjūvio plotas F, m2</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Dujų tūrio debitas realiomis sąlygomis Vk = wvid × F, m3/s</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>Dujų tūrio debitas normaliosiomis sąlygomis Vdr n.s =Vk *0,269*(P±ΔP)/(273+t), m3/s</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>Vandens kondensato masė m H2O, kg</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Vandens garų konc. dujose x=mH2O/Vmn*qn, kg/kg</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>Sausų dujų tūrio debitas normaliosiomis sąlygomis Vn= Vdr n.s *((1/(1+(x*qn/0.8038)))</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>Prasiurbtas dujų tūris normaliosiomis sąlygomis Vmn, Nm3</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>Išplėstinės neapibrėžties koef. A</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Išplėstinė neapibrėžtis (dujų tūrio debitas) Uv</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>Išplėstinė neapibrėžtis (dujų srauto greitis) Uw</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Sausų dujų tankis normaliosioms sąlygomis qn, (kg/m3)</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>Skaičiavimus atliko (inicialai, data)</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="D5" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>1,57</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="D6" s="1" t="n">
-        <v>68</v>
+        <v>58</v>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>1,75</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="D7" s="1" t="n">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8">
       <c r="D8" s="1" t="n">
-        <v>158</v>
+        <v>136</v>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -826,13 +1044,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26DB1D6B-D3B8-4921-9BA4-737F01866245}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEBE2C37-2C2D-4C28-A631-0871300752EA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C17C3D95-C071-4D81-B5B1-056490C57A07}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CDA3A50-E5E8-4AF6-8F7C-E395BB0529F7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A063B15-F2FF-42E6-ACFD-A31986A9C588}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90C72CEF-7F82-4BB1-BA65-A03953A50152}"/>
 </file>
--- a/Rezultatai.xlsx
+++ b/Rezultatai.xlsx
@@ -22,7 +22,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -71,7 +73,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -659,25 +663,29 @@
       <c r="D5" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>1,57</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="D6" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="V6" s="4" t="inlineStr">
-        <is>
-          <t>1,75</t>
-        </is>
+      <c r="V6" s="1" t="inlineStr">
+        <is>
+          <t>1,57</t>
+        </is>
+      </c>
+      <c r="W6" s="4">
+        <f>V6*V7</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="D7" s="1" t="n">
         <v>97</v>
+      </c>
+      <c r="V7" s="1" t="inlineStr">
+        <is>
+          <t>1,75</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1044,13 +1052,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEBE2C37-2C2D-4C28-A631-0871300752EA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A133032C-8DA4-4325-99B9-1B63B6280A77}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CDA3A50-E5E8-4AF6-8F7C-E395BB0529F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01AF40AF-96A7-45CC-AFDC-4FF63D6D9469}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90C72CEF-7F82-4BB1-BA65-A03953A50152}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{671E46D8-4263-4B7F-AA57-26D8A7A885B7}"/>
 </file>
--- a/Rezultatai.xlsx
+++ b/Rezultatai.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AH8"/>
+  <dimension ref="A2:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -474,10 +474,6 @@
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="15" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="15" customWidth="1" min="31" max="31"/>
-    <col width="15" customWidth="1" min="32" max="32"/>
-    <col width="15" customWidth="1" min="33" max="33"/>
-    <col width="15" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -525,175 +521,158 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Išmatuotas diferencinis slėgis taškuose 4 linija, Pdi, hPa</t>
+          <t>Pito vamzdelio koeficientas, K</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Išmatuotas diferencinis slėgis taškuose 5 linija, Pdi, hPa</t>
+          <t>Temperatūra ortakyje t, oC</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Pito vamzdelio koeficientas, K</t>
+          <t>Atmosferinis slėgis P, hPa</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Temperatūra ortakyje t, oC</t>
+          <t>Statinis slėgis ortakyje ± ΔP, hPa</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Atmosferinis slėgis P, hPa</t>
+          <t>Dujų slėgis kamine Pk= P+ ΔP, hPa</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Statinis slėgis ortakyje ± ΔP, hPa</t>
+          <t>Dujų mol. masė Ms= qn *22.4, kg/</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>Dujų slėgis kamine Pk= P+ ΔP, hPa</t>
+          <t>Dujų srauto greitis matavimo taškuose, 1 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Dujų mol. masė Ms= qn *22.4, kg/</t>
+          <t>Dujų srauto greitis matavimo taškuose, 2 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Dujų srauto greitis matavimo taškuose, 1 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+          <t>Dujų srauto greitis matavimo taškuose, 3 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>Dujų srauto greitis matavimo taškuose, 2 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+          <t>Vidutinis dujų srauto greitis ortakyje w, m/s</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>Dujų srauto greitis matavimo taškuose, 3 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+          <t>Ortakio diametras, matmenys, m</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>Dujų srauto greitis matavimo taškuose, 4 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+          <t>Ortakio skerspjūvio plotas F, m2</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Dujų srauto greitis matavimo taškuose, 5 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+          <t>Dujų tūrio debitas realiomis sąlygomis Vk = wvid × F, m3/s</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>Vidutinis dujų srauto greitis ortakyje w, m/s</t>
+          <t>Dujų tūrio debitas normaliosiomis sąlygomis Vdr n.s =Vk *0,269*(P±ΔP)/(273+t), m3/s</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>Ortakio diametras, matmenys, m</t>
+          <t>Vandens kondensato masė m H2O, kg</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>Ortakio skerspjūvio plotas F, m2</t>
+          <t>Vandens garų konc. dujose x=mH2O/Vmn*qn, kg/kg</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>Dujų tūrio debitas realiomis sąlygomis Vk = wvid × F, m3/s</t>
+          <t>Sausų dujų tūrio debitas normaliosiomis sąlygomis Vn= Vdr n.s *((1/(1+(x*qn/0.8038)))</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>Dujų tūrio debitas normaliosiomis sąlygomis Vdr n.s =Vk *0,269*(P±ΔP)/(273+t), m3/s</t>
+          <t>Prasiurbtas dujų tūris normaliosiomis sąlygomis Vmn, Nm3</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>Vandens kondensato masė m H2O, kg</t>
+          <t>Išplėstinės neapibrėžties koef. A</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>Vandens garų konc. dujose x=mH2O/Vmn*qn, kg/kg</t>
+          <t>Išplėstinė neapibrėžtis (dujų tūrio debitas) Uv</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>Sausų dujų tūrio debitas normaliosiomis sąlygomis Vn= Vdr n.s *((1/(1+(x*qn/0.8038)))</t>
+          <t>Išplėstinė neapibrėžtis (dujų srauto greitis) Uw</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>Prasiurbtas dujų tūris normaliosiomis sąlygomis Vmn, Nm3</t>
+          <t>Sausų dujų tankis normaliosioms sąlygomis qn, (kg/m3)</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>Išplėstinės neapibrėžties koef. A</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>Išplėstinė neapibrėžtis (dujų tūrio debitas) Uv</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>Išplėstinė neapibrėžtis (dujų srauto greitis) Uw</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>Sausų dujų tankis normaliosioms sąlygomis qn, (kg/m3)</t>
-        </is>
-      </c>
-      <c r="AH4" s="3" t="inlineStr">
         <is>
           <t>Skaičiavimus atliko (inicialai, data)</t>
         </is>
       </c>
     </row>
     <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="n"/>
+      <c r="C5" s="1" t="n"/>
       <c r="D5" s="1" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="D6" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="V6" s="1" t="inlineStr">
-        <is>
-          <t>1,57</t>
-        </is>
-      </c>
-      <c r="W6" s="4">
-        <f>V6*V7</f>
+        <v>42.5</v>
+      </c>
+      <c r="R6" s="1" t="inlineStr">
+        <is>
+          <t>0,86</t>
+        </is>
+      </c>
+      <c r="S6" s="4">
+        <f>R6*R7</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="D7" s="1" t="n">
-        <v>97</v>
-      </c>
-      <c r="V7" s="1" t="inlineStr">
-        <is>
-          <t>1,75</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="D8" s="1" t="n">
-        <v>136</v>
+        <v>71</v>
+      </c>
+      <c r="R7" s="1" t="inlineStr">
+        <is>
+          <t>0,87</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -774,291 +753,4 @@
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumentas" ma:contentTypeID="0x010100BAB57CF81AE55C4698AAD22D302297F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Kurkite naują dokumentą." ma:contentTypeScope="" ma:versionID="49ab401eb4052690d2a2629974c22fd6">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="453e7e53-5eb2-45cf-b2ab-34c867e554b8" xmlns:ns3="aa0d983d-359a-438c-9953-3af1a8ac0831" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab9969d50e0b13c63bc5bd0499c928dc" ns2:_="" ns3:_="">
-    <xsd:import namespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
-    <xsd:import namespace="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="11" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="15" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="16" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Vaizdų žymės" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="993cf2ba-b7a7-49f7-97d1-76e12a88c412" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="23" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="aa0d983d-359a-438c-9953-3af1a8ac0831" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{82c4fa3c-500e-4213-91e5-1b9e2014ea63}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="aa0d983d-359a-438c-9953-3af1a8ac0831">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="21" nillable="true" ma:displayName="Bendrinama su" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="22" nillable="true" ma:displayName="Bendrinta su išsamia informacija" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Turinio tipas"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Antraštė"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="453e7e53-5eb2-45cf-b2ab-34c867e554b8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="aa0d983d-359a-438c-9953-3af1a8ac0831" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A133032C-8DA4-4325-99B9-1B63B6280A77}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01AF40AF-96A7-45CC-AFDC-4FF63D6D9469}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{671E46D8-4263-4B7F-AA57-26D8A7A885B7}"/>
 </file>
--- a/Rezultatai.xlsx
+++ b/Rezultatai.xlsx
@@ -22,8 +22,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -64,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -74,6 +75,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -441,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AD7"/>
+  <dimension ref="A2:AF8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -474,6 +484,8 @@
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="15" customWidth="1" min="29" max="29"/>
     <col width="15" customWidth="1" min="30" max="30"/>
+    <col width="15" customWidth="1" min="31" max="31"/>
+    <col width="15" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -521,115 +533,125 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 4 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>Pito vamzdelio koeficientas, K</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Temperatūra ortakyje t, oC</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Atmosferinis slėgis P, hPa</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Statinis slėgis ortakyje ± ΔP, hPa</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Dujų slėgis kamine Pk= P+ ΔP, hPa</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Dujų mol. masė Ms= qn *22.4, kg/</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Dujų srauto greitis matavimo taškuose, 1 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>Dujų srauto greitis matavimo taškuose, 2 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>Dujų srauto greitis matavimo taškuose, 3 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>Dujų srauto greitis matavimo taškuose, 4 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>Vidutinis dujų srauto greitis ortakyje w, m/s</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>Ortakio diametras, matmenys, m</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>Ortakio skerspjūvio plotas F, m2</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>Dujų tūrio debitas realiomis sąlygomis Vk = wvid × F, m3/s</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>Dujų tūrio debitas normaliosiomis sąlygomis Vdr n.s =Vk *0,269*(P±ΔP)/(273+t), m3/s</t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>Vandens kondensato masė m H2O, kg</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>Vandens garų konc. dujose x=mH2O/Vmn*qn, kg/kg</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>Sausų dujų tūrio debitas normaliosiomis sąlygomis Vn= Vdr n.s *((1/(1+(x*qn/0.8038)))</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>Prasiurbtas dujų tūris normaliosiomis sąlygomis Vmn, Nm3</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>Išplėstinės neapibrėžties koef. A</t>
         </is>
       </c>
-      <c r="AA4" s="3" t="inlineStr">
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>Išplėstinė neapibrėžtis (dujų tūrio debitas) Uv</t>
         </is>
       </c>
-      <c r="AB4" s="3" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr">
         <is>
           <t>Išplėstinė neapibrėžtis (dujų srauto greitis) Uw</t>
         </is>
       </c>
-      <c r="AC4" s="3" t="inlineStr">
+      <c r="AE4" s="3" t="inlineStr">
         <is>
           <t>Sausų dujų tankis normaliosioms sąlygomis qn, (kg/m3)</t>
         </is>
       </c>
-      <c r="AD4" s="3" t="inlineStr">
+      <c r="AF4" s="3" t="inlineStr">
         <is>
           <t>Skaičiavimus atliko (inicialai, data)</t>
         </is>
@@ -640,38 +662,61 @@
       <c r="B5" s="1" t="n"/>
       <c r="C5" s="1" t="n"/>
       <c r="D5" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="AB5" s="6" t="n">
+        <v>0.036</v>
       </c>
     </row>
     <row r="6">
       <c r="D6" s="1" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="R6" s="1" t="inlineStr">
-        <is>
-          <t>0,86</t>
-        </is>
-      </c>
-      <c r="S6" s="4">
-        <f>R6*R7</f>
+        <v>56</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="T6" s="1" t="inlineStr">
+        <is>
+          <t>1,52</t>
+        </is>
+      </c>
+      <c r="U6" s="7">
+        <f>T6*T7</f>
         <v/>
+      </c>
+      <c r="AB6" s="6" t="n">
+        <v>0.036</v>
       </c>
     </row>
     <row r="7">
       <c r="D7" s="1" t="n">
-        <v>71</v>
-      </c>
-      <c r="R7" s="1" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
+        <v>94</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="T7" s="1" t="inlineStr">
+        <is>
+          <t>1,25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0.678</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="A5:A8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -753,4 +798,291 @@
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumentas" ma:contentTypeID="0x010100BAB57CF81AE55C4698AAD22D302297F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Kurkite naują dokumentą." ma:contentTypeScope="" ma:versionID="49ab401eb4052690d2a2629974c22fd6">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="453e7e53-5eb2-45cf-b2ab-34c867e554b8" xmlns:ns3="aa0d983d-359a-438c-9953-3af1a8ac0831" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab9969d50e0b13c63bc5bd0499c928dc" ns2:_="" ns3:_="">
+    <xsd:import namespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
+    <xsd:import namespace="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="11" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="15" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="16" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Vaizdų žymės" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="993cf2ba-b7a7-49f7-97d1-76e12a88c412" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="23" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="aa0d983d-359a-438c-9953-3af1a8ac0831" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{82c4fa3c-500e-4213-91e5-1b9e2014ea63}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="aa0d983d-359a-438c-9953-3af1a8ac0831">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="21" nillable="true" ma:displayName="Bendrinama su" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="22" nillable="true" ma:displayName="Bendrinta su išsamia informacija" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Turinio tipas"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Antraštė"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="453e7e53-5eb2-45cf-b2ab-34c867e554b8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="aa0d983d-359a-438c-9953-3af1a8ac0831" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D596D96-774B-4DD9-B8B2-43EDF3AE7B3E}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A734439-A10D-4E61-8C11-C2776BA11DB2}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{961E9FE6-A5BC-4AE6-9A0C-698CF88F8BD3}"/>
 </file>
--- a/Rezultatai.xlsx
+++ b/Rezultatai.xlsx
@@ -47,7 +47,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -61,11 +61,12 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -86,6 +87,16 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -451,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AF8"/>
+  <dimension ref="A2:Z17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -480,12 +491,6 @@
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="15" customWidth="1" min="25" max="25"/>
     <col width="15" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="15" customWidth="1" min="29" max="29"/>
-    <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="15" customWidth="1" min="31" max="31"/>
-    <col width="15" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -523,135 +528,105 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Išmatuotas diferencinis slėgis taškuose 2 linija, Pdi, hPa</t>
+          <t>Pito vamzdelio koeficientas, K</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Išmatuotas diferencinis slėgis taškuose 3 linija, Pdi, hPa</t>
+          <t>Temperatūra ortakyje t, oC</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Išmatuotas diferencinis slėgis taškuose 4 linija, Pdi, hPa</t>
+          <t>Atmosferinis slėgis P, hPa</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Pito vamzdelio koeficientas, K</t>
+          <t>Statinis slėgis ortakyje ± ΔP, hPa</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Temperatūra ortakyje t, oC</t>
+          <t>Dujų slėgis kamine Pk= P+ ΔP, hPa</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Atmosferinis slėgis P, hPa</t>
+          <t>Dujų mol. masė Ms= qn *22.4, kg/</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Statinis slėgis ortakyje ± ΔP, hPa</t>
+          <t>Dujų srauto greitis matavimo taškuose, 1 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Dujų slėgis kamine Pk= P+ ΔP, hPa</t>
+          <t>Vidutinis dujų srauto greitis ortakyje w, m/s</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>Dujų mol. masė Ms= qn *22.4, kg/</t>
+          <t>Ortakio diametras, matmenys, m</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Dujų srauto greitis matavimo taškuose, 1 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+          <t>Ortakio skerspjūvio plotas F, m2</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Dujų srauto greitis matavimo taškuose, 2 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+          <t>Dujų tūrio debitas realiomis sąlygomis Vk = wvid × F, m3/s</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>Dujų srauto greitis matavimo taškuose, 3 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+          <t>Dujų tūrio debitas normaliosiomis sąlygomis Vdr n.s =Vk *0,269*(P±ΔP)/(273+t), m3/s</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>Dujų srauto greitis matavimo taškuose, 4 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+          <t>Vandens kondensato masė m H2O, kg</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>Vidutinis dujų srauto greitis ortakyje w, m/s</t>
+          <t>Vandens garų konc. dujose x=mH2O/Vmn*qn, kg/kg</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Ortakio diametras, matmenys, m</t>
+          <t>Sausų dujų tūrio debitas normaliosiomis sąlygomis Vn= Vdr n.s *((1/(1+(x*qn/0.8038)))</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>Ortakio skerspjūvio plotas F, m2</t>
+          <t>Prasiurbtas dujų tūris normaliosiomis sąlygomis Vmn, Nm3</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>Dujų tūrio debitas realiomis sąlygomis Vk = wvid × F, m3/s</t>
+          <t>Išplėstinės neapibrėžties koef. A</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>Dujų tūrio debitas normaliosiomis sąlygomis Vdr n.s =Vk *0,269*(P±ΔP)/(273+t), m3/s</t>
+          <t>Išplėstinė neapibrėžtis (dujų tūrio debitas) Uv</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>Vandens kondensato masė m H2O, kg</t>
+          <t>Išplėstinė neapibrėžtis (dujų srauto greitis) Uw</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>Vandens garų konc. dujose x=mH2O/Vmn*qn, kg/kg</t>
+          <t>Sausų dujų tankis normaliosioms sąlygomis qn, (kg/m3)</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>Sausų dujų tūrio debitas normaliosiomis sąlygomis Vn= Vdr n.s *((1/(1+(x*qn/0.8038)))</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>Prasiurbtas dujų tūris normaliosiomis sąlygomis Vmn, Nm3</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>Išplėstinės neapibrėžties koef. A</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>Išplėstinė neapibrėžtis (dujų tūrio debitas) Uv</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>Išplėstinė neapibrėžtis (dujų srauto greitis) Uw</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>Sausų dujų tankis normaliosioms sąlygomis qn, (kg/m3)</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr">
         <is>
           <t>Skaičiavimus atliko (inicialai, data)</t>
         </is>
@@ -662,61 +637,128 @@
       <c r="B5" s="1" t="n"/>
       <c r="C5" s="1" t="n"/>
       <c r="D5" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>0.678</v>
-      </c>
-      <c r="AB5" s="6" t="n">
-        <v>0.036</v>
+        <v>5</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>1,20</t>
+        </is>
+      </c>
+      <c r="O5" s="7">
+        <f>(N5^2*3.14)/4</f>
+        <v/>
+      </c>
+      <c r="V5" s="6" t="n">
+        <v>0.079</v>
       </c>
     </row>
     <row r="6">
       <c r="D6" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>0.678</v>
-      </c>
-      <c r="T6" s="1" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="U6" s="7">
-        <f>T6*T7</f>
-        <v/>
-      </c>
-      <c r="AB6" s="6" t="n">
-        <v>0.036</v>
+        <v>8</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="V6" s="6" t="n">
+        <v>0.079</v>
       </c>
     </row>
     <row r="7">
       <c r="D7" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>0.678</v>
-      </c>
-      <c r="T7" s="1" t="inlineStr">
-        <is>
-          <t>1,25</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.827</v>
       </c>
     </row>
     <row r="8">
       <c r="D8" s="1" t="n">
-        <v>131</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>0.678</v>
+        <v>20</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0.827</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.827</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="D10" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.827</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="D11" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>0.827</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.827</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="D13" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.827</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="D14" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0.827</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="D15" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.827</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="D16" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.827</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0.827</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="A5:A17"/>
+    <mergeCell ref="B5:B17"/>
+    <mergeCell ref="C5:C17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -728,9 +770,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A3:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Skaičiuoklė kietųjų dalelių koncentracijai nustatyti. H2O skaičiavimas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Ėminių ėmimo laikas t, min.</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Paėmimo greitis, l/min</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Atmosferinis slėgis, hPa</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Išretėjimas, -hPa</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Temperatūra prie aspiratoriaus, Vtr oC</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Dujų tūris normaliomis sąlygomis, Vn l.</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Prasiurbtas dujų tūris normaliosiomis sąlygomis Vmn, Nm3</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Vandens kondensato masė m H2O, kg</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Sausų dujų tankis normaliosioms sąlygomis qn (kg/m3)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Drėgmės kiekis X (%) (izokinetinei sistemai)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Pastabos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:L3"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -741,9 +866,153 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A5:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Matavimo data</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Ėminių registracijos Nr. T-107-2026-E-</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Objekto pavadinimas, adresas, taršos šaltinio Nr.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Ortakio skersmuo d, m</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Skerspjūvio plotas A (m2)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Temperatūra ortakyje tor (°C)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Vidutinis srauto greitis ortakyje wor (m/s)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Atmosferinis slėgis P (hPa)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Statinis slėgis ortakyje ΔPor (hPa)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Slėgis prieš rotametrą ΔPr (±hPa)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Antgalio diametras da (mm)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Prasiurbtas dujų tūris Vm (m3)</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Siurbimo laikas t (min)</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Siurbimo greitis Vo (l/min)</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>Siurbiamų dujų temperatūra prieš rotametrą tr (°C)</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>O2iš (%) (ore 21 %)</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>CO2iš (%) (ore 0,04 %)</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>Darbuotojo inicialai, data</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>Pastabos</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>Išmatuota O2 koncentracija (%)</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>Išmatuota CO2 koncentracija (%)</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>Temperatūra ortakyje tor (°C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>1,20</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -754,9 +1023,108 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A2:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Skaičiuoklė kietųjų dalelių koncentracijai nustatyti. Izokinetiškumo nustatymas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Matavimo data</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Ėminių registracijos Nr. T-107-2026-E-</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Objekto pavadinimas, adresas, taršos šaltinio Nr.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Prasiurbtas dujų tūris Vm (m3)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Prasiurbtas dujų tūris normaliosiomis sąlygomis Vmn (Nm3)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Prasiurbto dujų tūrio normaliosiomis sąlygomis suma Vmn(sum) (Nm3)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Sausų dujų tankis normaliosioms sąlygomis qn (kg/m3)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Drėgmės kiekis X (%)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Pratrauktas drėgnų dujų tūris realiomis sąlygomis Vmk (m3)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Dujų srauto greitis antgalyje v antg. (m/s)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Izokinetiškumas (0,95-1,15)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Izokinetiškumo vidurkis (0,95-1,15)</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Skaičiavimus atlikusio asmens inicialai, data</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Pastabos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:N2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -767,9 +1135,120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A2:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Skaičiuoklė kietųjų dalelių koncentracijai nustatyti. Kietųjų dalelių koncentracijos nustatymas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Matavimo data</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Ėminių registracijos Nr. T-107-2026-E-</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Objekto pavadinimas, adresas, taršos šaltinio Nr.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Filtro Nr.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Filtro svoris prieš KD ėmimą mpr (g)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Filtro svoris po KD ėmimo mpo (g)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Tuščiojo ėminio KD svoris mt (g)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Nuosėdų kiekis mn (g)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Indų svorių pokytis mIt (g)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Sausų dujų tūris n.s. Vmn (Nm3)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Kietų dalelių koncentracija c1 (neįvert. O2) (mg/Nm3)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Tuščiojo filtro vertė mft (mg/m3) (&lt; 2 mg/m3)</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Surinktų dulkių ir tuščiojo ėminio santykis mFtk (&gt;5)</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Skaičiavimus atlikusio asmens inicialai, data</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>Filtrų skaičius Fsk (vnt.)</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Pastabos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -780,9 +1259,150 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A2:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Skaičiuoklė kietųjų dalelių koncentracijai nustatyti. Svėrimas</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Ėminių registracijos Nr. T-107-2026-E-</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Objekto pavadinimas, adresas, taršos šaltinio Nr.</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Filtro/ indo Nr.</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Tuščio filtro/indo svėrimo data</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Filtro/indo svoris prieš KD ėmimą mpr (g)</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="n"/>
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Atsakingo asmens inicialai, data</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Filtro/indo su ėminiu svėrimo data</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>Filtro/indo svoris po KD ėmimo mpo (g)</t>
+        </is>
+      </c>
+      <c r="K4" s="11" t="n"/>
+      <c r="L4" s="11" t="n"/>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>Kietųjų dalelių svoris mf/Svorių pokytis (g) (&lt;2,20 g filtro talpumas)</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>Atsakingo asmens inicialai, data</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>Pastabos</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="n"/>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="n"/>
+      <c r="I5" s="11" t="n"/>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M5" s="11" t="n"/>
+      <c r="N5" s="11" t="n"/>
+      <c r="O5" s="11" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="J4:L4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -793,9 +1413,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A3:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Patikrinimas, ar planuojamas surinkti dulkių kiekis suderinamas su tuščiojo ėminio verte ir ar filtras nebus per daug apkrautas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Planuojama surinkti dulkių masė m, g (&lt;2,20 g)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Mažiausia ėminio ėmimo trukmė t, 30 min</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Tikėtina dulkių koncentracija cexs, mg/Nm3;</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Planuojamas dujų tūrio siurbimo greitis matavimo metu ortakio sąlygomis Vo, l/min.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:D3"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1076,13 +1735,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D596D96-774B-4DD9-B8B2-43EDF3AE7B3E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{993B1FAA-30F2-4307-BC21-9627AB878FB9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A734439-A10D-4E61-8C11-C2776BA11DB2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FB2E5CD-0090-4A92-B693-912EDC998A43}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{961E9FE6-A5BC-4AE6-9A0C-698CF88F8BD3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D9184D5-5844-4593-B5F7-CC80AB64064E}"/>
 </file>
--- a/Rezultatai.xlsx
+++ b/Rezultatai.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:Z17"/>
+  <dimension ref="A3:AB12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -592,275 +592,239 @@
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="15" customWidth="1" min="25" max="25"/>
     <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Debitas pagal matuotą diferencinį slėgį</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="130" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="5" ht="130" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Matavimo data</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Ėminių registracijos Nr. T-107-2026-E-</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Objekto pavadinimas, adresas, taršos šaltinio Nr.</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Matavimo taškai ortakyje nuo vidinės sienelės, cm</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Išmatuotas diferencinis slėgis taškuose 1 linija, Pdi, hPa</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 2 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Pito vamzdelio koeficientas, K</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Temperatūra ortakyje t, oC</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Atmosferinis slėgis P, hPa</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Statinis slėgis ortakyje ± ΔP, hPa</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Dujų slėgis kamine Pk= P+ ΔP, hPa</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Dujų mol. masė Ms= qn *22.4, kg/</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Dujų srauto greitis matavimo taškuose, 1 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Dujų srauto greitis matavimo taškuose, 2 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Vidutinis dujų srauto greitis ortakyje w, m/s</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Ortakio diametras, matmenys, m</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Ortakio skerspjūvio plotas F, m2</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>Dujų tūrio debitas realiomis sąlygomis Vk = wvid × F, m3/s</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>Dujų tūrio debitas normaliosiomis sąlygomis Vdr n.s =Vk *0,269*(P±ΔP)/(273+t), m3/s</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>Vandens kondensato masė m H2O, kg</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>Vandens garų konc. dujose x=mH2O/Vmn*qn, kg/kg</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>Sausų dujų tūrio debitas normaliosiomis sąlygomis Vn= Vdr n.s *((1/(1+(x*qn/0.8038)))</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t>Prasiurbtas dujų tūris normaliosiomis sąlygomis Vmn, Nm3</t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t>Išplėstinės neapibrėžties koef. A</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>Išplėstinė neapibrėžtis (dujų tūrio debitas) Uv</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="Z5" s="3" t="inlineStr">
         <is>
           <t>Išplėstinė neapibrėžtis (dujų srauto greitis) Uw</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>Sausų dujų tankis normaliosioms sąlygomis qn, (kg/m3)</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="AB5" s="3" t="inlineStr">
         <is>
           <t>Skaičiavimus atliko (inicialai, data)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="1" t="n"/>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n">
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="n"/>
+      <c r="D6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G6" s="6" t="n">
         <v>0.827</v>
       </c>
-      <c r="N5" s="1" t="inlineStr">
+      <c r="P6" s="1" t="inlineStr">
         <is>
           <t>1,20</t>
         </is>
       </c>
-      <c r="O5" s="7">
-        <f>(N5^2*3.14)/4</f>
+      <c r="Q6" s="7">
+        <f>(P6^2*3.14)/4</f>
         <v/>
       </c>
-      <c r="V5" s="6" t="n">
-        <v>0.079</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="D6" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>0.827</v>
-      </c>
-      <c r="V6" s="6" t="n">
+      <c r="X6" s="6" t="n">
         <v>0.079</v>
       </c>
     </row>
     <row r="7">
       <c r="D7" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="F7" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G7" s="6" t="n">
         <v>0.827</v>
+      </c>
+      <c r="X7" s="6" t="n">
+        <v>0.079</v>
       </c>
     </row>
     <row r="8">
       <c r="D8" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="F8" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="G8" s="6" t="n">
         <v>0.827</v>
       </c>
     </row>
     <row r="9">
       <c r="D9" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="F9" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G9" s="6" t="n">
         <v>0.827</v>
       </c>
     </row>
     <row r="10">
       <c r="D10" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="F10" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="G10" s="6" t="n">
         <v>0.827</v>
       </c>
     </row>
     <row r="11">
       <c r="D11" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="F11" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="G11" s="6" t="n">
         <v>0.827</v>
       </c>
     </row>
     <row r="12">
       <c r="D12" s="1" t="n">
-        <v>81</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>0.827</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="D13" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>0.827</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="D14" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>0.827</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="D15" s="1" t="n">
-        <v>106</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>0.827</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="D16" s="1" t="n">
-        <v>112</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>0.827</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="D17" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G12" s="6" t="n">
         <v>0.827</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A5:A17"/>
-    <mergeCell ref="B5:B17"/>
-    <mergeCell ref="A2:Z2"/>
-    <mergeCell ref="C5:C17"/>
+    <mergeCell ref="A3:AB3"/>
+    <mergeCell ref="B6:B12"/>
+    <mergeCell ref="C6:C12"/>
+    <mergeCell ref="A6:A12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1121,7 +1085,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <f>'Greitis'!O5</f>
+        <f>'Greitis'!Q6</f>
         <v/>
       </c>
     </row>
@@ -1523,23 +1487,25 @@
       <c r="N6" s="16" t="n"/>
       <c r="O6" s="20" t="inlineStr">
         <is>
-          <t>1 linija, 1 filtras</t>
+          <t>2 linijos, 3 filtrai</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="21" t="n"/>
       <c r="B7" s="21" t="n"/>
-      <c r="C7" s="12" t="n"/>
+      <c r="C7" s="17" t="n">
+        <v>2</v>
+      </c>
       <c r="D7" s="21" t="n"/>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="18" t="n"/>
       <c r="H7" s="21" t="n"/>
       <c r="I7" s="21" t="n"/>
-      <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
+      <c r="J7" s="18" t="n"/>
+      <c r="K7" s="18" t="n"/>
+      <c r="L7" s="18" t="n"/>
       <c r="M7" s="19" t="n"/>
       <c r="N7" s="21" t="n"/>
       <c r="O7" s="12" t="n"/>
@@ -1547,16 +1513,18 @@
     <row r="8">
       <c r="A8" s="21" t="n"/>
       <c r="B8" s="21" t="n"/>
-      <c r="C8" s="12" t="n"/>
+      <c r="C8" s="17" t="n">
+        <v>3</v>
+      </c>
       <c r="D8" s="21" t="n"/>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="12" t="n"/>
-      <c r="G8" s="12" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="18" t="n"/>
       <c r="H8" s="21" t="n"/>
       <c r="I8" s="21" t="n"/>
-      <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
+      <c r="J8" s="18" t="n"/>
+      <c r="K8" s="18" t="n"/>
+      <c r="L8" s="18" t="n"/>
       <c r="M8" s="19" t="n"/>
       <c r="N8" s="21" t="n"/>
       <c r="O8" s="12" t="n"/>
@@ -1819,4 +1787,291 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumentas" ma:contentTypeID="0x010100BAB57CF81AE55C4698AAD22D302297F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Kurkite naują dokumentą." ma:contentTypeScope="" ma:versionID="49ab401eb4052690d2a2629974c22fd6">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="453e7e53-5eb2-45cf-b2ab-34c867e554b8" xmlns:ns3="aa0d983d-359a-438c-9953-3af1a8ac0831" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab9969d50e0b13c63bc5bd0499c928dc" ns2:_="" ns3:_="">
+    <xsd:import namespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
+    <xsd:import namespace="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="11" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="15" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="16" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Vaizdų žymės" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="993cf2ba-b7a7-49f7-97d1-76e12a88c412" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="23" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="aa0d983d-359a-438c-9953-3af1a8ac0831" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{82c4fa3c-500e-4213-91e5-1b9e2014ea63}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="aa0d983d-359a-438c-9953-3af1a8ac0831">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="21" nillable="true" ma:displayName="Bendrinama su" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="22" nillable="true" ma:displayName="Bendrinta su išsamia informacija" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Turinio tipas"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Antraštė"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="453e7e53-5eb2-45cf-b2ab-34c867e554b8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="aa0d983d-359a-438c-9953-3af1a8ac0831" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D17A693-FB25-430D-B6B5-6C6FA6A677DC}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C6E3F74-698D-4806-8770-263B1DB4FFAE}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F82DFE4-46CF-46BA-8AA9-D8B27E229D52}"/>
 </file>
--- a/Rezultatai.xlsx
+++ b/Rezultatai.xlsx
@@ -145,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -169,6 +169,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -563,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:AB12"/>
+  <dimension ref="A3:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -594,6 +597,10 @@
     <col width="15" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
+    <col width="15" customWidth="1" min="30" max="30"/>
+    <col width="15" customWidth="1" min="31" max="31"/>
+    <col width="15" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -636,110 +643,130 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 3 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 4 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>Pito vamzdelio koeficientas, K</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Temperatūra ortakyje t, oC</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Atmosferinis slėgis P, hPa</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Statinis slėgis ortakyje ± ΔP, hPa</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Dujų slėgis kamine Pk= P+ ΔP, hPa</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Dujų mol. masė Ms= qn *22.4, kg/</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Dujų srauto greitis matavimo taškuose, 1 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Dujų srauto greitis matavimo taškuose, 2 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>Dujų srauto greitis matavimo taškuose, 3 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>Dujų srauto greitis matavimo taškuose, 4 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>Vidutinis dujų srauto greitis ortakyje w, m/s</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>Ortakio diametras, matmenys, m</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>Ortakio skerspjūvio plotas F, m2</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>Dujų tūrio debitas realiomis sąlygomis Vk = wvid × F, m3/s</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t>Dujų tūrio debitas normaliosiomis sąlygomis Vdr n.s =Vk *0,269*(P±ΔP)/(273+t), m3/s</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t>Vandens kondensato masė m H2O, kg</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>Vandens garų konc. dujose x=mH2O/Vmn*qn, kg/kg</t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
+      <c r="Z5" s="3" t="inlineStr">
         <is>
           <t>Sausų dujų tūrio debitas normaliosiomis sąlygomis Vn= Vdr n.s *((1/(1+(x*qn/0.8038)))</t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr">
+      <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>Prasiurbtas dujų tūris normaliosiomis sąlygomis Vmn, Nm3</t>
         </is>
       </c>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="AB5" s="3" t="inlineStr">
         <is>
           <t>Išplėstinės neapibrėžties koef. A</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
+      <c r="AC5" s="3" t="inlineStr">
         <is>
           <t>Išplėstinė neapibrėžtis (dujų tūrio debitas) Uv</t>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
+      <c r="AD5" s="3" t="inlineStr">
         <is>
           <t>Išplėstinė neapibrėžtis (dujų srauto greitis) Uw</t>
         </is>
       </c>
-      <c r="AA5" s="3" t="inlineStr">
+      <c r="AE5" s="3" t="inlineStr">
         <is>
           <t>Sausų dujų tankis normaliosioms sąlygomis qn, (kg/m3)</t>
         </is>
       </c>
-      <c r="AB5" s="3" t="inlineStr">
+      <c r="AF5" s="3" t="inlineStr">
         <is>
           <t>Skaičiavimus atliko (inicialai, data)</t>
         </is>
@@ -750,81 +777,62 @@
       <c r="B6" s="1" t="n"/>
       <c r="C6" s="1" t="n"/>
       <c r="D6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="I6" s="6" t="n">
         <v>0.827</v>
       </c>
-      <c r="P6" s="1" t="inlineStr">
-        <is>
-          <t>1,20</t>
-        </is>
-      </c>
-      <c r="Q6" s="7">
-        <f>(P6^2*3.14)/4</f>
-        <v/>
-      </c>
-      <c r="X6" s="6" t="n">
+      <c r="AB6" s="6" t="n">
         <v>0.079</v>
       </c>
     </row>
     <row r="7">
       <c r="D7" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G7" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="I7" s="6" t="n">
         <v>0.827</v>
       </c>
-      <c r="X7" s="6" t="n">
+      <c r="T7" s="1" t="inlineStr">
+        <is>
+          <t>1,50</t>
+        </is>
+      </c>
+      <c r="U7" s="7">
+        <f>T7*T8</f>
+        <v/>
+      </c>
+      <c r="AB7" s="6" t="n">
         <v>0.079</v>
       </c>
     </row>
     <row r="8">
       <c r="D8" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="G8" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="I8" s="6" t="n">
         <v>0.827</v>
+      </c>
+      <c r="T8" s="1" t="inlineStr">
+        <is>
+          <t>1,50</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="D9" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>0.827</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="D10" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>0.827</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="D11" s="1" t="n">
-        <v>104</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>0.827</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="D12" s="1" t="n">
-        <v>115</v>
-      </c>
-      <c r="G12" s="6" t="n">
+        <v>131</v>
+      </c>
+      <c r="I9" s="6" t="n">
         <v>0.827</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A3:AB3"/>
-    <mergeCell ref="B6:B12"/>
-    <mergeCell ref="C6:C12"/>
-    <mergeCell ref="A6:A12"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="C6:C9"/>
+    <mergeCell ref="A3:AF3"/>
+    <mergeCell ref="A6:A9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -932,7 +940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:V6"/>
+  <dimension ref="A2:AA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -957,6 +965,11 @@
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -984,7 +997,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Ortakio skersmuo d, m</t>
+          <t>Ortakio matmenys, m</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -999,7 +1012,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Vidutinis srauto greitis ortakyje wor (m/s)</t>
+          <t>Srauto greitis ortakyje wor (m/s)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -1077,15 +1090,36 @@
           <t>Temperatūra ortakyje tor (°C)</t>
         </is>
       </c>
+      <c r="W5" s="9" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>Srauto greitis ortakyje wor (m/s)</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>Izokinetiškumas (0,95-1,15)</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Pito vamzdelio koeficientas, K</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>1,20</t>
-        </is>
-      </c>
-      <c r="E6" s="10">
-        <f>'Greitis'!Q6</f>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>1,50 x 1,50</t>
+        </is>
+      </c>
+      <c r="E6" s="11">
+        <f>'Greitis'!U7</f>
         <v/>
       </c>
     </row>
@@ -1367,351 +1401,351 @@
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Ėminių registracijos Nr. T-107-2026-E-</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Objekto pavadinimas, adresas, taršos šaltinio Nr.</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Filtro/ indo Nr.</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Tuščio filtro/indo svėrimo data</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>Filtro/indo svoris prieš KD ėmimą mpr (g)</t>
         </is>
       </c>
-      <c r="F4" s="13" t="n"/>
-      <c r="G4" s="14" t="n"/>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>Atsakingo asmens inicialai, data</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>Filtro/indo su ėminiu svėrimo data</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>Filtro/indo svoris po KD ėmimo mpo (g)</t>
         </is>
       </c>
-      <c r="K4" s="13" t="n"/>
-      <c r="L4" s="14" t="n"/>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="15" t="n"/>
+      <c r="M4" s="12" t="inlineStr">
         <is>
           <t>Kietųjų dalelių svoris mf/Svorių pokytis (g) (&lt;2,20 g filtro talpumas)</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N4" s="12" t="inlineStr">
         <is>
           <t>Atsakingo asmens inicialai, data</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O4" s="12" t="inlineStr">
         <is>
           <t>Pastabos</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n"/>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H5" s="15" t="n"/>
-      <c r="I5" s="15" t="n"/>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="H5" s="16" t="n"/>
+      <c r="I5" s="16" t="n"/>
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M5" s="15" t="n"/>
-      <c r="N5" s="15" t="n"/>
-      <c r="O5" s="15" t="n"/>
+      <c r="M5" s="16" t="n"/>
+      <c r="N5" s="16" t="n"/>
+      <c r="O5" s="16" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n"/>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="17" t="n">
+      <c r="A6" s="17" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="18" t="n"/>
-      <c r="F6" s="18" t="n"/>
-      <c r="G6" s="18" t="n"/>
-      <c r="H6" s="16" t="n"/>
-      <c r="I6" s="16" t="n"/>
-      <c r="J6" s="18" t="n"/>
-      <c r="K6" s="18" t="n"/>
-      <c r="L6" s="18" t="n"/>
-      <c r="M6" s="19" t="n"/>
-      <c r="N6" s="16" t="n"/>
-      <c r="O6" s="20" t="inlineStr">
-        <is>
-          <t>2 linijos, 3 filtrai</t>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="19" t="n"/>
+      <c r="F6" s="19" t="n"/>
+      <c r="G6" s="19" t="n"/>
+      <c r="H6" s="17" t="n"/>
+      <c r="I6" s="17" t="n"/>
+      <c r="J6" s="19" t="n"/>
+      <c r="K6" s="19" t="n"/>
+      <c r="L6" s="19" t="n"/>
+      <c r="M6" s="20" t="n"/>
+      <c r="N6" s="17" t="n"/>
+      <c r="O6" s="21" t="inlineStr">
+        <is>
+          <t>4 linijos, 3 filtrai</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n"/>
-      <c r="B7" s="21" t="n"/>
-      <c r="C7" s="17" t="n">
+      <c r="A7" s="22" t="n"/>
+      <c r="B7" s="22" t="n"/>
+      <c r="C7" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="21" t="n"/>
-      <c r="E7" s="18" t="n"/>
-      <c r="F7" s="18" t="n"/>
-      <c r="G7" s="18" t="n"/>
-      <c r="H7" s="21" t="n"/>
-      <c r="I7" s="21" t="n"/>
-      <c r="J7" s="18" t="n"/>
-      <c r="K7" s="18" t="n"/>
-      <c r="L7" s="18" t="n"/>
-      <c r="M7" s="19" t="n"/>
-      <c r="N7" s="21" t="n"/>
-      <c r="O7" s="12" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="19" t="n"/>
+      <c r="F7" s="19" t="n"/>
+      <c r="G7" s="19" t="n"/>
+      <c r="H7" s="22" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="19" t="n"/>
+      <c r="K7" s="19" t="n"/>
+      <c r="L7" s="19" t="n"/>
+      <c r="M7" s="20" t="n"/>
+      <c r="N7" s="22" t="n"/>
+      <c r="O7" s="13" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="n"/>
-      <c r="B8" s="21" t="n"/>
-      <c r="C8" s="17" t="n">
+      <c r="A8" s="22" t="n"/>
+      <c r="B8" s="22" t="n"/>
+      <c r="C8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="21" t="n"/>
-      <c r="E8" s="18" t="n"/>
-      <c r="F8" s="18" t="n"/>
-      <c r="G8" s="18" t="n"/>
-      <c r="H8" s="21" t="n"/>
-      <c r="I8" s="21" t="n"/>
-      <c r="J8" s="18" t="n"/>
-      <c r="K8" s="18" t="n"/>
-      <c r="L8" s="18" t="n"/>
-      <c r="M8" s="19" t="n"/>
-      <c r="N8" s="21" t="n"/>
-      <c r="O8" s="12" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="19" t="n"/>
+      <c r="G8" s="19" t="n"/>
+      <c r="H8" s="22" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="19" t="n"/>
+      <c r="K8" s="19" t="n"/>
+      <c r="L8" s="19" t="n"/>
+      <c r="M8" s="20" t="n"/>
+      <c r="N8" s="22" t="n"/>
+      <c r="O8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n"/>
-      <c r="B9" s="21" t="n"/>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="A9" s="22" t="n"/>
+      <c r="B9" s="22" t="n"/>
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="21" t="n"/>
-      <c r="E9" s="18" t="n"/>
-      <c r="F9" s="18" t="n"/>
-      <c r="G9" s="18" t="n"/>
-      <c r="H9" s="21" t="n"/>
-      <c r="I9" s="21" t="n"/>
-      <c r="J9" s="18" t="n"/>
-      <c r="K9" s="18" t="n"/>
-      <c r="L9" s="18" t="n"/>
-      <c r="M9" s="19" t="n"/>
-      <c r="N9" s="21" t="n"/>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="19" t="n"/>
+      <c r="H9" s="22" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="19" t="n"/>
+      <c r="K9" s="19" t="n"/>
+      <c r="L9" s="19" t="n"/>
+      <c r="M9" s="20" t="n"/>
+      <c r="N9" s="22" t="n"/>
+      <c r="O9" s="23" t="inlineStr">
         <is>
           <t>Tuščiasis ėminys (mt)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="n"/>
-      <c r="B10" s="21" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="21" t="n"/>
-      <c r="I10" s="21" t="n"/>
-      <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
-      <c r="M10" s="12" t="n"/>
-      <c r="N10" s="21" t="n"/>
-      <c r="O10" s="12" t="n"/>
+      <c r="A10" s="22" t="n"/>
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="13" t="n"/>
+      <c r="K10" s="13" t="n"/>
+      <c r="L10" s="13" t="n"/>
+      <c r="M10" s="13" t="n"/>
+      <c r="N10" s="22" t="n"/>
+      <c r="O10" s="13" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="n"/>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="A11" s="22" t="n"/>
+      <c r="B11" s="22" t="n"/>
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="18" t="n"/>
-      <c r="F11" s="18" t="n"/>
-      <c r="G11" s="18" t="n"/>
-      <c r="H11" s="21" t="n"/>
-      <c r="I11" s="21" t="n"/>
-      <c r="J11" s="18" t="n"/>
-      <c r="K11" s="18" t="n"/>
-      <c r="L11" s="18" t="n"/>
-      <c r="M11" s="19" t="n"/>
-      <c r="N11" s="21" t="n"/>
-      <c r="O11" s="22" t="inlineStr">
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="19" t="n"/>
+      <c r="H11" s="22" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="19" t="n"/>
+      <c r="K11" s="19" t="n"/>
+      <c r="L11" s="19" t="n"/>
+      <c r="M11" s="20" t="n"/>
+      <c r="N11" s="22" t="n"/>
+      <c r="O11" s="23" t="inlineStr">
         <is>
           <t>Išplautos nuosėdos (mn)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="n"/>
-      <c r="B12" s="21" t="n"/>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="A12" s="22" t="n"/>
+      <c r="B12" s="22" t="n"/>
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="18" t="n"/>
-      <c r="F12" s="18" t="n"/>
-      <c r="G12" s="18" t="n"/>
-      <c r="H12" s="21" t="n"/>
-      <c r="I12" s="21" t="n"/>
-      <c r="J12" s="18" t="n"/>
-      <c r="K12" s="18" t="n"/>
-      <c r="L12" s="18" t="n"/>
-      <c r="M12" s="19" t="n"/>
-      <c r="N12" s="21" t="n"/>
-      <c r="O12" s="22" t="inlineStr">
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="19" t="n"/>
+      <c r="H12" s="22" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="19" t="n"/>
+      <c r="K12" s="19" t="n"/>
+      <c r="L12" s="19" t="n"/>
+      <c r="M12" s="20" t="n"/>
+      <c r="N12" s="22" t="n"/>
+      <c r="O12" s="23" t="inlineStr">
         <is>
           <t>Išvalytos ėminių sistemos tuščiasis ėminys (mIt)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n"/>
-      <c r="B13" s="21" t="n"/>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="A13" s="22" t="n"/>
+      <c r="B13" s="22" t="n"/>
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D13" s="21" t="n"/>
-      <c r="E13" s="18" t="n"/>
-      <c r="F13" s="18" t="n"/>
-      <c r="G13" s="18" t="n"/>
-      <c r="H13" s="21" t="n"/>
-      <c r="I13" s="21" t="n"/>
-      <c r="J13" s="18" t="n"/>
-      <c r="K13" s="18" t="n"/>
-      <c r="L13" s="18" t="n"/>
-      <c r="M13" s="19" t="n"/>
-      <c r="N13" s="21" t="n"/>
-      <c r="O13" s="22" t="inlineStr">
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="19" t="n"/>
+      <c r="G13" s="19" t="n"/>
+      <c r="H13" s="22" t="n"/>
+      <c r="I13" s="22" t="n"/>
+      <c r="J13" s="19" t="n"/>
+      <c r="K13" s="19" t="n"/>
+      <c r="L13" s="19" t="n"/>
+      <c r="M13" s="20" t="n"/>
+      <c r="N13" s="22" t="n"/>
+      <c r="O13" s="23" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt1)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="n"/>
-      <c r="B14" s="21" t="n"/>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="A14" s="22" t="n"/>
+      <c r="B14" s="22" t="n"/>
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="D14" s="21" t="n"/>
-      <c r="E14" s="18" t="n"/>
-      <c r="F14" s="18" t="n"/>
-      <c r="G14" s="18" t="n"/>
-      <c r="H14" s="21" t="n"/>
-      <c r="I14" s="21" t="n"/>
-      <c r="J14" s="18" t="n"/>
-      <c r="K14" s="18" t="n"/>
-      <c r="L14" s="18" t="n"/>
-      <c r="M14" s="19" t="n"/>
-      <c r="N14" s="21" t="n"/>
-      <c r="O14" s="22" t="inlineStr">
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19" t="n"/>
+      <c r="H14" s="22" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="19" t="n"/>
+      <c r="K14" s="19" t="n"/>
+      <c r="L14" s="19" t="n"/>
+      <c r="M14" s="20" t="n"/>
+      <c r="N14" s="22" t="n"/>
+      <c r="O14" s="23" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt2)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n"/>
-      <c r="B15" s="21" t="n"/>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="A15" s="22" t="n"/>
+      <c r="B15" s="22" t="n"/>
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D15" s="21" t="n"/>
-      <c r="E15" s="18" t="n"/>
-      <c r="F15" s="18" t="n"/>
-      <c r="G15" s="18" t="n"/>
-      <c r="H15" s="21" t="n"/>
-      <c r="I15" s="21" t="n"/>
-      <c r="J15" s="18" t="n"/>
-      <c r="K15" s="18" t="n"/>
-      <c r="L15" s="18" t="n"/>
-      <c r="M15" s="19" t="n"/>
-      <c r="N15" s="21" t="n"/>
-      <c r="O15" s="22" t="inlineStr">
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="19" t="n"/>
+      <c r="G15" s="19" t="n"/>
+      <c r="H15" s="22" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="19" t="n"/>
+      <c r="K15" s="19" t="n"/>
+      <c r="L15" s="19" t="n"/>
+      <c r="M15" s="20" t="n"/>
+      <c r="N15" s="22" t="n"/>
+      <c r="O15" s="23" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt3)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="n"/>
-      <c r="B16" s="23" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="23" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="23" t="n"/>
-      <c r="I16" s="23" t="n"/>
-      <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="12" t="n"/>
-      <c r="M16" s="19" t="n"/>
-      <c r="N16" s="23" t="n"/>
-      <c r="O16" s="22" t="inlineStr">
+      <c r="A16" s="24" t="n"/>
+      <c r="B16" s="24" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="24" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="24" t="n"/>
+      <c r="I16" s="24" t="n"/>
+      <c r="J16" s="13" t="n"/>
+      <c r="K16" s="13" t="n"/>
+      <c r="L16" s="13" t="n"/>
+      <c r="M16" s="20" t="n"/>
+      <c r="N16" s="24" t="n"/>
+      <c r="O16" s="23" t="inlineStr">
         <is>
           <t>Tuščių indų ir išvalytos ėminių sistemos tuščiojo ėminio svorio pokytis (mItp)</t>
         </is>
@@ -1787,291 +1821,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumentas" ma:contentTypeID="0x010100BAB57CF81AE55C4698AAD22D302297F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Kurkite naują dokumentą." ma:contentTypeScope="" ma:versionID="49ab401eb4052690d2a2629974c22fd6">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="453e7e53-5eb2-45cf-b2ab-34c867e554b8" xmlns:ns3="aa0d983d-359a-438c-9953-3af1a8ac0831" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab9969d50e0b13c63bc5bd0499c928dc" ns2:_="" ns3:_="">
-    <xsd:import namespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
-    <xsd:import namespace="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="11" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="15" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="16" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Vaizdų žymės" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="993cf2ba-b7a7-49f7-97d1-76e12a88c412" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="23" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="aa0d983d-359a-438c-9953-3af1a8ac0831" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{82c4fa3c-500e-4213-91e5-1b9e2014ea63}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="aa0d983d-359a-438c-9953-3af1a8ac0831">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="21" nillable="true" ma:displayName="Bendrinama su" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="22" nillable="true" ma:displayName="Bendrinta su išsamia informacija" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Turinio tipas"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Antraštė"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="453e7e53-5eb2-45cf-b2ab-34c867e554b8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="aa0d983d-359a-438c-9953-3af1a8ac0831" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D17A693-FB25-430D-B6B5-6C6FA6A677DC}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C6E3F74-698D-4806-8770-263B1DB4FFAE}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F82DFE4-46CF-46BA-8AA9-D8B27E229D52}"/>
 </file>
--- a/Rezultatai.xlsx
+++ b/Rezultatai.xlsx
@@ -63,7 +63,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -128,6 +128,83 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
@@ -145,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -184,23 +261,46 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:AF9"/>
+  <dimension ref="A3:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -595,12 +695,6 @@
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="15" customWidth="1" min="25" max="25"/>
     <col width="15" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="15" customWidth="1" min="29" max="29"/>
-    <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="15" customWidth="1" min="31" max="31"/>
-    <col width="15" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -638,201 +732,369 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Išmatuotas diferencinis slėgis taškuose 2 linija, Pdi, hPa</t>
+          <t>Pito vamzdelio koeficientas, K</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Išmatuotas diferencinis slėgis taškuose 3 linija, Pdi, hPa</t>
+          <t>Temperatūra ortakyje t, oC</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Išmatuotas diferencinis slėgis taškuose 4 linija, Pdi, hPa</t>
+          <t>Atmosferinis slėgis P, hPa</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Pito vamzdelio koeficientas, K</t>
+          <t>Statinis slėgis ortakyje ± ΔP, hPa</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Temperatūra ortakyje t, oC</t>
+          <t>Dujų slėgis kamine Pk= P+ ΔP, hPa</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Atmosferinis slėgis P, hPa</t>
+          <t>Dujų mol. masė Ms= qn *22.4, kg/</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Statinis slėgis ortakyje ± ΔP, hPa</t>
+          <t>Dujų srauto greitis matavimo taškuose, 1 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Dujų slėgis kamine Pk= P+ ΔP, hPa</t>
+          <t>Vidutinis dujų srauto greitis ortakyje w, m/s</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>Dujų mol. masė Ms= qn *22.4, kg/</t>
+          <t>Ortakio diametras, matmenys, m</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>Dujų srauto greitis matavimo taškuose, 1 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+          <t>Ortakio skerspjūvio plotas F, m2</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Dujų srauto greitis matavimo taškuose, 2 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+          <t>Dujų tūrio debitas realiomis sąlygomis Vk = wvid × F, m3/s</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>Dujų srauto greitis matavimo taškuose, 3 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+          <t>Dujų tūrio debitas normaliosiomis sąlygomis Vdr n.s =Vk *0,269*(P±ΔP)/(273+t), m3/s</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>Dujų srauto greitis matavimo taškuose, 4 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+          <t>Vandens kondensato masė m H2O, kg</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>Vidutinis dujų srauto greitis ortakyje w, m/s</t>
+          <t>Vandens garų konc. dujose x=mH2O/Vmn*qn, kg/kg</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>Ortakio diametras, matmenys, m</t>
+          <t>Sausų dujų tūrio debitas normaliosiomis sąlygomis Vn= Vdr n.s *((1/(1+(x*qn/0.8038)))</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>Ortakio skerspjūvio plotas F, m2</t>
+          <t>Prasiurbtas dujų tūris normaliosiomis sąlygomis Vmn, Nm3</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>Dujų tūrio debitas realiomis sąlygomis Vk = wvid × F, m3/s</t>
+          <t>Išplėstinės neapibrėžties koef. A</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>Dujų tūrio debitas normaliosiomis sąlygomis Vdr n.s =Vk *0,269*(P±ΔP)/(273+t), m3/s</t>
+          <t>Išplėstinė neapibrėžtis (dujų tūrio debitas) Uv</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>Vandens kondensato masė m H2O, kg</t>
+          <t>Išplėstinė neapibrėžtis (dujų srauto greitis) Uw</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>Vandens garų konc. dujose x=mH2O/Vmn*qn, kg/kg</t>
+          <t>Sausų dujų tankis normaliosioms sąlygomis qn, (kg/m3)</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>Sausų dujų tūrio debitas normaliosiomis sąlygomis Vn= Vdr n.s *((1/(1+(x*qn/0.8038)))</t>
-        </is>
-      </c>
-      <c r="AA5" s="3" t="inlineStr">
-        <is>
-          <t>Prasiurbtas dujų tūris normaliosiomis sąlygomis Vmn, Nm3</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="inlineStr">
-        <is>
-          <t>Išplėstinės neapibrėžties koef. A</t>
-        </is>
-      </c>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t>Išplėstinė neapibrėžtis (dujų tūrio debitas) Uv</t>
-        </is>
-      </c>
-      <c r="AD5" s="3" t="inlineStr">
-        <is>
-          <t>Išplėstinė neapibrėžtis (dujų srauto greitis) Uw</t>
-        </is>
-      </c>
-      <c r="AE5" s="3" t="inlineStr">
-        <is>
-          <t>Sausų dujų tankis normaliosioms sąlygomis qn, (kg/m3)</t>
-        </is>
-      </c>
-      <c r="AF5" s="3" t="inlineStr">
-        <is>
           <t>Skaičiavimus atliko (inicialai, data)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n"/>
-      <c r="B6" s="1" t="n"/>
-      <c r="C6" s="1" t="n"/>
-      <c r="D6" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="I6" s="6" t="n">
+      <c r="A6" s="14" t="n"/>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="17" t="n">
         <v>0.827</v>
       </c>
-      <c r="AB6" s="6" t="n">
+      <c r="G6" s="16" t="n"/>
+      <c r="H6" s="16" t="n"/>
+      <c r="I6" s="16" t="n"/>
+      <c r="J6" s="18" t="n"/>
+      <c r="K6" s="18" t="n"/>
+      <c r="L6" s="18" t="n"/>
+      <c r="M6" s="13" t="n"/>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>1,20</t>
+        </is>
+      </c>
+      <c r="O6" s="7">
+        <f>(N6^2*3.14)/4</f>
+        <v/>
+      </c>
+      <c r="V6" s="6" t="n">
         <v>0.079</v>
       </c>
     </row>
     <row r="7">
-      <c r="D7" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="I7" s="6" t="n">
+      <c r="A7" s="22" t="n"/>
+      <c r="B7" s="22" t="n"/>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="17" t="n">
         <v>0.827</v>
       </c>
-      <c r="T7" s="1" t="inlineStr">
-        <is>
-          <t>1,50</t>
-        </is>
-      </c>
-      <c r="U7" s="7">
-        <f>T7*T8</f>
-        <v/>
-      </c>
-      <c r="AB7" s="6" t="n">
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="16" t="n"/>
+      <c r="I7" s="16" t="n"/>
+      <c r="J7" s="18" t="n"/>
+      <c r="K7" s="18" t="n"/>
+      <c r="L7" s="18" t="n"/>
+      <c r="V7" s="6" t="n">
         <v>0.079</v>
       </c>
     </row>
     <row r="8">
-      <c r="D8" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="I8" s="6" t="n">
+      <c r="A8" s="22" t="n"/>
+      <c r="B8" s="22" t="n"/>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="17" t="n">
         <v>0.827</v>
       </c>
-      <c r="T8" s="1" t="inlineStr">
-        <is>
-          <t>1,50</t>
-        </is>
-      </c>
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="16" t="n"/>
+      <c r="I8" s="16" t="n"/>
+      <c r="J8" s="18" t="n"/>
+      <c r="K8" s="18" t="n"/>
+      <c r="L8" s="18" t="n"/>
     </row>
     <row r="9">
-      <c r="D9" s="1" t="n">
-        <v>131</v>
-      </c>
-      <c r="I9" s="6" t="n">
+      <c r="A9" s="22" t="n"/>
+      <c r="B9" s="22" t="n"/>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="17" t="n">
         <v>0.827</v>
       </c>
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="16" t="n"/>
+      <c r="I9" s="16" t="n"/>
+      <c r="J9" s="18" t="n"/>
+      <c r="K9" s="18" t="n"/>
+      <c r="L9" s="18" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="n"/>
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="17" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="G10" s="16" t="n"/>
+      <c r="H10" s="16" t="n"/>
+      <c r="I10" s="16" t="n"/>
+      <c r="J10" s="18" t="n"/>
+      <c r="K10" s="18" t="n"/>
+      <c r="L10" s="18" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="n"/>
+      <c r="B11" s="22" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="17" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="16" t="n"/>
+      <c r="I11" s="16" t="n"/>
+      <c r="J11" s="18" t="n"/>
+      <c r="K11" s="18" t="n"/>
+      <c r="L11" s="18" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="n"/>
+      <c r="B12" s="22" t="n"/>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="17" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="16" t="n"/>
+      <c r="I12" s="16" t="n"/>
+      <c r="J12" s="18" t="n"/>
+      <c r="K12" s="18" t="n"/>
+      <c r="L12" s="18" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="n"/>
+      <c r="B13" s="22" t="n"/>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="15" t="n">
+        <v>81</v>
+      </c>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="17" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="16" t="n"/>
+      <c r="I13" s="16" t="n"/>
+      <c r="J13" s="18" t="n"/>
+      <c r="K13" s="18" t="n"/>
+      <c r="L13" s="18" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="n"/>
+      <c r="B14" s="22" t="n"/>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="15" t="n">
+        <v>92</v>
+      </c>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="17" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="16" t="n"/>
+      <c r="I14" s="16" t="n"/>
+      <c r="J14" s="18" t="n"/>
+      <c r="K14" s="18" t="n"/>
+      <c r="L14" s="18" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="n"/>
+      <c r="B15" s="22" t="n"/>
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="17" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="16" t="n"/>
+      <c r="I15" s="16" t="n"/>
+      <c r="J15" s="18" t="n"/>
+      <c r="K15" s="18" t="n"/>
+      <c r="L15" s="18" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="n"/>
+      <c r="B16" s="22" t="n"/>
+      <c r="C16" s="22" t="n"/>
+      <c r="D16" s="15" t="n">
+        <v>106</v>
+      </c>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="17" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="16" t="n"/>
+      <c r="I16" s="16" t="n"/>
+      <c r="J16" s="18" t="n"/>
+      <c r="K16" s="18" t="n"/>
+      <c r="L16" s="18" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="n"/>
+      <c r="B17" s="22" t="n"/>
+      <c r="C17" s="22" t="n"/>
+      <c r="D17" s="15" t="n">
+        <v>112</v>
+      </c>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="17" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="16" t="n"/>
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="18" t="n"/>
+      <c r="K17" s="18" t="n"/>
+      <c r="L17" s="18" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="n"/>
+      <c r="B18" s="21" t="n"/>
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="15" t="n">
+        <v>115</v>
+      </c>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="17" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="G18" s="16" t="n"/>
+      <c r="H18" s="16" t="n"/>
+      <c r="I18" s="16" t="n"/>
+      <c r="J18" s="18" t="n"/>
+      <c r="K18" s="18" t="n"/>
+      <c r="L18" s="18" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="C6:C9"/>
-    <mergeCell ref="A3:AF3"/>
-    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="B6:B18"/>
+    <mergeCell ref="A3:Z3"/>
+    <mergeCell ref="C6:C18"/>
+    <mergeCell ref="A6:A18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -997,7 +1259,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Ortakio matmenys, m</t>
+          <t>Ortakio skersmuo d, m</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -1115,11 +1377,11 @@
     <row r="6">
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>1,50 x 1,50</t>
+          <t>1,20</t>
         </is>
       </c>
       <c r="E6" s="11">
-        <f>'Greitis'!U7</f>
+        <f>'Greitis'!O6</f>
         <v/>
       </c>
     </row>
@@ -1249,7 +1511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:P5"/>
+  <dimension ref="A2:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1359,8 +1621,77 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="23" t="n"/>
+      <c r="B6" s="23" t="n"/>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="25" t="n"/>
+      <c r="E6" s="26" t="n"/>
+      <c r="F6" s="26" t="n"/>
+      <c r="G6" s="26" t="n"/>
+      <c r="H6" s="26" t="n"/>
+      <c r="I6" s="26" t="n"/>
+      <c r="J6" s="26" t="n"/>
+      <c r="K6" s="26" t="n"/>
+      <c r="L6" s="27" t="n"/>
+      <c r="M6" s="27" t="n"/>
+      <c r="N6" s="24" t="n"/>
+      <c r="O6" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="28" t="inlineStr">
+        <is>
+          <t>1 linija, 1 filtras</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="n"/>
+      <c r="B7" s="29" t="n"/>
+      <c r="C7" s="31" t="n"/>
+      <c r="D7" s="25" t="n"/>
+      <c r="E7" s="26" t="n"/>
+      <c r="F7" s="26" t="n"/>
+      <c r="G7" s="26" t="n"/>
+      <c r="H7" s="26" t="n"/>
+      <c r="I7" s="26" t="n"/>
+      <c r="J7" s="26" t="n"/>
+      <c r="K7" s="26" t="n"/>
+      <c r="L7" s="31" t="n"/>
+      <c r="M7" s="31" t="n"/>
+      <c r="N7" s="31" t="n"/>
+      <c r="O7" s="31" t="n"/>
+      <c r="P7" s="28" t="inlineStr">
+        <is>
+          <t>1 linija, 2 filtras</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="n"/>
+      <c r="B8" s="30" t="n"/>
+      <c r="C8" s="32" t="n"/>
+      <c r="D8" s="25" t="n"/>
+      <c r="E8" s="26" t="n"/>
+      <c r="F8" s="26" t="n"/>
+      <c r="G8" s="26" t="n"/>
+      <c r="H8" s="26" t="n"/>
+      <c r="I8" s="26" t="n"/>
+      <c r="J8" s="26" t="n"/>
+      <c r="K8" s="26" t="n"/>
+      <c r="L8" s="32" t="n"/>
+      <c r="M8" s="32" t="n"/>
+      <c r="N8" s="32" t="n"/>
+      <c r="O8" s="32" t="n"/>
+      <c r="P8" s="25" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="6">
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="O6:O8"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1426,8 +1757,8 @@
           <t>Filtro/indo svoris prieš KD ėmimą mpr (g)</t>
         </is>
       </c>
-      <c r="F4" s="14" t="n"/>
-      <c r="G4" s="15" t="n"/>
+      <c r="F4" s="19" t="n"/>
+      <c r="G4" s="20" t="n"/>
       <c r="H4" s="12" t="inlineStr">
         <is>
           <t>Atsakingo asmens inicialai, data</t>
@@ -1443,8 +1774,8 @@
           <t>Filtro/indo svoris po KD ėmimo mpo (g)</t>
         </is>
       </c>
-      <c r="K4" s="14" t="n"/>
-      <c r="L4" s="15" t="n"/>
+      <c r="K4" s="19" t="n"/>
+      <c r="L4" s="20" t="n"/>
       <c r="M4" s="12" t="inlineStr">
         <is>
           <t>Kietųjų dalelių svoris mf/Svorių pokytis (g) (&lt;2,20 g filtro talpumas)</t>
@@ -1462,10 +1793,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="16" t="n"/>
+      <c r="A5" s="21" t="n"/>
+      <c r="B5" s="21" t="n"/>
+      <c r="C5" s="21" t="n"/>
+      <c r="D5" s="21" t="n"/>
       <c r="E5" s="12" t="inlineStr">
         <is>
           <t>1</t>
@@ -1481,8 +1812,8 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H5" s="16" t="n"/>
-      <c r="I5" s="16" t="n"/>
+      <c r="H5" s="21" t="n"/>
+      <c r="I5" s="21" t="n"/>
       <c r="J5" s="12" t="inlineStr">
         <is>
           <t>1</t>
@@ -1498,254 +1829,252 @@
           <t>3</t>
         </is>
       </c>
-      <c r="M5" s="16" t="n"/>
-      <c r="N5" s="16" t="n"/>
-      <c r="O5" s="16" t="n"/>
+      <c r="M5" s="21" t="n"/>
+      <c r="N5" s="21" t="n"/>
+      <c r="O5" s="21" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="n"/>
-      <c r="B6" s="17" t="n"/>
-      <c r="C6" s="18" t="n">
+      <c r="A6" s="33" t="n"/>
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="17" t="n"/>
-      <c r="E6" s="19" t="n"/>
-      <c r="F6" s="19" t="n"/>
-      <c r="G6" s="19" t="n"/>
-      <c r="H6" s="17" t="n"/>
-      <c r="I6" s="17" t="n"/>
-      <c r="J6" s="19" t="n"/>
-      <c r="K6" s="19" t="n"/>
-      <c r="L6" s="19" t="n"/>
-      <c r="M6" s="20" t="n"/>
-      <c r="N6" s="17" t="n"/>
-      <c r="O6" s="21" t="inlineStr">
-        <is>
-          <t>4 linijos, 3 filtrai</t>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="16" t="n"/>
+      <c r="H6" s="33" t="n"/>
+      <c r="I6" s="33" t="n"/>
+      <c r="J6" s="16" t="n"/>
+      <c r="K6" s="16" t="n"/>
+      <c r="L6" s="16" t="n"/>
+      <c r="M6" s="18" t="n"/>
+      <c r="N6" s="33" t="n"/>
+      <c r="O6" s="34" t="inlineStr">
+        <is>
+          <t>1 linija, 2 filtrai</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="n"/>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="18" t="n">
+      <c r="A7" s="35" t="n"/>
+      <c r="B7" s="35" t="n"/>
+      <c r="C7" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="19" t="n"/>
-      <c r="F7" s="19" t="n"/>
-      <c r="G7" s="19" t="n"/>
-      <c r="H7" s="22" t="n"/>
-      <c r="I7" s="22" t="n"/>
-      <c r="J7" s="19" t="n"/>
-      <c r="K7" s="19" t="n"/>
-      <c r="L7" s="19" t="n"/>
-      <c r="M7" s="20" t="n"/>
-      <c r="N7" s="22" t="n"/>
+      <c r="D7" s="35" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="35" t="n"/>
+      <c r="I7" s="35" t="n"/>
+      <c r="J7" s="16" t="n"/>
+      <c r="K7" s="16" t="n"/>
+      <c r="L7" s="16" t="n"/>
+      <c r="M7" s="18" t="n"/>
+      <c r="N7" s="35" t="n"/>
       <c r="O7" s="13" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="n"/>
-      <c r="B8" s="22" t="n"/>
-      <c r="C8" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" s="22" t="n"/>
-      <c r="E8" s="19" t="n"/>
-      <c r="F8" s="19" t="n"/>
-      <c r="G8" s="19" t="n"/>
-      <c r="H8" s="22" t="n"/>
-      <c r="I8" s="22" t="n"/>
-      <c r="J8" s="19" t="n"/>
-      <c r="K8" s="19" t="n"/>
-      <c r="L8" s="19" t="n"/>
-      <c r="M8" s="20" t="n"/>
-      <c r="N8" s="22" t="n"/>
+      <c r="A8" s="35" t="n"/>
+      <c r="B8" s="35" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="13" t="n"/>
+      <c r="H8" s="35" t="n"/>
+      <c r="I8" s="35" t="n"/>
+      <c r="J8" s="13" t="n"/>
+      <c r="K8" s="13" t="n"/>
+      <c r="L8" s="13" t="n"/>
+      <c r="M8" s="18" t="n"/>
+      <c r="N8" s="35" t="n"/>
       <c r="O8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="22" t="n"/>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="A9" s="35" t="n"/>
+      <c r="B9" s="35" t="n"/>
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="19" t="n"/>
-      <c r="F9" s="19" t="n"/>
-      <c r="G9" s="19" t="n"/>
-      <c r="H9" s="22" t="n"/>
-      <c r="I9" s="22" t="n"/>
-      <c r="J9" s="19" t="n"/>
-      <c r="K9" s="19" t="n"/>
-      <c r="L9" s="19" t="n"/>
-      <c r="M9" s="20" t="n"/>
-      <c r="N9" s="22" t="n"/>
-      <c r="O9" s="23" t="inlineStr">
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="35" t="n"/>
+      <c r="I9" s="35" t="n"/>
+      <c r="J9" s="16" t="n"/>
+      <c r="K9" s="16" t="n"/>
+      <c r="L9" s="16" t="n"/>
+      <c r="M9" s="18" t="n"/>
+      <c r="N9" s="35" t="n"/>
+      <c r="O9" s="36" t="inlineStr">
         <is>
           <t>Tuščiasis ėminys (mt)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="22" t="n"/>
+      <c r="A10" s="35" t="n"/>
+      <c r="B10" s="35" t="n"/>
       <c r="C10" s="13" t="n"/>
-      <c r="D10" s="22" t="n"/>
+      <c r="D10" s="35" t="n"/>
       <c r="E10" s="13" t="n"/>
       <c r="F10" s="13" t="n"/>
       <c r="G10" s="13" t="n"/>
-      <c r="H10" s="22" t="n"/>
-      <c r="I10" s="22" t="n"/>
+      <c r="H10" s="35" t="n"/>
+      <c r="I10" s="35" t="n"/>
       <c r="J10" s="13" t="n"/>
       <c r="K10" s="13" t="n"/>
       <c r="L10" s="13" t="n"/>
       <c r="M10" s="13" t="n"/>
-      <c r="N10" s="22" t="n"/>
+      <c r="N10" s="35" t="n"/>
       <c r="O10" s="13" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n"/>
-      <c r="B11" s="22" t="n"/>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="A11" s="35" t="n"/>
+      <c r="B11" s="35" t="n"/>
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D11" s="22" t="n"/>
-      <c r="E11" s="19" t="n"/>
-      <c r="F11" s="19" t="n"/>
-      <c r="G11" s="19" t="n"/>
-      <c r="H11" s="22" t="n"/>
-      <c r="I11" s="22" t="n"/>
-      <c r="J11" s="19" t="n"/>
-      <c r="K11" s="19" t="n"/>
-      <c r="L11" s="19" t="n"/>
-      <c r="M11" s="20" t="n"/>
-      <c r="N11" s="22" t="n"/>
-      <c r="O11" s="23" t="inlineStr">
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="35" t="n"/>
+      <c r="I11" s="35" t="n"/>
+      <c r="J11" s="16" t="n"/>
+      <c r="K11" s="16" t="n"/>
+      <c r="L11" s="16" t="n"/>
+      <c r="M11" s="18" t="n"/>
+      <c r="N11" s="35" t="n"/>
+      <c r="O11" s="36" t="inlineStr">
         <is>
           <t>Išplautos nuosėdos (mn)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="22" t="n"/>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="A12" s="35" t="n"/>
+      <c r="B12" s="35" t="n"/>
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="D12" s="22" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="22" t="n"/>
-      <c r="I12" s="22" t="n"/>
-      <c r="J12" s="19" t="n"/>
-      <c r="K12" s="19" t="n"/>
-      <c r="L12" s="19" t="n"/>
-      <c r="M12" s="20" t="n"/>
-      <c r="N12" s="22" t="n"/>
-      <c r="O12" s="23" t="inlineStr">
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="35" t="n"/>
+      <c r="I12" s="35" t="n"/>
+      <c r="J12" s="16" t="n"/>
+      <c r="K12" s="16" t="n"/>
+      <c r="L12" s="16" t="n"/>
+      <c r="M12" s="18" t="n"/>
+      <c r="N12" s="35" t="n"/>
+      <c r="O12" s="36" t="inlineStr">
         <is>
           <t>Išvalytos ėminių sistemos tuščiasis ėminys (mIt)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="n"/>
-      <c r="B13" s="22" t="n"/>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="A13" s="35" t="n"/>
+      <c r="B13" s="35" t="n"/>
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D13" s="22" t="n"/>
-      <c r="E13" s="19" t="n"/>
-      <c r="F13" s="19" t="n"/>
-      <c r="G13" s="19" t="n"/>
-      <c r="H13" s="22" t="n"/>
-      <c r="I13" s="22" t="n"/>
-      <c r="J13" s="19" t="n"/>
-      <c r="K13" s="19" t="n"/>
-      <c r="L13" s="19" t="n"/>
-      <c r="M13" s="20" t="n"/>
-      <c r="N13" s="22" t="n"/>
-      <c r="O13" s="23" t="inlineStr">
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n"/>
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="35" t="n"/>
+      <c r="I13" s="35" t="n"/>
+      <c r="J13" s="16" t="n"/>
+      <c r="K13" s="16" t="n"/>
+      <c r="L13" s="16" t="n"/>
+      <c r="M13" s="18" t="n"/>
+      <c r="N13" s="35" t="n"/>
+      <c r="O13" s="36" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt1)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="A14" s="35" t="n"/>
+      <c r="B14" s="35" t="n"/>
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="D14" s="22" t="n"/>
-      <c r="E14" s="19" t="n"/>
-      <c r="F14" s="19" t="n"/>
-      <c r="G14" s="19" t="n"/>
-      <c r="H14" s="22" t="n"/>
-      <c r="I14" s="22" t="n"/>
-      <c r="J14" s="19" t="n"/>
-      <c r="K14" s="19" t="n"/>
-      <c r="L14" s="19" t="n"/>
-      <c r="M14" s="20" t="n"/>
-      <c r="N14" s="22" t="n"/>
-      <c r="O14" s="23" t="inlineStr">
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="35" t="n"/>
+      <c r="I14" s="35" t="n"/>
+      <c r="J14" s="16" t="n"/>
+      <c r="K14" s="16" t="n"/>
+      <c r="L14" s="16" t="n"/>
+      <c r="M14" s="18" t="n"/>
+      <c r="N14" s="35" t="n"/>
+      <c r="O14" s="36" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt2)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n"/>
-      <c r="B15" s="22" t="n"/>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="A15" s="35" t="n"/>
+      <c r="B15" s="35" t="n"/>
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D15" s="22" t="n"/>
-      <c r="E15" s="19" t="n"/>
-      <c r="F15" s="19" t="n"/>
-      <c r="G15" s="19" t="n"/>
-      <c r="H15" s="22" t="n"/>
-      <c r="I15" s="22" t="n"/>
-      <c r="J15" s="19" t="n"/>
-      <c r="K15" s="19" t="n"/>
-      <c r="L15" s="19" t="n"/>
-      <c r="M15" s="20" t="n"/>
-      <c r="N15" s="22" t="n"/>
-      <c r="O15" s="23" t="inlineStr">
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="16" t="n"/>
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="35" t="n"/>
+      <c r="I15" s="35" t="n"/>
+      <c r="J15" s="16" t="n"/>
+      <c r="K15" s="16" t="n"/>
+      <c r="L15" s="16" t="n"/>
+      <c r="M15" s="18" t="n"/>
+      <c r="N15" s="35" t="n"/>
+      <c r="O15" s="36" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt3)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="n"/>
-      <c r="B16" s="24" t="n"/>
+      <c r="A16" s="37" t="n"/>
+      <c r="B16" s="37" t="n"/>
       <c r="C16" s="13" t="n"/>
-      <c r="D16" s="24" t="n"/>
+      <c r="D16" s="37" t="n"/>
       <c r="E16" s="13" t="n"/>
       <c r="F16" s="13" t="n"/>
       <c r="G16" s="13" t="n"/>
-      <c r="H16" s="24" t="n"/>
-      <c r="I16" s="24" t="n"/>
+      <c r="H16" s="37" t="n"/>
+      <c r="I16" s="37" t="n"/>
       <c r="J16" s="13" t="n"/>
       <c r="K16" s="13" t="n"/>
       <c r="L16" s="13" t="n"/>
-      <c r="M16" s="20" t="n"/>
-      <c r="N16" s="24" t="n"/>
-      <c r="O16" s="23" t="inlineStr">
+      <c r="M16" s="18" t="n"/>
+      <c r="N16" s="37" t="n"/>
+      <c r="O16" s="36" t="inlineStr">
         <is>
           <t>Tuščių indų ir išvalytos ėminių sistemos tuščiojo ėminio svorio pokytis (mItp)</t>
         </is>

--- a/Rezultatai.xlsx
+++ b/Rezultatai.xlsx
@@ -43,7 +43,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -60,6 +60,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFF00"/>
         <bgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF9900"/>
+        <bgColor rgb="00FF9900"/>
       </patternFill>
     </fill>
   </fills>
@@ -222,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -272,6 +278,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -666,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:Z19"/>
+  <dimension ref="A3:Z23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -853,24 +868,34 @@
       <c r="J6" s="18" t="n"/>
       <c r="K6" s="18" t="n"/>
       <c r="L6" s="18" t="n"/>
-      <c r="M6" s="13" t="n"/>
-      <c r="N6" s="1" t="inlineStr">
+      <c r="M6" s="18" t="n"/>
+      <c r="N6" s="15" t="inlineStr">
         <is>
           <t>1,20</t>
         </is>
       </c>
-      <c r="O6" s="7">
+      <c r="O6" s="19">
         <f>(N6^2*3.14)/4</f>
         <v/>
       </c>
-      <c r="V6" s="6" t="n">
+      <c r="P6" s="18" t="n"/>
+      <c r="Q6" s="16" t="n"/>
+      <c r="R6" s="16" t="n"/>
+      <c r="S6" s="18" t="n"/>
+      <c r="T6" s="16" t="n"/>
+      <c r="U6" s="16" t="n"/>
+      <c r="V6" s="17" t="n">
         <v>0.079</v>
       </c>
+      <c r="W6" s="18" t="n"/>
+      <c r="X6" s="18" t="n"/>
+      <c r="Y6" s="16" t="n"/>
+      <c r="Z6" s="13" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="n"/>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
+      <c r="A7" s="25" t="n"/>
+      <c r="B7" s="25" t="n"/>
+      <c r="C7" s="25" t="n"/>
       <c r="D7" s="15" t="n">
         <v>8</v>
       </c>
@@ -884,14 +909,26 @@
       <c r="J7" s="18" t="n"/>
       <c r="K7" s="18" t="n"/>
       <c r="L7" s="18" t="n"/>
-      <c r="V7" s="6" t="n">
+      <c r="M7" s="13" t="n"/>
+      <c r="N7" s="16" t="n"/>
+      <c r="O7" s="18" t="n"/>
+      <c r="P7" s="18" t="n"/>
+      <c r="Q7" s="16" t="n"/>
+      <c r="R7" s="16" t="n"/>
+      <c r="S7" s="18" t="n"/>
+      <c r="T7" s="16" t="n"/>
+      <c r="U7" s="16" t="n"/>
+      <c r="V7" s="17" t="n">
         <v>0.079</v>
       </c>
+      <c r="W7" s="18" t="n"/>
+      <c r="X7" s="18" t="n"/>
+      <c r="Z7" s="24" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="n"/>
-      <c r="B8" s="22" t="n"/>
-      <c r="C8" s="22" t="n"/>
+      <c r="A8" s="25" t="n"/>
+      <c r="B8" s="25" t="n"/>
+      <c r="C8" s="25" t="n"/>
       <c r="D8" s="15" t="n">
         <v>14</v>
       </c>
@@ -905,11 +942,16 @@
       <c r="J8" s="18" t="n"/>
       <c r="K8" s="18" t="n"/>
       <c r="L8" s="18" t="n"/>
+      <c r="M8" s="13" t="n"/>
+      <c r="N8" s="16" t="n"/>
+      <c r="O8" s="13" t="n"/>
+      <c r="P8" s="13" t="n"/>
+      <c r="Q8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="22" t="n"/>
-      <c r="C9" s="22" t="n"/>
+      <c r="A9" s="25" t="n"/>
+      <c r="B9" s="25" t="n"/>
+      <c r="C9" s="25" t="n"/>
       <c r="D9" s="15" t="n">
         <v>20</v>
       </c>
@@ -923,11 +965,16 @@
       <c r="J9" s="18" t="n"/>
       <c r="K9" s="18" t="n"/>
       <c r="L9" s="18" t="n"/>
+      <c r="M9" s="13" t="n"/>
+      <c r="N9" s="13" t="n"/>
+      <c r="O9" s="13" t="n"/>
+      <c r="P9" s="13" t="n"/>
+      <c r="Q9" s="13" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
+      <c r="A10" s="25" t="n"/>
+      <c r="B10" s="25" t="n"/>
+      <c r="C10" s="25" t="n"/>
       <c r="D10" s="15" t="n">
         <v>28</v>
       </c>
@@ -943,9 +990,9 @@
       <c r="L10" s="18" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n"/>
-      <c r="B11" s="22" t="n"/>
-      <c r="C11" s="22" t="n"/>
+      <c r="A11" s="25" t="n"/>
+      <c r="B11" s="25" t="n"/>
+      <c r="C11" s="25" t="n"/>
       <c r="D11" s="15" t="n">
         <v>39</v>
       </c>
@@ -961,9 +1008,9 @@
       <c r="L11" s="18" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="22" t="n"/>
-      <c r="C12" s="22" t="n"/>
+      <c r="A12" s="25" t="n"/>
+      <c r="B12" s="25" t="n"/>
+      <c r="C12" s="25" t="n"/>
       <c r="D12" s="15" t="n">
         <v>60</v>
       </c>
@@ -979,9 +1026,9 @@
       <c r="L12" s="18" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="n"/>
-      <c r="B13" s="22" t="n"/>
-      <c r="C13" s="22" t="n"/>
+      <c r="A13" s="25" t="n"/>
+      <c r="B13" s="25" t="n"/>
+      <c r="C13" s="25" t="n"/>
       <c r="D13" s="15" t="n">
         <v>81</v>
       </c>
@@ -997,9 +1044,9 @@
       <c r="L13" s="18" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="22" t="n"/>
+      <c r="A14" s="25" t="n"/>
+      <c r="B14" s="25" t="n"/>
+      <c r="C14" s="25" t="n"/>
       <c r="D14" s="15" t="n">
         <v>92</v>
       </c>
@@ -1015,9 +1062,9 @@
       <c r="L14" s="18" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n"/>
-      <c r="B15" s="22" t="n"/>
-      <c r="C15" s="22" t="n"/>
+      <c r="A15" s="25" t="n"/>
+      <c r="B15" s="25" t="n"/>
+      <c r="C15" s="25" t="n"/>
       <c r="D15" s="15" t="n">
         <v>100</v>
       </c>
@@ -1033,9 +1080,9 @@
       <c r="L15" s="18" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="22" t="n"/>
-      <c r="C16" s="22" t="n"/>
+      <c r="A16" s="25" t="n"/>
+      <c r="B16" s="25" t="n"/>
+      <c r="C16" s="25" t="n"/>
       <c r="D16" s="15" t="n">
         <v>106</v>
       </c>
@@ -1051,9 +1098,9 @@
       <c r="L16" s="18" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="n"/>
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="22" t="n"/>
+      <c r="A17" s="25" t="n"/>
+      <c r="B17" s="25" t="n"/>
+      <c r="C17" s="25" t="n"/>
       <c r="D17" s="15" t="n">
         <v>112</v>
       </c>
@@ -1069,9 +1116,9 @@
       <c r="L17" s="18" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="n"/>
-      <c r="B18" s="21" t="n"/>
-      <c r="C18" s="21" t="n"/>
+      <c r="A18" s="24" t="n"/>
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="24" t="n"/>
       <c r="D18" s="15" t="n">
         <v>115</v>
       </c>
@@ -1088,13 +1135,63 @@
     </row>
     <row r="19">
       <c r="A19" s="13" t="n"/>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="13" t="n"/>
+      <c r="I19" s="13" t="n"/>
+      <c r="J19" s="13" t="n"/>
+      <c r="K19" s="13" t="n"/>
+      <c r="L19" s="13" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>RPU***</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>Kai bus 2 linijos, RPU*** yra 2 linijos vidurinis taškas</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="n"/>
+      <c r="G20" s="22" t="n"/>
+      <c r="H20" s="22" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="22" t="n"/>
+      <c r="K20" s="22" t="n"/>
+      <c r="L20" s="23" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
+    <mergeCell ref="E20:L20"/>
+    <mergeCell ref="A3:Z3"/>
     <mergeCell ref="B6:B18"/>
-    <mergeCell ref="A3:Z3"/>
     <mergeCell ref="C6:C18"/>
     <mergeCell ref="A6:A18"/>
+    <mergeCell ref="Z6:Z7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1622,68 +1719,68 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="n"/>
-      <c r="B6" s="23" t="n"/>
-      <c r="C6" s="24" t="n"/>
-      <c r="D6" s="25" t="n"/>
-      <c r="E6" s="26" t="n"/>
-      <c r="F6" s="26" t="n"/>
-      <c r="G6" s="26" t="n"/>
-      <c r="H6" s="26" t="n"/>
-      <c r="I6" s="26" t="n"/>
-      <c r="J6" s="26" t="n"/>
-      <c r="K6" s="26" t="n"/>
-      <c r="L6" s="27" t="n"/>
-      <c r="M6" s="27" t="n"/>
-      <c r="N6" s="24" t="n"/>
-      <c r="O6" s="24" t="n">
+      <c r="A6" s="26" t="n"/>
+      <c r="B6" s="26" t="n"/>
+      <c r="C6" s="27" t="n"/>
+      <c r="D6" s="28" t="n"/>
+      <c r="E6" s="29" t="n"/>
+      <c r="F6" s="29" t="n"/>
+      <c r="G6" s="29" t="n"/>
+      <c r="H6" s="29" t="n"/>
+      <c r="I6" s="29" t="n"/>
+      <c r="J6" s="29" t="n"/>
+      <c r="K6" s="29" t="n"/>
+      <c r="L6" s="30" t="n"/>
+      <c r="M6" s="30" t="n"/>
+      <c r="N6" s="27" t="n"/>
+      <c r="O6" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="28" t="inlineStr">
+      <c r="P6" s="31" t="inlineStr">
         <is>
           <t>1 linija, 1 filtras</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="n"/>
-      <c r="B7" s="29" t="n"/>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="25" t="n"/>
-      <c r="E7" s="26" t="n"/>
-      <c r="F7" s="26" t="n"/>
-      <c r="G7" s="26" t="n"/>
-      <c r="H7" s="26" t="n"/>
-      <c r="I7" s="26" t="n"/>
-      <c r="J7" s="26" t="n"/>
-      <c r="K7" s="26" t="n"/>
-      <c r="L7" s="31" t="n"/>
-      <c r="M7" s="31" t="n"/>
-      <c r="N7" s="31" t="n"/>
-      <c r="O7" s="31" t="n"/>
-      <c r="P7" s="28" t="inlineStr">
+      <c r="A7" s="32" t="n"/>
+      <c r="B7" s="32" t="n"/>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="29" t="n"/>
+      <c r="F7" s="29" t="n"/>
+      <c r="G7" s="29" t="n"/>
+      <c r="H7" s="29" t="n"/>
+      <c r="I7" s="29" t="n"/>
+      <c r="J7" s="29" t="n"/>
+      <c r="K7" s="29" t="n"/>
+      <c r="L7" s="34" t="n"/>
+      <c r="M7" s="34" t="n"/>
+      <c r="N7" s="34" t="n"/>
+      <c r="O7" s="34" t="n"/>
+      <c r="P7" s="31" t="inlineStr">
         <is>
           <t>1 linija, 2 filtras</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="n"/>
-      <c r="B8" s="30" t="n"/>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="25" t="n"/>
-      <c r="E8" s="26" t="n"/>
-      <c r="F8" s="26" t="n"/>
-      <c r="G8" s="26" t="n"/>
-      <c r="H8" s="26" t="n"/>
-      <c r="I8" s="26" t="n"/>
-      <c r="J8" s="26" t="n"/>
-      <c r="K8" s="26" t="n"/>
-      <c r="L8" s="32" t="n"/>
-      <c r="M8" s="32" t="n"/>
-      <c r="N8" s="32" t="n"/>
-      <c r="O8" s="32" t="n"/>
-      <c r="P8" s="25" t="n"/>
+      <c r="A8" s="33" t="n"/>
+      <c r="B8" s="33" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="28" t="n"/>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="29" t="n"/>
+      <c r="H8" s="29" t="n"/>
+      <c r="I8" s="29" t="n"/>
+      <c r="J8" s="29" t="n"/>
+      <c r="K8" s="29" t="n"/>
+      <c r="L8" s="35" t="n"/>
+      <c r="M8" s="35" t="n"/>
+      <c r="N8" s="35" t="n"/>
+      <c r="O8" s="35" t="n"/>
+      <c r="P8" s="28" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1757,8 +1854,8 @@
           <t>Filtro/indo svoris prieš KD ėmimą mpr (g)</t>
         </is>
       </c>
-      <c r="F4" s="19" t="n"/>
-      <c r="G4" s="20" t="n"/>
+      <c r="F4" s="22" t="n"/>
+      <c r="G4" s="23" t="n"/>
       <c r="H4" s="12" t="inlineStr">
         <is>
           <t>Atsakingo asmens inicialai, data</t>
@@ -1774,8 +1871,8 @@
           <t>Filtro/indo svoris po KD ėmimo mpo (g)</t>
         </is>
       </c>
-      <c r="K4" s="19" t="n"/>
-      <c r="L4" s="20" t="n"/>
+      <c r="K4" s="22" t="n"/>
+      <c r="L4" s="23" t="n"/>
       <c r="M4" s="12" t="inlineStr">
         <is>
           <t>Kietųjų dalelių svoris mf/Svorių pokytis (g) (&lt;2,20 g filtro talpumas)</t>
@@ -1793,10 +1890,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="n"/>
-      <c r="B5" s="21" t="n"/>
-      <c r="C5" s="21" t="n"/>
-      <c r="D5" s="21" t="n"/>
+      <c r="A5" s="24" t="n"/>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
       <c r="E5" s="12" t="inlineStr">
         <is>
           <t>1</t>
@@ -1812,8 +1909,8 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H5" s="21" t="n"/>
-      <c r="I5" s="21" t="n"/>
+      <c r="H5" s="24" t="n"/>
+      <c r="I5" s="24" t="n"/>
       <c r="J5" s="12" t="inlineStr">
         <is>
           <t>1</t>
@@ -1829,252 +1926,252 @@
           <t>3</t>
         </is>
       </c>
-      <c r="M5" s="21" t="n"/>
-      <c r="N5" s="21" t="n"/>
-      <c r="O5" s="21" t="n"/>
+      <c r="M5" s="24" t="n"/>
+      <c r="N5" s="24" t="n"/>
+      <c r="O5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="n"/>
-      <c r="B6" s="33" t="n"/>
+      <c r="A6" s="36" t="n"/>
+      <c r="B6" s="36" t="n"/>
       <c r="C6" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="33" t="n"/>
+      <c r="D6" s="36" t="n"/>
       <c r="E6" s="16" t="n"/>
       <c r="F6" s="16" t="n"/>
       <c r="G6" s="16" t="n"/>
-      <c r="H6" s="33" t="n"/>
-      <c r="I6" s="33" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="36" t="n"/>
       <c r="J6" s="16" t="n"/>
       <c r="K6" s="16" t="n"/>
       <c r="L6" s="16" t="n"/>
       <c r="M6" s="18" t="n"/>
-      <c r="N6" s="33" t="n"/>
-      <c r="O6" s="34" t="inlineStr">
+      <c r="N6" s="36" t="n"/>
+      <c r="O6" s="37" t="inlineStr">
         <is>
           <t>1 linija, 2 filtrai</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="n"/>
-      <c r="B7" s="35" t="n"/>
+      <c r="A7" s="38" t="n"/>
+      <c r="B7" s="38" t="n"/>
       <c r="C7" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="35" t="n"/>
+      <c r="D7" s="38" t="n"/>
       <c r="E7" s="16" t="n"/>
       <c r="F7" s="16" t="n"/>
       <c r="G7" s="16" t="n"/>
-      <c r="H7" s="35" t="n"/>
-      <c r="I7" s="35" t="n"/>
+      <c r="H7" s="38" t="n"/>
+      <c r="I7" s="38" t="n"/>
       <c r="J7" s="16" t="n"/>
       <c r="K7" s="16" t="n"/>
       <c r="L7" s="16" t="n"/>
       <c r="M7" s="18" t="n"/>
-      <c r="N7" s="35" t="n"/>
+      <c r="N7" s="38" t="n"/>
       <c r="O7" s="13" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="n"/>
-      <c r="B8" s="35" t="n"/>
+      <c r="A8" s="38" t="n"/>
+      <c r="B8" s="38" t="n"/>
       <c r="C8" s="13" t="n"/>
-      <c r="D8" s="35" t="n"/>
+      <c r="D8" s="38" t="n"/>
       <c r="E8" s="13" t="n"/>
       <c r="F8" s="13" t="n"/>
       <c r="G8" s="13" t="n"/>
-      <c r="H8" s="35" t="n"/>
-      <c r="I8" s="35" t="n"/>
+      <c r="H8" s="38" t="n"/>
+      <c r="I8" s="38" t="n"/>
       <c r="J8" s="13" t="n"/>
       <c r="K8" s="13" t="n"/>
       <c r="L8" s="13" t="n"/>
       <c r="M8" s="18" t="n"/>
-      <c r="N8" s="35" t="n"/>
+      <c r="N8" s="38" t="n"/>
       <c r="O8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="n"/>
-      <c r="B9" s="35" t="n"/>
+      <c r="A9" s="38" t="n"/>
+      <c r="B9" s="38" t="n"/>
       <c r="C9" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="35" t="n"/>
+      <c r="D9" s="38" t="n"/>
       <c r="E9" s="16" t="n"/>
       <c r="F9" s="16" t="n"/>
       <c r="G9" s="16" t="n"/>
-      <c r="H9" s="35" t="n"/>
-      <c r="I9" s="35" t="n"/>
+      <c r="H9" s="38" t="n"/>
+      <c r="I9" s="38" t="n"/>
       <c r="J9" s="16" t="n"/>
       <c r="K9" s="16" t="n"/>
       <c r="L9" s="16" t="n"/>
       <c r="M9" s="18" t="n"/>
-      <c r="N9" s="35" t="n"/>
-      <c r="O9" s="36" t="inlineStr">
+      <c r="N9" s="38" t="n"/>
+      <c r="O9" s="39" t="inlineStr">
         <is>
           <t>Tuščiasis ėminys (mt)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="35" t="n"/>
+      <c r="A10" s="38" t="n"/>
+      <c r="B10" s="38" t="n"/>
       <c r="C10" s="13" t="n"/>
-      <c r="D10" s="35" t="n"/>
+      <c r="D10" s="38" t="n"/>
       <c r="E10" s="13" t="n"/>
       <c r="F10" s="13" t="n"/>
       <c r="G10" s="13" t="n"/>
-      <c r="H10" s="35" t="n"/>
-      <c r="I10" s="35" t="n"/>
+      <c r="H10" s="38" t="n"/>
+      <c r="I10" s="38" t="n"/>
       <c r="J10" s="13" t="n"/>
       <c r="K10" s="13" t="n"/>
       <c r="L10" s="13" t="n"/>
       <c r="M10" s="13" t="n"/>
-      <c r="N10" s="35" t="n"/>
+      <c r="N10" s="38" t="n"/>
       <c r="O10" s="13" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="35" t="n"/>
+      <c r="A11" s="38" t="n"/>
+      <c r="B11" s="38" t="n"/>
       <c r="C11" s="14" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D11" s="35" t="n"/>
+      <c r="D11" s="38" t="n"/>
       <c r="E11" s="16" t="n"/>
       <c r="F11" s="16" t="n"/>
       <c r="G11" s="16" t="n"/>
-      <c r="H11" s="35" t="n"/>
-      <c r="I11" s="35" t="n"/>
+      <c r="H11" s="38" t="n"/>
+      <c r="I11" s="38" t="n"/>
       <c r="J11" s="16" t="n"/>
       <c r="K11" s="16" t="n"/>
       <c r="L11" s="16" t="n"/>
       <c r="M11" s="18" t="n"/>
-      <c r="N11" s="35" t="n"/>
-      <c r="O11" s="36" t="inlineStr">
+      <c r="N11" s="38" t="n"/>
+      <c r="O11" s="39" t="inlineStr">
         <is>
           <t>Išplautos nuosėdos (mn)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="n"/>
-      <c r="B12" s="35" t="n"/>
+      <c r="A12" s="38" t="n"/>
+      <c r="B12" s="38" t="n"/>
       <c r="C12" s="14" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="D12" s="35" t="n"/>
+      <c r="D12" s="38" t="n"/>
       <c r="E12" s="16" t="n"/>
       <c r="F12" s="16" t="n"/>
       <c r="G12" s="16" t="n"/>
-      <c r="H12" s="35" t="n"/>
-      <c r="I12" s="35" t="n"/>
+      <c r="H12" s="38" t="n"/>
+      <c r="I12" s="38" t="n"/>
       <c r="J12" s="16" t="n"/>
       <c r="K12" s="16" t="n"/>
       <c r="L12" s="16" t="n"/>
       <c r="M12" s="18" t="n"/>
-      <c r="N12" s="35" t="n"/>
-      <c r="O12" s="36" t="inlineStr">
+      <c r="N12" s="38" t="n"/>
+      <c r="O12" s="39" t="inlineStr">
         <is>
           <t>Išvalytos ėminių sistemos tuščiasis ėminys (mIt)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="n"/>
-      <c r="B13" s="35" t="n"/>
+      <c r="A13" s="38" t="n"/>
+      <c r="B13" s="38" t="n"/>
       <c r="C13" s="14" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D13" s="35" t="n"/>
+      <c r="D13" s="38" t="n"/>
       <c r="E13" s="16" t="n"/>
       <c r="F13" s="16" t="n"/>
       <c r="G13" s="16" t="n"/>
-      <c r="H13" s="35" t="n"/>
-      <c r="I13" s="35" t="n"/>
+      <c r="H13" s="38" t="n"/>
+      <c r="I13" s="38" t="n"/>
       <c r="J13" s="16" t="n"/>
       <c r="K13" s="16" t="n"/>
       <c r="L13" s="16" t="n"/>
       <c r="M13" s="18" t="n"/>
-      <c r="N13" s="35" t="n"/>
-      <c r="O13" s="36" t="inlineStr">
+      <c r="N13" s="38" t="n"/>
+      <c r="O13" s="39" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt1)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="35" t="n"/>
+      <c r="A14" s="38" t="n"/>
+      <c r="B14" s="38" t="n"/>
       <c r="C14" s="14" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="D14" s="35" t="n"/>
+      <c r="D14" s="38" t="n"/>
       <c r="E14" s="16" t="n"/>
       <c r="F14" s="16" t="n"/>
       <c r="G14" s="16" t="n"/>
-      <c r="H14" s="35" t="n"/>
-      <c r="I14" s="35" t="n"/>
+      <c r="H14" s="38" t="n"/>
+      <c r="I14" s="38" t="n"/>
       <c r="J14" s="16" t="n"/>
       <c r="K14" s="16" t="n"/>
       <c r="L14" s="16" t="n"/>
       <c r="M14" s="18" t="n"/>
-      <c r="N14" s="35" t="n"/>
-      <c r="O14" s="36" t="inlineStr">
+      <c r="N14" s="38" t="n"/>
+      <c r="O14" s="39" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt2)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="n"/>
-      <c r="B15" s="35" t="n"/>
+      <c r="A15" s="38" t="n"/>
+      <c r="B15" s="38" t="n"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D15" s="35" t="n"/>
+      <c r="D15" s="38" t="n"/>
       <c r="E15" s="16" t="n"/>
       <c r="F15" s="16" t="n"/>
       <c r="G15" s="16" t="n"/>
-      <c r="H15" s="35" t="n"/>
-      <c r="I15" s="35" t="n"/>
+      <c r="H15" s="38" t="n"/>
+      <c r="I15" s="38" t="n"/>
       <c r="J15" s="16" t="n"/>
       <c r="K15" s="16" t="n"/>
       <c r="L15" s="16" t="n"/>
       <c r="M15" s="18" t="n"/>
-      <c r="N15" s="35" t="n"/>
-      <c r="O15" s="36" t="inlineStr">
+      <c r="N15" s="38" t="n"/>
+      <c r="O15" s="39" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt3)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="n"/>
-      <c r="B16" s="37" t="n"/>
+      <c r="A16" s="40" t="n"/>
+      <c r="B16" s="40" t="n"/>
       <c r="C16" s="13" t="n"/>
-      <c r="D16" s="37" t="n"/>
+      <c r="D16" s="40" t="n"/>
       <c r="E16" s="13" t="n"/>
       <c r="F16" s="13" t="n"/>
       <c r="G16" s="13" t="n"/>
-      <c r="H16" s="37" t="n"/>
-      <c r="I16" s="37" t="n"/>
+      <c r="H16" s="40" t="n"/>
+      <c r="I16" s="40" t="n"/>
       <c r="J16" s="13" t="n"/>
       <c r="K16" s="13" t="n"/>
       <c r="L16" s="13" t="n"/>
       <c r="M16" s="18" t="n"/>
-      <c r="N16" s="37" t="n"/>
-      <c r="O16" s="36" t="inlineStr">
+      <c r="N16" s="40" t="n"/>
+      <c r="O16" s="39" t="inlineStr">
         <is>
           <t>Tuščių indų ir išvalytos ėminių sistemos tuščiojo ėminio svorio pokytis (mItp)</t>
         </is>
@@ -2150,4 +2247,291 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumentas" ma:contentTypeID="0x010100BAB57CF81AE55C4698AAD22D302297F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Kurkite naują dokumentą." ma:contentTypeScope="" ma:versionID="49ab401eb4052690d2a2629974c22fd6">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="453e7e53-5eb2-45cf-b2ab-34c867e554b8" xmlns:ns3="aa0d983d-359a-438c-9953-3af1a8ac0831" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab9969d50e0b13c63bc5bd0499c928dc" ns2:_="" ns3:_="">
+    <xsd:import namespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
+    <xsd:import namespace="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="11" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="15" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="16" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Vaizdų žymės" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="993cf2ba-b7a7-49f7-97d1-76e12a88c412" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="23" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="aa0d983d-359a-438c-9953-3af1a8ac0831" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{82c4fa3c-500e-4213-91e5-1b9e2014ea63}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="aa0d983d-359a-438c-9953-3af1a8ac0831">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="21" nillable="true" ma:displayName="Bendrinama su" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="22" nillable="true" ma:displayName="Bendrinta su išsamia informacija" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Turinio tipas"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Antraštė"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="453e7e53-5eb2-45cf-b2ab-34c867e554b8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="aa0d983d-359a-438c-9953-3af1a8ac0831" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DEB40B8-8AF4-4C88-8F9E-FB64A82FE8F0}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC542CFB-1FD9-432C-86E5-B15DDE8B6777}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{431465D1-10D6-47A7-B207-6D8BB8936332}"/>
 </file>
--- a/Rezultatai.xlsx
+++ b/Rezultatai.xlsx
@@ -228,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -267,9 +267,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -287,9 +290,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -308,6 +308,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -852,98 +855,108 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="n"/>
-      <c r="B6" s="14" t="n"/>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="15" t="n">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="17" t="n">
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="19" t="n"/>
+      <c r="F6" s="20" t="n">
         <v>0.827</v>
       </c>
-      <c r="G6" s="16" t="n"/>
-      <c r="H6" s="16" t="n"/>
-      <c r="I6" s="16" t="n"/>
-      <c r="J6" s="18" t="n"/>
-      <c r="K6" s="18" t="n"/>
-      <c r="L6" s="18" t="n"/>
-      <c r="M6" s="18" t="n"/>
-      <c r="N6" s="15" t="inlineStr">
+      <c r="G6" s="19" t="n"/>
+      <c r="H6" s="19" t="n"/>
+      <c r="I6" s="19" t="n"/>
+      <c r="J6" s="21" t="n"/>
+      <c r="K6" s="21" t="n"/>
+      <c r="L6" s="21" t="n"/>
+      <c r="M6" s="21" t="n"/>
+      <c r="N6" s="18" t="inlineStr">
         <is>
           <t>1,20</t>
         </is>
       </c>
-      <c r="O6" s="19">
+      <c r="O6" s="22">
         <f>(N6^2*3.14)/4</f>
         <v/>
       </c>
-      <c r="P6" s="18" t="n"/>
-      <c r="Q6" s="16" t="n"/>
-      <c r="R6" s="16" t="n"/>
-      <c r="S6" s="18" t="n"/>
-      <c r="T6" s="16" t="n"/>
-      <c r="U6" s="16" t="n"/>
-      <c r="V6" s="17" t="n">
+      <c r="P6" s="21" t="n"/>
+      <c r="Q6" s="19" t="n"/>
+      <c r="R6" s="19" t="n"/>
+      <c r="S6" s="21" t="n"/>
+      <c r="T6" s="19" t="n"/>
+      <c r="U6" s="19" t="n"/>
+      <c r="V6" s="20" t="n">
         <v>0.079</v>
       </c>
-      <c r="W6" s="18" t="n"/>
-      <c r="X6" s="18" t="n"/>
-      <c r="Y6" s="16" t="n"/>
+      <c r="W6" s="21" t="n"/>
+      <c r="X6" s="21" t="n"/>
+      <c r="Y6" s="19" t="n"/>
       <c r="Z6" s="13" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="25" t="n"/>
       <c r="B7" s="25" t="n"/>
       <c r="C7" s="25" t="n"/>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="17" t="n">
+      <c r="E7" s="19" t="n"/>
+      <c r="F7" s="20" t="n">
         <v>0.827</v>
       </c>
-      <c r="G7" s="16" t="n"/>
-      <c r="H7" s="16" t="n"/>
-      <c r="I7" s="16" t="n"/>
-      <c r="J7" s="18" t="n"/>
-      <c r="K7" s="18" t="n"/>
-      <c r="L7" s="18" t="n"/>
+      <c r="G7" s="19" t="n"/>
+      <c r="H7" s="19" t="n"/>
+      <c r="I7" s="19" t="n"/>
+      <c r="J7" s="21" t="n"/>
+      <c r="K7" s="21" t="n"/>
+      <c r="L7" s="21" t="n"/>
       <c r="M7" s="13" t="n"/>
-      <c r="N7" s="16" t="n"/>
-      <c r="O7" s="18" t="n"/>
-      <c r="P7" s="18" t="n"/>
-      <c r="Q7" s="16" t="n"/>
-      <c r="R7" s="16" t="n"/>
-      <c r="S7" s="18" t="n"/>
-      <c r="T7" s="16" t="n"/>
-      <c r="U7" s="16" t="n"/>
-      <c r="V7" s="17" t="n">
+      <c r="N7" s="19" t="n"/>
+      <c r="O7" s="21" t="n"/>
+      <c r="P7" s="21" t="n"/>
+      <c r="Q7" s="19" t="n"/>
+      <c r="R7" s="19" t="n"/>
+      <c r="S7" s="21" t="n"/>
+      <c r="T7" s="19" t="n"/>
+      <c r="U7" s="19" t="n"/>
+      <c r="V7" s="20" t="n">
         <v>0.079</v>
       </c>
-      <c r="W7" s="18" t="n"/>
-      <c r="X7" s="18" t="n"/>
-      <c r="Z7" s="24" t="n"/>
+      <c r="W7" s="21" t="n"/>
+      <c r="X7" s="21" t="n"/>
+      <c r="Z7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="25" t="n"/>
       <c r="B8" s="25" t="n"/>
       <c r="C8" s="25" t="n"/>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="18" t="n">
         <v>14</v>
       </c>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="17" t="n">
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="20" t="n">
         <v>0.827</v>
       </c>
-      <c r="G8" s="16" t="n"/>
-      <c r="H8" s="16" t="n"/>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="18" t="n"/>
-      <c r="K8" s="18" t="n"/>
-      <c r="L8" s="18" t="n"/>
+      <c r="G8" s="19" t="n"/>
+      <c r="H8" s="19" t="n"/>
+      <c r="I8" s="19" t="n"/>
+      <c r="J8" s="21" t="n"/>
+      <c r="K8" s="21" t="n"/>
+      <c r="L8" s="21" t="n"/>
       <c r="M8" s="13" t="n"/>
-      <c r="N8" s="16" t="n"/>
+      <c r="N8" s="19" t="n"/>
       <c r="O8" s="13" t="n"/>
       <c r="P8" s="13" t="n"/>
       <c r="Q8" s="13" t="n"/>
@@ -952,19 +965,19 @@
       <c r="A9" s="25" t="n"/>
       <c r="B9" s="25" t="n"/>
       <c r="C9" s="25" t="n"/>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="17" t="n">
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="20" t="n">
         <v>0.827</v>
       </c>
-      <c r="G9" s="16" t="n"/>
-      <c r="H9" s="16" t="n"/>
-      <c r="I9" s="16" t="n"/>
-      <c r="J9" s="18" t="n"/>
-      <c r="K9" s="18" t="n"/>
-      <c r="L9" s="18" t="n"/>
+      <c r="G9" s="19" t="n"/>
+      <c r="H9" s="19" t="n"/>
+      <c r="I9" s="19" t="n"/>
+      <c r="J9" s="21" t="n"/>
+      <c r="K9" s="21" t="n"/>
+      <c r="L9" s="21" t="n"/>
       <c r="M9" s="13" t="n"/>
       <c r="N9" s="13" t="n"/>
       <c r="O9" s="13" t="n"/>
@@ -975,163 +988,163 @@
       <c r="A10" s="25" t="n"/>
       <c r="B10" s="25" t="n"/>
       <c r="C10" s="25" t="n"/>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="18" t="n">
         <v>28</v>
       </c>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="17" t="n">
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="20" t="n">
         <v>0.827</v>
       </c>
-      <c r="G10" s="16" t="n"/>
-      <c r="H10" s="16" t="n"/>
-      <c r="I10" s="16" t="n"/>
-      <c r="J10" s="18" t="n"/>
-      <c r="K10" s="18" t="n"/>
-      <c r="L10" s="18" t="n"/>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="19" t="n"/>
+      <c r="I10" s="19" t="n"/>
+      <c r="J10" s="21" t="n"/>
+      <c r="K10" s="21" t="n"/>
+      <c r="L10" s="21" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="25" t="n"/>
       <c r="B11" s="25" t="n"/>
       <c r="C11" s="25" t="n"/>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="18" t="n">
         <v>39</v>
       </c>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="17" t="n">
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="20" t="n">
         <v>0.827</v>
       </c>
-      <c r="G11" s="16" t="n"/>
-      <c r="H11" s="16" t="n"/>
-      <c r="I11" s="16" t="n"/>
-      <c r="J11" s="18" t="n"/>
-      <c r="K11" s="18" t="n"/>
-      <c r="L11" s="18" t="n"/>
+      <c r="G11" s="19" t="n"/>
+      <c r="H11" s="19" t="n"/>
+      <c r="I11" s="19" t="n"/>
+      <c r="J11" s="21" t="n"/>
+      <c r="K11" s="21" t="n"/>
+      <c r="L11" s="21" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="25" t="n"/>
       <c r="B12" s="25" t="n"/>
       <c r="C12" s="25" t="n"/>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="18" t="n">
         <v>60</v>
       </c>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="17" t="n">
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="20" t="n">
         <v>0.827</v>
       </c>
-      <c r="G12" s="16" t="n"/>
-      <c r="H12" s="16" t="n"/>
-      <c r="I12" s="16" t="n"/>
-      <c r="J12" s="18" t="n"/>
-      <c r="K12" s="18" t="n"/>
-      <c r="L12" s="18" t="n"/>
+      <c r="G12" s="19" t="n"/>
+      <c r="H12" s="19" t="n"/>
+      <c r="I12" s="19" t="n"/>
+      <c r="J12" s="21" t="n"/>
+      <c r="K12" s="21" t="n"/>
+      <c r="L12" s="21" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="25" t="n"/>
       <c r="B13" s="25" t="n"/>
       <c r="C13" s="25" t="n"/>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="18" t="n">
         <v>81</v>
       </c>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="17" t="n">
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="20" t="n">
         <v>0.827</v>
       </c>
-      <c r="G13" s="16" t="n"/>
-      <c r="H13" s="16" t="n"/>
-      <c r="I13" s="16" t="n"/>
-      <c r="J13" s="18" t="n"/>
-      <c r="K13" s="18" t="n"/>
-      <c r="L13" s="18" t="n"/>
+      <c r="G13" s="19" t="n"/>
+      <c r="H13" s="19" t="n"/>
+      <c r="I13" s="19" t="n"/>
+      <c r="J13" s="21" t="n"/>
+      <c r="K13" s="21" t="n"/>
+      <c r="L13" s="21" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="25" t="n"/>
       <c r="B14" s="25" t="n"/>
       <c r="C14" s="25" t="n"/>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="18" t="n">
         <v>92</v>
       </c>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="17" t="n">
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="20" t="n">
         <v>0.827</v>
       </c>
-      <c r="G14" s="16" t="n"/>
-      <c r="H14" s="16" t="n"/>
-      <c r="I14" s="16" t="n"/>
-      <c r="J14" s="18" t="n"/>
-      <c r="K14" s="18" t="n"/>
-      <c r="L14" s="18" t="n"/>
+      <c r="G14" s="19" t="n"/>
+      <c r="H14" s="19" t="n"/>
+      <c r="I14" s="19" t="n"/>
+      <c r="J14" s="21" t="n"/>
+      <c r="K14" s="21" t="n"/>
+      <c r="L14" s="21" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="25" t="n"/>
       <c r="B15" s="25" t="n"/>
       <c r="C15" s="25" t="n"/>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="17" t="n">
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="20" t="n">
         <v>0.827</v>
       </c>
-      <c r="G15" s="16" t="n"/>
-      <c r="H15" s="16" t="n"/>
-      <c r="I15" s="16" t="n"/>
-      <c r="J15" s="18" t="n"/>
-      <c r="K15" s="18" t="n"/>
-      <c r="L15" s="18" t="n"/>
+      <c r="G15" s="19" t="n"/>
+      <c r="H15" s="19" t="n"/>
+      <c r="I15" s="19" t="n"/>
+      <c r="J15" s="21" t="n"/>
+      <c r="K15" s="21" t="n"/>
+      <c r="L15" s="21" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="25" t="n"/>
       <c r="B16" s="25" t="n"/>
       <c r="C16" s="25" t="n"/>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="18" t="n">
         <v>106</v>
       </c>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="17" t="n">
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="20" t="n">
         <v>0.827</v>
       </c>
-      <c r="G16" s="16" t="n"/>
-      <c r="H16" s="16" t="n"/>
-      <c r="I16" s="16" t="n"/>
-      <c r="J16" s="18" t="n"/>
-      <c r="K16" s="18" t="n"/>
-      <c r="L16" s="18" t="n"/>
+      <c r="G16" s="19" t="n"/>
+      <c r="H16" s="19" t="n"/>
+      <c r="I16" s="19" t="n"/>
+      <c r="J16" s="21" t="n"/>
+      <c r="K16" s="21" t="n"/>
+      <c r="L16" s="21" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="25" t="n"/>
       <c r="B17" s="25" t="n"/>
       <c r="C17" s="25" t="n"/>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="18" t="n">
         <v>112</v>
       </c>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="17" t="n">
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="20" t="n">
         <v>0.827</v>
       </c>
-      <c r="G17" s="16" t="n"/>
-      <c r="H17" s="16" t="n"/>
-      <c r="I17" s="16" t="n"/>
-      <c r="J17" s="18" t="n"/>
-      <c r="K17" s="18" t="n"/>
-      <c r="L17" s="18" t="n"/>
+      <c r="G17" s="19" t="n"/>
+      <c r="H17" s="19" t="n"/>
+      <c r="I17" s="19" t="n"/>
+      <c r="J17" s="21" t="n"/>
+      <c r="K17" s="21" t="n"/>
+      <c r="L17" s="21" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="n"/>
-      <c r="B18" s="24" t="n"/>
-      <c r="C18" s="24" t="n"/>
-      <c r="D18" s="15" t="n">
+      <c r="A18" s="17" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="18" t="n">
         <v>115</v>
       </c>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="17" t="n">
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="20" t="n">
         <v>0.827</v>
       </c>
-      <c r="G18" s="16" t="n"/>
-      <c r="H18" s="16" t="n"/>
-      <c r="I18" s="16" t="n"/>
-      <c r="J18" s="18" t="n"/>
-      <c r="K18" s="18" t="n"/>
-      <c r="L18" s="18" t="n"/>
+      <c r="G18" s="19" t="n"/>
+      <c r="H18" s="19" t="n"/>
+      <c r="I18" s="19" t="n"/>
+      <c r="J18" s="21" t="n"/>
+      <c r="K18" s="21" t="n"/>
+      <c r="L18" s="21" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="13" t="n"/>
@@ -1151,23 +1164,23 @@
       <c r="A20" s="13" t="n"/>
       <c r="B20" s="13" t="n"/>
       <c r="C20" s="13" t="n"/>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>RPU***</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>Kai bus 2 linijos, RPU*** yra 2 linijos vidurinis taškas</t>
         </is>
       </c>
-      <c r="F20" s="22" t="n"/>
-      <c r="G20" s="22" t="n"/>
-      <c r="H20" s="22" t="n"/>
-      <c r="I20" s="22" t="n"/>
-      <c r="J20" s="22" t="n"/>
-      <c r="K20" s="22" t="n"/>
-      <c r="L20" s="23" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="15" t="n"/>
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="15" t="n"/>
+      <c r="K20" s="15" t="n"/>
+      <c r="L20" s="16" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="13" t="n"/>
@@ -1299,7 +1312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AA6"/>
+  <dimension ref="A2:AA18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1472,6 +1485,19 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
           <t>1,20</t>
@@ -1482,9 +1508,24 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
     <mergeCell ref="A2:V2"/>
+    <mergeCell ref="B6:B18"/>
+    <mergeCell ref="C6:C18"/>
+    <mergeCell ref="A6:A18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1854,8 +1895,8 @@
           <t>Filtro/indo svoris prieš KD ėmimą mpr (g)</t>
         </is>
       </c>
-      <c r="F4" s="22" t="n"/>
-      <c r="G4" s="23" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="16" t="n"/>
       <c r="H4" s="12" t="inlineStr">
         <is>
           <t>Atsakingo asmens inicialai, data</t>
@@ -1871,8 +1912,8 @@
           <t>Filtro/indo svoris po KD ėmimo mpo (g)</t>
         </is>
       </c>
-      <c r="K4" s="22" t="n"/>
-      <c r="L4" s="23" t="n"/>
+      <c r="K4" s="15" t="n"/>
+      <c r="L4" s="16" t="n"/>
       <c r="M4" s="12" t="inlineStr">
         <is>
           <t>Kietųjų dalelių svoris mf/Svorių pokytis (g) (&lt;2,20 g filtro talpumas)</t>
@@ -1890,10 +1931,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="n"/>
-      <c r="B5" s="24" t="n"/>
-      <c r="C5" s="24" t="n"/>
-      <c r="D5" s="24" t="n"/>
+      <c r="A5" s="17" t="n"/>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
       <c r="E5" s="12" t="inlineStr">
         <is>
           <t>1</t>
@@ -1909,8 +1950,8 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H5" s="24" t="n"/>
-      <c r="I5" s="24" t="n"/>
+      <c r="H5" s="17" t="n"/>
+      <c r="I5" s="17" t="n"/>
       <c r="J5" s="12" t="inlineStr">
         <is>
           <t>1</t>
@@ -1926,252 +1967,252 @@
           <t>3</t>
         </is>
       </c>
-      <c r="M5" s="24" t="n"/>
-      <c r="N5" s="24" t="n"/>
-      <c r="O5" s="24" t="n"/>
+      <c r="M5" s="17" t="n"/>
+      <c r="N5" s="17" t="n"/>
+      <c r="O5" s="17" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="36" t="n"/>
       <c r="B6" s="36" t="n"/>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="36" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
-      <c r="G6" s="16" t="n"/>
+      <c r="E6" s="19" t="n"/>
+      <c r="F6" s="19" t="n"/>
+      <c r="G6" s="19" t="n"/>
       <c r="H6" s="36" t="n"/>
       <c r="I6" s="36" t="n"/>
-      <c r="J6" s="16" t="n"/>
-      <c r="K6" s="16" t="n"/>
-      <c r="L6" s="16" t="n"/>
-      <c r="M6" s="18" t="n"/>
+      <c r="J6" s="19" t="n"/>
+      <c r="K6" s="19" t="n"/>
+      <c r="L6" s="19" t="n"/>
+      <c r="M6" s="21" t="n"/>
       <c r="N6" s="36" t="n"/>
-      <c r="O6" s="37" t="inlineStr">
+      <c r="O6" s="38" t="inlineStr">
         <is>
           <t>1 linija, 2 filtrai</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="n"/>
-      <c r="B7" s="38" t="n"/>
-      <c r="C7" s="14" t="n">
+      <c r="A7" s="39" t="n"/>
+      <c r="B7" s="39" t="n"/>
+      <c r="C7" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="38" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
-      <c r="G7" s="16" t="n"/>
-      <c r="H7" s="38" t="n"/>
-      <c r="I7" s="38" t="n"/>
-      <c r="J7" s="16" t="n"/>
-      <c r="K7" s="16" t="n"/>
-      <c r="L7" s="16" t="n"/>
-      <c r="M7" s="18" t="n"/>
-      <c r="N7" s="38" t="n"/>
+      <c r="D7" s="39" t="n"/>
+      <c r="E7" s="19" t="n"/>
+      <c r="F7" s="19" t="n"/>
+      <c r="G7" s="19" t="n"/>
+      <c r="H7" s="39" t="n"/>
+      <c r="I7" s="39" t="n"/>
+      <c r="J7" s="19" t="n"/>
+      <c r="K7" s="19" t="n"/>
+      <c r="L7" s="19" t="n"/>
+      <c r="M7" s="21" t="n"/>
+      <c r="N7" s="39" t="n"/>
       <c r="O7" s="13" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="n"/>
-      <c r="B8" s="38" t="n"/>
+      <c r="A8" s="39" t="n"/>
+      <c r="B8" s="39" t="n"/>
       <c r="C8" s="13" t="n"/>
-      <c r="D8" s="38" t="n"/>
+      <c r="D8" s="39" t="n"/>
       <c r="E8" s="13" t="n"/>
       <c r="F8" s="13" t="n"/>
       <c r="G8" s="13" t="n"/>
-      <c r="H8" s="38" t="n"/>
-      <c r="I8" s="38" t="n"/>
+      <c r="H8" s="39" t="n"/>
+      <c r="I8" s="39" t="n"/>
       <c r="J8" s="13" t="n"/>
       <c r="K8" s="13" t="n"/>
       <c r="L8" s="13" t="n"/>
-      <c r="M8" s="18" t="n"/>
-      <c r="N8" s="38" t="n"/>
+      <c r="M8" s="21" t="n"/>
+      <c r="N8" s="39" t="n"/>
       <c r="O8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="n"/>
-      <c r="B9" s="38" t="n"/>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="A9" s="39" t="n"/>
+      <c r="B9" s="39" t="n"/>
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="38" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
-      <c r="G9" s="16" t="n"/>
-      <c r="H9" s="38" t="n"/>
-      <c r="I9" s="38" t="n"/>
-      <c r="J9" s="16" t="n"/>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="16" t="n"/>
-      <c r="M9" s="18" t="n"/>
-      <c r="N9" s="38" t="n"/>
-      <c r="O9" s="39" t="inlineStr">
+      <c r="D9" s="39" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="19" t="n"/>
+      <c r="H9" s="39" t="n"/>
+      <c r="I9" s="39" t="n"/>
+      <c r="J9" s="19" t="n"/>
+      <c r="K9" s="19" t="n"/>
+      <c r="L9" s="19" t="n"/>
+      <c r="M9" s="21" t="n"/>
+      <c r="N9" s="39" t="n"/>
+      <c r="O9" s="40" t="inlineStr">
         <is>
           <t>Tuščiasis ėminys (mt)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="n"/>
-      <c r="B10" s="38" t="n"/>
+      <c r="A10" s="39" t="n"/>
+      <c r="B10" s="39" t="n"/>
       <c r="C10" s="13" t="n"/>
-      <c r="D10" s="38" t="n"/>
+      <c r="D10" s="39" t="n"/>
       <c r="E10" s="13" t="n"/>
       <c r="F10" s="13" t="n"/>
       <c r="G10" s="13" t="n"/>
-      <c r="H10" s="38" t="n"/>
-      <c r="I10" s="38" t="n"/>
+      <c r="H10" s="39" t="n"/>
+      <c r="I10" s="39" t="n"/>
       <c r="J10" s="13" t="n"/>
       <c r="K10" s="13" t="n"/>
       <c r="L10" s="13" t="n"/>
       <c r="M10" s="13" t="n"/>
-      <c r="N10" s="38" t="n"/>
+      <c r="N10" s="39" t="n"/>
       <c r="O10" s="13" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="n"/>
-      <c r="B11" s="38" t="n"/>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="A11" s="39" t="n"/>
+      <c r="B11" s="39" t="n"/>
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D11" s="38" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="16" t="n"/>
-      <c r="H11" s="38" t="n"/>
-      <c r="I11" s="38" t="n"/>
-      <c r="J11" s="16" t="n"/>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="16" t="n"/>
-      <c r="M11" s="18" t="n"/>
-      <c r="N11" s="38" t="n"/>
-      <c r="O11" s="39" t="inlineStr">
+      <c r="D11" s="39" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="19" t="n"/>
+      <c r="H11" s="39" t="n"/>
+      <c r="I11" s="39" t="n"/>
+      <c r="J11" s="19" t="n"/>
+      <c r="K11" s="19" t="n"/>
+      <c r="L11" s="19" t="n"/>
+      <c r="M11" s="21" t="n"/>
+      <c r="N11" s="39" t="n"/>
+      <c r="O11" s="40" t="inlineStr">
         <is>
           <t>Išplautos nuosėdos (mn)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="n"/>
-      <c r="B12" s="38" t="n"/>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="A12" s="39" t="n"/>
+      <c r="B12" s="39" t="n"/>
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="D12" s="38" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
-      <c r="G12" s="16" t="n"/>
-      <c r="H12" s="38" t="n"/>
-      <c r="I12" s="38" t="n"/>
-      <c r="J12" s="16" t="n"/>
-      <c r="K12" s="16" t="n"/>
-      <c r="L12" s="16" t="n"/>
-      <c r="M12" s="18" t="n"/>
-      <c r="N12" s="38" t="n"/>
-      <c r="O12" s="39" t="inlineStr">
+      <c r="D12" s="39" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="19" t="n"/>
+      <c r="H12" s="39" t="n"/>
+      <c r="I12" s="39" t="n"/>
+      <c r="J12" s="19" t="n"/>
+      <c r="K12" s="19" t="n"/>
+      <c r="L12" s="19" t="n"/>
+      <c r="M12" s="21" t="n"/>
+      <c r="N12" s="39" t="n"/>
+      <c r="O12" s="40" t="inlineStr">
         <is>
           <t>Išvalytos ėminių sistemos tuščiasis ėminys (mIt)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="38" t="n"/>
-      <c r="B13" s="38" t="n"/>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="A13" s="39" t="n"/>
+      <c r="B13" s="39" t="n"/>
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D13" s="38" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="16" t="n"/>
-      <c r="H13" s="38" t="n"/>
-      <c r="I13" s="38" t="n"/>
-      <c r="J13" s="16" t="n"/>
-      <c r="K13" s="16" t="n"/>
-      <c r="L13" s="16" t="n"/>
-      <c r="M13" s="18" t="n"/>
-      <c r="N13" s="38" t="n"/>
-      <c r="O13" s="39" t="inlineStr">
+      <c r="D13" s="39" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="19" t="n"/>
+      <c r="G13" s="19" t="n"/>
+      <c r="H13" s="39" t="n"/>
+      <c r="I13" s="39" t="n"/>
+      <c r="J13" s="19" t="n"/>
+      <c r="K13" s="19" t="n"/>
+      <c r="L13" s="19" t="n"/>
+      <c r="M13" s="21" t="n"/>
+      <c r="N13" s="39" t="n"/>
+      <c r="O13" s="40" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt1)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="n"/>
-      <c r="B14" s="38" t="n"/>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="A14" s="39" t="n"/>
+      <c r="B14" s="39" t="n"/>
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="D14" s="38" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="16" t="n"/>
-      <c r="H14" s="38" t="n"/>
-      <c r="I14" s="38" t="n"/>
-      <c r="J14" s="16" t="n"/>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="16" t="n"/>
-      <c r="M14" s="18" t="n"/>
-      <c r="N14" s="38" t="n"/>
-      <c r="O14" s="39" t="inlineStr">
+      <c r="D14" s="39" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19" t="n"/>
+      <c r="H14" s="39" t="n"/>
+      <c r="I14" s="39" t="n"/>
+      <c r="J14" s="19" t="n"/>
+      <c r="K14" s="19" t="n"/>
+      <c r="L14" s="19" t="n"/>
+      <c r="M14" s="21" t="n"/>
+      <c r="N14" s="39" t="n"/>
+      <c r="O14" s="40" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt2)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="n"/>
-      <c r="B15" s="38" t="n"/>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="A15" s="39" t="n"/>
+      <c r="B15" s="39" t="n"/>
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D15" s="38" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="16" t="n"/>
-      <c r="H15" s="38" t="n"/>
-      <c r="I15" s="38" t="n"/>
-      <c r="J15" s="16" t="n"/>
-      <c r="K15" s="16" t="n"/>
-      <c r="L15" s="16" t="n"/>
-      <c r="M15" s="18" t="n"/>
-      <c r="N15" s="38" t="n"/>
-      <c r="O15" s="39" t="inlineStr">
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="19" t="n"/>
+      <c r="G15" s="19" t="n"/>
+      <c r="H15" s="39" t="n"/>
+      <c r="I15" s="39" t="n"/>
+      <c r="J15" s="19" t="n"/>
+      <c r="K15" s="19" t="n"/>
+      <c r="L15" s="19" t="n"/>
+      <c r="M15" s="21" t="n"/>
+      <c r="N15" s="39" t="n"/>
+      <c r="O15" s="40" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt3)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="40" t="n"/>
-      <c r="B16" s="40" t="n"/>
+      <c r="A16" s="41" t="n"/>
+      <c r="B16" s="41" t="n"/>
       <c r="C16" s="13" t="n"/>
-      <c r="D16" s="40" t="n"/>
+      <c r="D16" s="41" t="n"/>
       <c r="E16" s="13" t="n"/>
       <c r="F16" s="13" t="n"/>
       <c r="G16" s="13" t="n"/>
-      <c r="H16" s="40" t="n"/>
-      <c r="I16" s="40" t="n"/>
+      <c r="H16" s="41" t="n"/>
+      <c r="I16" s="41" t="n"/>
       <c r="J16" s="13" t="n"/>
       <c r="K16" s="13" t="n"/>
       <c r="L16" s="13" t="n"/>
-      <c r="M16" s="18" t="n"/>
-      <c r="N16" s="40" t="n"/>
-      <c r="O16" s="39" t="inlineStr">
+      <c r="M16" s="21" t="n"/>
+      <c r="N16" s="41" t="n"/>
+      <c r="O16" s="40" t="inlineStr">
         <is>
           <t>Tuščių indų ir išvalytos ėminių sistemos tuščiojo ėminio svorio pokytis (mItp)</t>
         </is>
@@ -2247,291 +2288,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumentas" ma:contentTypeID="0x010100BAB57CF81AE55C4698AAD22D302297F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Kurkite naują dokumentą." ma:contentTypeScope="" ma:versionID="49ab401eb4052690d2a2629974c22fd6">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="453e7e53-5eb2-45cf-b2ab-34c867e554b8" xmlns:ns3="aa0d983d-359a-438c-9953-3af1a8ac0831" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab9969d50e0b13c63bc5bd0499c928dc" ns2:_="" ns3:_="">
-    <xsd:import namespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
-    <xsd:import namespace="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="11" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="15" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="16" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Vaizdų žymės" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="993cf2ba-b7a7-49f7-97d1-76e12a88c412" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="23" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="aa0d983d-359a-438c-9953-3af1a8ac0831" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{82c4fa3c-500e-4213-91e5-1b9e2014ea63}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="aa0d983d-359a-438c-9953-3af1a8ac0831">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="21" nillable="true" ma:displayName="Bendrinama su" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="22" nillable="true" ma:displayName="Bendrinta su išsamia informacija" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Turinio tipas"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Antraštė"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="453e7e53-5eb2-45cf-b2ab-34c867e554b8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="aa0d983d-359a-438c-9953-3af1a8ac0831" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DEB40B8-8AF4-4C88-8F9E-FB64A82FE8F0}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC542CFB-1FD9-432C-86E5-B15DDE8B6777}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{431465D1-10D6-47A7-B207-6D8BB8936332}"/>
 </file>
--- a/Rezultatai.xlsx
+++ b/Rezultatai.xlsx
@@ -228,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -270,9 +270,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -290,8 +291,9 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -305,12 +307,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -684,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:Z23"/>
+  <dimension ref="A3:AH14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -713,6 +721,14 @@
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="15" customWidth="1" min="25" max="25"/>
     <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
+    <col width="15" customWidth="1" min="30" max="30"/>
+    <col width="15" customWidth="1" min="31" max="31"/>
+    <col width="15" customWidth="1" min="32" max="32"/>
+    <col width="15" customWidth="1" min="33" max="33"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -750,105 +766,145 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 2 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 3 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 4 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Išmatuotas diferencinis slėgis taškuose 5 linija, Pdi, hPa</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>Pito vamzdelio koeficientas, K</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Temperatūra ortakyje t, oC</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Atmosferinis slėgis P, hPa</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Statinis slėgis ortakyje ± ΔP, hPa</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Dujų slėgis kamine Pk= P+ ΔP, hPa</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Dujų mol. masė Ms= qn *22.4, kg/</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Dujų srauto greitis matavimo taškuose, 1 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>Dujų srauto greitis matavimo taškuose, 2 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>Dujų srauto greitis matavimo taškuose, 3 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>Dujų srauto greitis matavimo taškuose, 4 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>Dujų srauto greitis matavimo taškuose, 5 linija, wi = K*129 *√t *√Pdi/ √Pk/√Ms, m/s</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>Vidutinis dujų srauto greitis ortakyje w, m/s</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>Ortakio diametras, matmenys, m</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t>Ortakio skerspjūvio plotas F, m2</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t>Dujų tūrio debitas realiomis sąlygomis Vk = wvid × F, m3/s</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>Dujų tūrio debitas normaliosiomis sąlygomis Vdr n.s =Vk *0,269*(P±ΔP)/(273+t), m3/s</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="Z5" s="3" t="inlineStr">
         <is>
           <t>Vandens kondensato masė m H2O, kg</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>Vandens garų konc. dujose x=mH2O/Vmn*qn, kg/kg</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="AB5" s="3" t="inlineStr">
         <is>
           <t>Sausų dujų tūrio debitas normaliosiomis sąlygomis Vn= Vdr n.s *((1/(1+(x*qn/0.8038)))</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="AC5" s="3" t="inlineStr">
         <is>
           <t>Prasiurbtas dujų tūris normaliosiomis sąlygomis Vmn, Nm3</t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
+      <c r="AD5" s="3" t="inlineStr">
         <is>
           <t>Išplėstinės neapibrėžties koef. A</t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr">
+      <c r="AE5" s="3" t="inlineStr">
         <is>
           <t>Išplėstinė neapibrėžtis (dujų tūrio debitas) Uv</t>
         </is>
       </c>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="AF5" s="3" t="inlineStr">
         <is>
           <t>Išplėstinė neapibrėžtis (dujų srauto greitis) Uw</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
+      <c r="AG5" s="3" t="inlineStr">
         <is>
           <t>Sausų dujų tankis normaliosioms sąlygomis qn, (kg/m3)</t>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
+      <c r="AH5" s="3" t="inlineStr">
         <is>
           <t>Skaičiavimus atliko (inicialai, data)</t>
         </is>
@@ -868,343 +924,233 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="D6" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="19" t="n"/>
-      <c r="F6" s="20" t="n">
+      <c r="D6" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="E6" s="20" t="n"/>
+      <c r="F6" s="20" t="n"/>
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="20" t="n"/>
+      <c r="J6" s="21" t="n">
         <v>0.827</v>
       </c>
-      <c r="G6" s="19" t="n"/>
-      <c r="H6" s="19" t="n"/>
-      <c r="I6" s="19" t="n"/>
-      <c r="J6" s="21" t="n"/>
-      <c r="K6" s="21" t="n"/>
-      <c r="L6" s="21" t="n"/>
-      <c r="M6" s="21" t="n"/>
-      <c r="N6" s="18" t="inlineStr">
-        <is>
-          <t>1,20</t>
-        </is>
-      </c>
-      <c r="O6" s="22">
-        <f>(N6^2*3.14)/4</f>
+      <c r="K6" s="20" t="n"/>
+      <c r="L6" s="20" t="n"/>
+      <c r="M6" s="20" t="n"/>
+      <c r="N6" s="22" t="n"/>
+      <c r="O6" s="22" t="n"/>
+      <c r="P6" s="22" t="n"/>
+      <c r="Q6" s="22" t="n"/>
+      <c r="R6" s="22" t="n"/>
+      <c r="S6" s="22" t="n"/>
+      <c r="T6" s="22" t="n"/>
+      <c r="U6" s="22" t="n"/>
+      <c r="V6" s="20" t="n"/>
+      <c r="W6" s="22" t="n"/>
+      <c r="X6" s="22" t="n"/>
+      <c r="Y6" s="20" t="n"/>
+      <c r="Z6" s="20" t="n"/>
+      <c r="AA6" s="22" t="n"/>
+      <c r="AB6" s="20" t="n"/>
+      <c r="AC6" s="20" t="n"/>
+      <c r="AD6" s="21" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="AE6" s="22" t="n"/>
+      <c r="AF6" s="22" t="n"/>
+      <c r="AG6" s="20" t="n"/>
+      <c r="AH6" s="13" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="19" t="n">
+        <v>47</v>
+      </c>
+      <c r="E7" s="20" t="n"/>
+      <c r="F7" s="20" t="n"/>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="20" t="n"/>
+      <c r="I7" s="20" t="n"/>
+      <c r="J7" s="21" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="K7" s="20" t="n"/>
+      <c r="L7" s="20" t="n"/>
+      <c r="M7" s="20" t="n"/>
+      <c r="N7" s="22" t="n"/>
+      <c r="O7" s="22" t="n"/>
+      <c r="P7" s="22" t="n"/>
+      <c r="Q7" s="22" t="n"/>
+      <c r="R7" s="22" t="n"/>
+      <c r="S7" s="22" t="n"/>
+      <c r="T7" s="22" t="n"/>
+      <c r="U7" s="13" t="n"/>
+      <c r="V7" s="19" t="inlineStr">
+        <is>
+          <t>1,25</t>
+        </is>
+      </c>
+      <c r="W7" s="23">
+        <f>V7*V8</f>
         <v/>
       </c>
-      <c r="P6" s="21" t="n"/>
-      <c r="Q6" s="19" t="n"/>
-      <c r="R6" s="19" t="n"/>
-      <c r="S6" s="21" t="n"/>
-      <c r="T6" s="19" t="n"/>
-      <c r="U6" s="19" t="n"/>
-      <c r="V6" s="20" t="n">
+      <c r="X7" s="22" t="n"/>
+      <c r="Y7" s="20" t="n"/>
+      <c r="Z7" s="20" t="n"/>
+      <c r="AA7" s="22" t="n"/>
+      <c r="AB7" s="20" t="n"/>
+      <c r="AC7" s="20" t="n"/>
+      <c r="AD7" s="21" t="n">
         <v>0.079</v>
       </c>
-      <c r="W6" s="21" t="n"/>
-      <c r="X6" s="21" t="n"/>
-      <c r="Y6" s="19" t="n"/>
-      <c r="Z6" s="13" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="25" t="n"/>
-      <c r="B7" s="25" t="n"/>
-      <c r="C7" s="25" t="n"/>
-      <c r="D7" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="E7" s="19" t="n"/>
-      <c r="F7" s="20" t="n">
+      <c r="AE7" s="22" t="n"/>
+      <c r="AF7" s="22" t="n"/>
+      <c r="AH7" s="16" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="19" t="n">
+        <v>78</v>
+      </c>
+      <c r="E8" s="20" t="n"/>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
+      <c r="I8" s="20" t="n"/>
+      <c r="J8" s="21" t="n">
         <v>0.827</v>
       </c>
-      <c r="G7" s="19" t="n"/>
-      <c r="H7" s="19" t="n"/>
-      <c r="I7" s="19" t="n"/>
-      <c r="J7" s="21" t="n"/>
-      <c r="K7" s="21" t="n"/>
-      <c r="L7" s="21" t="n"/>
-      <c r="M7" s="13" t="n"/>
-      <c r="N7" s="19" t="n"/>
-      <c r="O7" s="21" t="n"/>
-      <c r="P7" s="21" t="n"/>
-      <c r="Q7" s="19" t="n"/>
-      <c r="R7" s="19" t="n"/>
-      <c r="S7" s="21" t="n"/>
-      <c r="T7" s="19" t="n"/>
-      <c r="U7" s="19" t="n"/>
-      <c r="V7" s="20" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="W7" s="21" t="n"/>
-      <c r="X7" s="21" t="n"/>
-      <c r="Z7" s="17" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="25" t="n"/>
-      <c r="B8" s="25" t="n"/>
-      <c r="C8" s="25" t="n"/>
-      <c r="D8" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="E8" s="19" t="n"/>
-      <c r="F8" s="20" t="n">
+      <c r="K8" s="20" t="n"/>
+      <c r="L8" s="20" t="n"/>
+      <c r="M8" s="20" t="n"/>
+      <c r="N8" s="22" t="n"/>
+      <c r="O8" s="22" t="n"/>
+      <c r="P8" s="22" t="n"/>
+      <c r="Q8" s="22" t="n"/>
+      <c r="R8" s="22" t="n"/>
+      <c r="S8" s="22" t="n"/>
+      <c r="T8" s="22" t="n"/>
+      <c r="U8" s="13" t="n"/>
+      <c r="V8" s="19" t="inlineStr">
+        <is>
+          <t>1,25</t>
+        </is>
+      </c>
+      <c r="W8" s="13" t="n"/>
+      <c r="X8" s="13" t="n"/>
+      <c r="Y8" s="13" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="n"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="19" t="n">
+        <v>109</v>
+      </c>
+      <c r="E9" s="20" t="n"/>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
+      <c r="I9" s="20" t="n"/>
+      <c r="J9" s="21" t="n">
         <v>0.827</v>
       </c>
-      <c r="G8" s="19" t="n"/>
-      <c r="H8" s="19" t="n"/>
-      <c r="I8" s="19" t="n"/>
-      <c r="J8" s="21" t="n"/>
-      <c r="K8" s="21" t="n"/>
-      <c r="L8" s="21" t="n"/>
-      <c r="M8" s="13" t="n"/>
-      <c r="N8" s="19" t="n"/>
-      <c r="O8" s="13" t="n"/>
-      <c r="P8" s="13" t="n"/>
-      <c r="Q8" s="13" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="25" t="n"/>
-      <c r="B9" s="25" t="n"/>
-      <c r="C9" s="25" t="n"/>
-      <c r="D9" s="18" t="n">
-        <v>20</v>
-      </c>
-      <c r="E9" s="19" t="n"/>
-      <c r="F9" s="20" t="n">
-        <v>0.827</v>
-      </c>
-      <c r="G9" s="19" t="n"/>
-      <c r="H9" s="19" t="n"/>
-      <c r="I9" s="19" t="n"/>
-      <c r="J9" s="21" t="n"/>
-      <c r="K9" s="21" t="n"/>
-      <c r="L9" s="21" t="n"/>
-      <c r="M9" s="13" t="n"/>
-      <c r="N9" s="13" t="n"/>
-      <c r="O9" s="13" t="n"/>
-      <c r="P9" s="13" t="n"/>
-      <c r="Q9" s="13" t="n"/>
+      <c r="K9" s="20" t="n"/>
+      <c r="L9" s="20" t="n"/>
+      <c r="M9" s="20" t="n"/>
+      <c r="N9" s="22" t="n"/>
+      <c r="O9" s="22" t="n"/>
+      <c r="P9" s="22" t="n"/>
+      <c r="Q9" s="22" t="n"/>
+      <c r="R9" s="22" t="n"/>
+      <c r="S9" s="22" t="n"/>
+      <c r="T9" s="22" t="n"/>
+      <c r="U9" s="13" t="n"/>
+      <c r="V9" s="13" t="n"/>
+      <c r="W9" s="13" t="n"/>
+      <c r="X9" s="13" t="n"/>
+      <c r="Y9" s="13" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="n"/>
-      <c r="B10" s="25" t="n"/>
-      <c r="C10" s="25" t="n"/>
-      <c r="D10" s="18" t="n">
-        <v>28</v>
-      </c>
-      <c r="E10" s="19" t="n"/>
-      <c r="F10" s="20" t="n">
-        <v>0.827</v>
-      </c>
-      <c r="G10" s="19" t="n"/>
-      <c r="H10" s="19" t="n"/>
-      <c r="I10" s="19" t="n"/>
-      <c r="J10" s="21" t="n"/>
-      <c r="K10" s="21" t="n"/>
-      <c r="L10" s="21" t="n"/>
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="13" t="n"/>
+      <c r="I10" s="13" t="n"/>
+      <c r="J10" s="13" t="n"/>
+      <c r="K10" s="13" t="n"/>
+      <c r="L10" s="13" t="n"/>
+      <c r="M10" s="13" t="n"/>
+      <c r="N10" s="13" t="n"/>
+      <c r="O10" s="13" t="n"/>
+      <c r="P10" s="13" t="n"/>
+      <c r="Q10" s="13" t="n"/>
+      <c r="R10" s="13" t="n"/>
+      <c r="S10" s="13" t="n"/>
+      <c r="T10" s="13" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="n"/>
-      <c r="B11" s="25" t="n"/>
-      <c r="C11" s="25" t="n"/>
-      <c r="D11" s="18" t="n">
-        <v>39</v>
-      </c>
-      <c r="E11" s="19" t="n"/>
-      <c r="F11" s="20" t="n">
-        <v>0.827</v>
-      </c>
-      <c r="G11" s="19" t="n"/>
-      <c r="H11" s="19" t="n"/>
-      <c r="I11" s="19" t="n"/>
-      <c r="J11" s="21" t="n"/>
-      <c r="K11" s="21" t="n"/>
-      <c r="L11" s="21" t="n"/>
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>RPU***</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>Kai bus 2 linijos, RPU*** yra 2 linijos vidurinis taškas</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="17" t="n"/>
+      <c r="H11" s="17" t="n"/>
+      <c r="I11" s="17" t="n"/>
+      <c r="J11" s="17" t="n"/>
+      <c r="K11" s="17" t="n"/>
+      <c r="L11" s="17" t="n"/>
+      <c r="M11" s="17" t="n"/>
+      <c r="N11" s="17" t="n"/>
+      <c r="O11" s="17" t="n"/>
+      <c r="P11" s="17" t="n"/>
+      <c r="Q11" s="17" t="n"/>
+      <c r="R11" s="17" t="n"/>
+      <c r="S11" s="17" t="n"/>
+      <c r="T11" s="18" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="n"/>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="25" t="n"/>
-      <c r="D12" s="18" t="n">
-        <v>60</v>
-      </c>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="20" t="n">
-        <v>0.827</v>
-      </c>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="19" t="n"/>
-      <c r="I12" s="19" t="n"/>
-      <c r="J12" s="21" t="n"/>
-      <c r="K12" s="21" t="n"/>
-      <c r="L12" s="21" t="n"/>
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="n"/>
-      <c r="B13" s="25" t="n"/>
-      <c r="C13" s="25" t="n"/>
-      <c r="D13" s="18" t="n">
-        <v>81</v>
-      </c>
-      <c r="E13" s="19" t="n"/>
-      <c r="F13" s="20" t="n">
-        <v>0.827</v>
-      </c>
-      <c r="G13" s="19" t="n"/>
-      <c r="H13" s="19" t="n"/>
-      <c r="I13" s="19" t="n"/>
-      <c r="J13" s="21" t="n"/>
-      <c r="K13" s="21" t="n"/>
-      <c r="L13" s="21" t="n"/>
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="n"/>
-      <c r="B14" s="25" t="n"/>
-      <c r="C14" s="25" t="n"/>
-      <c r="D14" s="18" t="n">
-        <v>92</v>
-      </c>
-      <c r="E14" s="19" t="n"/>
-      <c r="F14" s="20" t="n">
-        <v>0.827</v>
-      </c>
-      <c r="G14" s="19" t="n"/>
-      <c r="H14" s="19" t="n"/>
-      <c r="I14" s="19" t="n"/>
-      <c r="J14" s="21" t="n"/>
-      <c r="K14" s="21" t="n"/>
-      <c r="L14" s="21" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="25" t="n"/>
-      <c r="B15" s="25" t="n"/>
-      <c r="C15" s="25" t="n"/>
-      <c r="D15" s="18" t="n">
-        <v>100</v>
-      </c>
-      <c r="E15" s="19" t="n"/>
-      <c r="F15" s="20" t="n">
-        <v>0.827</v>
-      </c>
-      <c r="G15" s="19" t="n"/>
-      <c r="H15" s="19" t="n"/>
-      <c r="I15" s="19" t="n"/>
-      <c r="J15" s="21" t="n"/>
-      <c r="K15" s="21" t="n"/>
-      <c r="L15" s="21" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="25" t="n"/>
-      <c r="B16" s="25" t="n"/>
-      <c r="C16" s="25" t="n"/>
-      <c r="D16" s="18" t="n">
-        <v>106</v>
-      </c>
-      <c r="E16" s="19" t="n"/>
-      <c r="F16" s="20" t="n">
-        <v>0.827</v>
-      </c>
-      <c r="G16" s="19" t="n"/>
-      <c r="H16" s="19" t="n"/>
-      <c r="I16" s="19" t="n"/>
-      <c r="J16" s="21" t="n"/>
-      <c r="K16" s="21" t="n"/>
-      <c r="L16" s="21" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="25" t="n"/>
-      <c r="B17" s="25" t="n"/>
-      <c r="C17" s="25" t="n"/>
-      <c r="D17" s="18" t="n">
-        <v>112</v>
-      </c>
-      <c r="E17" s="19" t="n"/>
-      <c r="F17" s="20" t="n">
-        <v>0.827</v>
-      </c>
-      <c r="G17" s="19" t="n"/>
-      <c r="H17" s="19" t="n"/>
-      <c r="I17" s="19" t="n"/>
-      <c r="J17" s="21" t="n"/>
-      <c r="K17" s="21" t="n"/>
-      <c r="L17" s="21" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="n"/>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="18" t="n">
-        <v>115</v>
-      </c>
-      <c r="E18" s="19" t="n"/>
-      <c r="F18" s="20" t="n">
-        <v>0.827</v>
-      </c>
-      <c r="G18" s="19" t="n"/>
-      <c r="H18" s="19" t="n"/>
-      <c r="I18" s="19" t="n"/>
-      <c r="J18" s="21" t="n"/>
-      <c r="K18" s="21" t="n"/>
-      <c r="L18" s="21" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="n"/>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="13" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
-      <c r="L19" s="13" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="n"/>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="23" t="inlineStr">
-        <is>
-          <t>RPU***</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="inlineStr">
-        <is>
-          <t>Kai bus 2 linijos, RPU*** yra 2 linijos vidurinis taškas</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
-      <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
-      <c r="K20" s="15" t="n"/>
-      <c r="L20" s="16" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="n"/>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="n"/>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="n"/>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="E20:L20"/>
-    <mergeCell ref="A3:Z3"/>
-    <mergeCell ref="B6:B18"/>
-    <mergeCell ref="C6:C18"/>
-    <mergeCell ref="A6:A18"/>
-    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="A3:AH3"/>
+    <mergeCell ref="E11:T11"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="AH6:AH7"/>
+    <mergeCell ref="C6:C9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1312,7 +1258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AA18"/>
+  <dimension ref="A2:AA9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1369,7 +1315,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Ortakio skersmuo d, m</t>
+          <t>Ortakio matmenys, m</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -1485,47 +1431,50 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>1,20</t>
+          <t>1,25 x 1,25</t>
         </is>
       </c>
       <c r="E6" s="11">
-        <f>'Greitis'!O6</f>
+        <f>'Greitis'!W7</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
+    <row r="7">
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="n"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:V2"/>
-    <mergeCell ref="B6:B18"/>
-    <mergeCell ref="C6:C18"/>
-    <mergeCell ref="A6:A18"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="C6:C9"/>
+    <mergeCell ref="A6:A9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1537,7 +1486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:N5"/>
+  <dimension ref="A2:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1635,9 +1584,42 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="n"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="C6:C9"/>
     <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A6:A9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1759,10 +1741,20 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="26" t="n"/>
-      <c r="B6" s="26" t="n"/>
-      <c r="C6" s="27" t="n"/>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="D6" s="28" t="n"/>
       <c r="E6" s="29" t="n"/>
       <c r="F6" s="29" t="n"/>
@@ -1775,18 +1767,18 @@
       <c r="M6" s="30" t="n"/>
       <c r="N6" s="27" t="n"/>
       <c r="O6" s="27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P6" s="31" t="inlineStr">
         <is>
-          <t>1 linija, 1 filtras</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="32" t="n"/>
-      <c r="B7" s="32" t="n"/>
-      <c r="C7" s="34" t="n"/>
+          <t>5 linijos, 1 filtras</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="35" t="n"/>
+      <c r="B7" s="35" t="n"/>
+      <c r="C7" s="35" t="n"/>
       <c r="D7" s="28" t="n"/>
       <c r="E7" s="29" t="n"/>
       <c r="F7" s="29" t="n"/>
@@ -1795,20 +1787,20 @@
       <c r="I7" s="29" t="n"/>
       <c r="J7" s="29" t="n"/>
       <c r="K7" s="29" t="n"/>
-      <c r="L7" s="34" t="n"/>
-      <c r="M7" s="34" t="n"/>
-      <c r="N7" s="34" t="n"/>
-      <c r="O7" s="34" t="n"/>
+      <c r="L7" s="35" t="n"/>
+      <c r="M7" s="35" t="n"/>
+      <c r="N7" s="35" t="n"/>
+      <c r="O7" s="35" t="n"/>
       <c r="P7" s="31" t="inlineStr">
         <is>
-          <t>1 linija, 2 filtras</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="33" t="n"/>
-      <c r="B8" s="33" t="n"/>
-      <c r="C8" s="35" t="n"/>
+          <t>5 linijos, 2 filtras</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
       <c r="D8" s="28" t="n"/>
       <c r="E8" s="29" t="n"/>
       <c r="F8" s="29" t="n"/>
@@ -1817,19 +1809,25 @@
       <c r="I8" s="29" t="n"/>
       <c r="J8" s="29" t="n"/>
       <c r="K8" s="29" t="n"/>
-      <c r="L8" s="35" t="n"/>
-      <c r="M8" s="35" t="n"/>
-      <c r="N8" s="35" t="n"/>
-      <c r="O8" s="35" t="n"/>
-      <c r="P8" s="28" t="n"/>
+      <c r="L8" s="36" t="n"/>
+      <c r="M8" s="36" t="n"/>
+      <c r="N8" s="36" t="n"/>
+      <c r="O8" s="36" t="n"/>
+      <c r="P8" s="31" t="inlineStr">
+        <is>
+          <t>5 linijos, 3 filtras</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="M6:M8"/>
     <mergeCell ref="L6:L8"/>
     <mergeCell ref="N6:N8"/>
     <mergeCell ref="C6:C8"/>
+    <mergeCell ref="A6:A8"/>
     <mergeCell ref="O6:O8"/>
+    <mergeCell ref="B6:B8"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1895,8 +1893,8 @@
           <t>Filtro/indo svoris prieš KD ėmimą mpr (g)</t>
         </is>
       </c>
-      <c r="F4" s="15" t="n"/>
-      <c r="G4" s="16" t="n"/>
+      <c r="F4" s="17" t="n"/>
+      <c r="G4" s="18" t="n"/>
       <c r="H4" s="12" t="inlineStr">
         <is>
           <t>Atsakingo asmens inicialai, data</t>
@@ -1912,8 +1910,8 @@
           <t>Filtro/indo svoris po KD ėmimo mpo (g)</t>
         </is>
       </c>
-      <c r="K4" s="15" t="n"/>
-      <c r="L4" s="16" t="n"/>
+      <c r="K4" s="17" t="n"/>
+      <c r="L4" s="18" t="n"/>
       <c r="M4" s="12" t="inlineStr">
         <is>
           <t>Kietųjų dalelių svoris mf/Svorių pokytis (g) (&lt;2,20 g filtro talpumas)</t>
@@ -1931,10 +1929,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="n"/>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
       <c r="E5" s="12" t="inlineStr">
         <is>
           <t>1</t>
@@ -1950,8 +1948,8 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H5" s="17" t="n"/>
-      <c r="I5" s="17" t="n"/>
+      <c r="H5" s="16" t="n"/>
+      <c r="I5" s="16" t="n"/>
       <c r="J5" s="12" t="inlineStr">
         <is>
           <t>1</t>
@@ -1967,259 +1965,267 @@
           <t>3</t>
         </is>
       </c>
-      <c r="M5" s="17" t="n"/>
-      <c r="N5" s="17" t="n"/>
-      <c r="O5" s="17" t="n"/>
+      <c r="M5" s="16" t="n"/>
+      <c r="N5" s="16" t="n"/>
+      <c r="O5" s="16" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="n"/>
-      <c r="B6" s="36" t="n"/>
-      <c r="C6" s="37" t="n">
+      <c r="A6" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="C6" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="36" t="n"/>
-      <c r="E6" s="19" t="n"/>
-      <c r="F6" s="19" t="n"/>
-      <c r="G6" s="19" t="n"/>
-      <c r="H6" s="36" t="n"/>
-      <c r="I6" s="36" t="n"/>
-      <c r="J6" s="19" t="n"/>
-      <c r="K6" s="19" t="n"/>
-      <c r="L6" s="19" t="n"/>
-      <c r="M6" s="21" t="n"/>
-      <c r="N6" s="36" t="n"/>
-      <c r="O6" s="38" t="inlineStr">
-        <is>
-          <t>1 linija, 2 filtrai</t>
+      <c r="D6" s="39" t="n"/>
+      <c r="E6" s="20" t="n"/>
+      <c r="F6" s="20" t="n"/>
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="39" t="n"/>
+      <c r="I6" s="39" t="n"/>
+      <c r="J6" s="20" t="n"/>
+      <c r="K6" s="20" t="n"/>
+      <c r="L6" s="20" t="n"/>
+      <c r="M6" s="22" t="n"/>
+      <c r="N6" s="39" t="n"/>
+      <c r="O6" s="40" t="inlineStr">
+        <is>
+          <t>5 linijos, 3 filtrai</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="n"/>
-      <c r="B7" s="39" t="n"/>
-      <c r="C7" s="37" t="n">
+      <c r="A7" s="41" t="n"/>
+      <c r="B7" s="41" t="n"/>
+      <c r="C7" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="39" t="n"/>
-      <c r="E7" s="19" t="n"/>
-      <c r="F7" s="19" t="n"/>
-      <c r="G7" s="19" t="n"/>
-      <c r="H7" s="39" t="n"/>
-      <c r="I7" s="39" t="n"/>
-      <c r="J7" s="19" t="n"/>
-      <c r="K7" s="19" t="n"/>
-      <c r="L7" s="19" t="n"/>
-      <c r="M7" s="21" t="n"/>
-      <c r="N7" s="39" t="n"/>
+      <c r="D7" s="41" t="n"/>
+      <c r="E7" s="20" t="n"/>
+      <c r="F7" s="20" t="n"/>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="41" t="n"/>
+      <c r="I7" s="41" t="n"/>
+      <c r="J7" s="20" t="n"/>
+      <c r="K7" s="20" t="n"/>
+      <c r="L7" s="20" t="n"/>
+      <c r="M7" s="22" t="n"/>
+      <c r="N7" s="41" t="n"/>
       <c r="O7" s="13" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="n"/>
-      <c r="B8" s="39" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="39" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="13" t="n"/>
-      <c r="H8" s="39" t="n"/>
-      <c r="I8" s="39" t="n"/>
-      <c r="J8" s="13" t="n"/>
-      <c r="K8" s="13" t="n"/>
-      <c r="L8" s="13" t="n"/>
-      <c r="M8" s="21" t="n"/>
-      <c r="N8" s="39" t="n"/>
+      <c r="A8" s="41" t="n"/>
+      <c r="B8" s="41" t="n"/>
+      <c r="C8" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="41" t="n"/>
+      <c r="E8" s="20" t="n"/>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="41" t="n"/>
+      <c r="I8" s="41" t="n"/>
+      <c r="J8" s="20" t="n"/>
+      <c r="K8" s="20" t="n"/>
+      <c r="L8" s="20" t="n"/>
+      <c r="M8" s="22" t="n"/>
+      <c r="N8" s="41" t="n"/>
       <c r="O8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="39" t="n"/>
-      <c r="B9" s="39" t="n"/>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="A9" s="41" t="n"/>
+      <c r="B9" s="41" t="n"/>
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="39" t="n"/>
-      <c r="E9" s="19" t="n"/>
-      <c r="F9" s="19" t="n"/>
-      <c r="G9" s="19" t="n"/>
-      <c r="H9" s="39" t="n"/>
-      <c r="I9" s="39" t="n"/>
-      <c r="J9" s="19" t="n"/>
-      <c r="K9" s="19" t="n"/>
-      <c r="L9" s="19" t="n"/>
-      <c r="M9" s="21" t="n"/>
-      <c r="N9" s="39" t="n"/>
-      <c r="O9" s="40" t="inlineStr">
+      <c r="D9" s="41" t="n"/>
+      <c r="E9" s="20" t="n"/>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="41" t="n"/>
+      <c r="I9" s="41" t="n"/>
+      <c r="J9" s="20" t="n"/>
+      <c r="K9" s="20" t="n"/>
+      <c r="L9" s="20" t="n"/>
+      <c r="M9" s="22" t="n"/>
+      <c r="N9" s="41" t="n"/>
+      <c r="O9" s="42" t="inlineStr">
         <is>
           <t>Tuščiasis ėminys (mt)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="n"/>
-      <c r="B10" s="39" t="n"/>
+      <c r="A10" s="41" t="n"/>
+      <c r="B10" s="41" t="n"/>
       <c r="C10" s="13" t="n"/>
-      <c r="D10" s="39" t="n"/>
+      <c r="D10" s="41" t="n"/>
       <c r="E10" s="13" t="n"/>
       <c r="F10" s="13" t="n"/>
       <c r="G10" s="13" t="n"/>
-      <c r="H10" s="39" t="n"/>
-      <c r="I10" s="39" t="n"/>
+      <c r="H10" s="41" t="n"/>
+      <c r="I10" s="41" t="n"/>
       <c r="J10" s="13" t="n"/>
       <c r="K10" s="13" t="n"/>
       <c r="L10" s="13" t="n"/>
       <c r="M10" s="13" t="n"/>
-      <c r="N10" s="39" t="n"/>
+      <c r="N10" s="41" t="n"/>
       <c r="O10" s="13" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="39" t="n"/>
-      <c r="B11" s="39" t="n"/>
-      <c r="C11" s="37" t="inlineStr">
+      <c r="A11" s="41" t="n"/>
+      <c r="B11" s="41" t="n"/>
+      <c r="C11" s="38" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D11" s="39" t="n"/>
-      <c r="E11" s="19" t="n"/>
-      <c r="F11" s="19" t="n"/>
-      <c r="G11" s="19" t="n"/>
-      <c r="H11" s="39" t="n"/>
-      <c r="I11" s="39" t="n"/>
-      <c r="J11" s="19" t="n"/>
-      <c r="K11" s="19" t="n"/>
-      <c r="L11" s="19" t="n"/>
-      <c r="M11" s="21" t="n"/>
-      <c r="N11" s="39" t="n"/>
-      <c r="O11" s="40" t="inlineStr">
+      <c r="D11" s="41" t="n"/>
+      <c r="E11" s="20" t="n"/>
+      <c r="F11" s="20" t="n"/>
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="41" t="n"/>
+      <c r="I11" s="41" t="n"/>
+      <c r="J11" s="20" t="n"/>
+      <c r="K11" s="20" t="n"/>
+      <c r="L11" s="20" t="n"/>
+      <c r="M11" s="22" t="n"/>
+      <c r="N11" s="41" t="n"/>
+      <c r="O11" s="42" t="inlineStr">
         <is>
           <t>Išplautos nuosėdos (mn)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="n"/>
-      <c r="B12" s="39" t="n"/>
-      <c r="C12" s="37" t="inlineStr">
+      <c r="A12" s="41" t="n"/>
+      <c r="B12" s="41" t="n"/>
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="D12" s="39" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="39" t="n"/>
-      <c r="I12" s="39" t="n"/>
-      <c r="J12" s="19" t="n"/>
-      <c r="K12" s="19" t="n"/>
-      <c r="L12" s="19" t="n"/>
-      <c r="M12" s="21" t="n"/>
-      <c r="N12" s="39" t="n"/>
-      <c r="O12" s="40" t="inlineStr">
+      <c r="D12" s="41" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="41" t="n"/>
+      <c r="I12" s="41" t="n"/>
+      <c r="J12" s="20" t="n"/>
+      <c r="K12" s="20" t="n"/>
+      <c r="L12" s="20" t="n"/>
+      <c r="M12" s="22" t="n"/>
+      <c r="N12" s="41" t="n"/>
+      <c r="O12" s="42" t="inlineStr">
         <is>
           <t>Išvalytos ėminių sistemos tuščiasis ėminys (mIt)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="n"/>
-      <c r="B13" s="39" t="n"/>
-      <c r="C13" s="37" t="inlineStr">
+      <c r="A13" s="41" t="n"/>
+      <c r="B13" s="41" t="n"/>
+      <c r="C13" s="38" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D13" s="39" t="n"/>
-      <c r="E13" s="19" t="n"/>
-      <c r="F13" s="19" t="n"/>
-      <c r="G13" s="19" t="n"/>
-      <c r="H13" s="39" t="n"/>
-      <c r="I13" s="39" t="n"/>
-      <c r="J13" s="19" t="n"/>
-      <c r="K13" s="19" t="n"/>
-      <c r="L13" s="19" t="n"/>
-      <c r="M13" s="21" t="n"/>
-      <c r="N13" s="39" t="n"/>
-      <c r="O13" s="40" t="inlineStr">
+      <c r="D13" s="41" t="n"/>
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="41" t="n"/>
+      <c r="I13" s="41" t="n"/>
+      <c r="J13" s="20" t="n"/>
+      <c r="K13" s="20" t="n"/>
+      <c r="L13" s="20" t="n"/>
+      <c r="M13" s="22" t="n"/>
+      <c r="N13" s="41" t="n"/>
+      <c r="O13" s="42" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt1)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="n"/>
-      <c r="B14" s="39" t="n"/>
-      <c r="C14" s="37" t="inlineStr">
+      <c r="A14" s="41" t="n"/>
+      <c r="B14" s="41" t="n"/>
+      <c r="C14" s="38" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="D14" s="39" t="n"/>
-      <c r="E14" s="19" t="n"/>
-      <c r="F14" s="19" t="n"/>
-      <c r="G14" s="19" t="n"/>
-      <c r="H14" s="39" t="n"/>
-      <c r="I14" s="39" t="n"/>
-      <c r="J14" s="19" t="n"/>
-      <c r="K14" s="19" t="n"/>
-      <c r="L14" s="19" t="n"/>
-      <c r="M14" s="21" t="n"/>
-      <c r="N14" s="39" t="n"/>
-      <c r="O14" s="40" t="inlineStr">
+      <c r="D14" s="41" t="n"/>
+      <c r="E14" s="20" t="n"/>
+      <c r="F14" s="20" t="n"/>
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="41" t="n"/>
+      <c r="I14" s="41" t="n"/>
+      <c r="J14" s="20" t="n"/>
+      <c r="K14" s="20" t="n"/>
+      <c r="L14" s="20" t="n"/>
+      <c r="M14" s="22" t="n"/>
+      <c r="N14" s="41" t="n"/>
+      <c r="O14" s="42" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt2)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="39" t="n"/>
-      <c r="B15" s="39" t="n"/>
-      <c r="C15" s="37" t="inlineStr">
+      <c r="A15" s="41" t="n"/>
+      <c r="B15" s="41" t="n"/>
+      <c r="C15" s="38" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D15" s="39" t="n"/>
-      <c r="E15" s="19" t="n"/>
-      <c r="F15" s="19" t="n"/>
-      <c r="G15" s="19" t="n"/>
-      <c r="H15" s="39" t="n"/>
-      <c r="I15" s="39" t="n"/>
-      <c r="J15" s="19" t="n"/>
-      <c r="K15" s="19" t="n"/>
-      <c r="L15" s="19" t="n"/>
-      <c r="M15" s="21" t="n"/>
-      <c r="N15" s="39" t="n"/>
-      <c r="O15" s="40" t="inlineStr">
+      <c r="D15" s="41" t="n"/>
+      <c r="E15" s="20" t="n"/>
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="20" t="n"/>
+      <c r="H15" s="41" t="n"/>
+      <c r="I15" s="41" t="n"/>
+      <c r="J15" s="20" t="n"/>
+      <c r="K15" s="20" t="n"/>
+      <c r="L15" s="20" t="n"/>
+      <c r="M15" s="22" t="n"/>
+      <c r="N15" s="41" t="n"/>
+      <c r="O15" s="42" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt3)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="41" t="n"/>
-      <c r="B16" s="41" t="n"/>
+      <c r="A16" s="43" t="n"/>
+      <c r="B16" s="43" t="n"/>
       <c r="C16" s="13" t="n"/>
-      <c r="D16" s="41" t="n"/>
+      <c r="D16" s="43" t="n"/>
       <c r="E16" s="13" t="n"/>
       <c r="F16" s="13" t="n"/>
       <c r="G16" s="13" t="n"/>
-      <c r="H16" s="41" t="n"/>
-      <c r="I16" s="41" t="n"/>
+      <c r="H16" s="43" t="n"/>
+      <c r="I16" s="43" t="n"/>
       <c r="J16" s="13" t="n"/>
       <c r="K16" s="13" t="n"/>
       <c r="L16" s="13" t="n"/>
-      <c r="M16" s="21" t="n"/>
-      <c r="N16" s="41" t="n"/>
-      <c r="O16" s="40" t="inlineStr">
+      <c r="M16" s="22" t="n"/>
+      <c r="N16" s="43" t="n"/>
+      <c r="O16" s="42" t="inlineStr">
         <is>
           <t>Tuščių indų ir išvalytos ėminių sistemos tuščiojo ėminio svorio pokytis (mItp)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="A2:O2"/>
@@ -2230,6 +2236,7 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="O4:O5"/>
+    <mergeCell ref="A6:A16"/>
     <mergeCell ref="E4:G4"/>
     <mergeCell ref="J4:L4"/>
     <mergeCell ref="B6:B16"/>

--- a/Rezultatai.xlsx
+++ b/Rezultatai.xlsx
@@ -228,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -274,12 +274,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -921,124 +930,166 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="E6" s="20" t="n"/>
-      <c r="F6" s="20" t="n"/>
-      <c r="G6" s="20" t="n"/>
-      <c r="H6" s="20" t="n"/>
-      <c r="I6" s="20" t="n"/>
-      <c r="J6" s="21" t="n">
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="22" t="n">
         <v>0.827</v>
       </c>
-      <c r="K6" s="20" t="n"/>
-      <c r="L6" s="20" t="n"/>
-      <c r="M6" s="20" t="n"/>
-      <c r="N6" s="22" t="n"/>
-      <c r="O6" s="22" t="n"/>
-      <c r="P6" s="22" t="n"/>
-      <c r="Q6" s="22" t="n"/>
-      <c r="R6" s="22" t="n"/>
-      <c r="S6" s="22" t="n"/>
-      <c r="T6" s="22" t="n"/>
-      <c r="U6" s="22" t="n"/>
-      <c r="V6" s="20" t="n"/>
-      <c r="W6" s="22" t="n"/>
-      <c r="X6" s="22" t="n"/>
-      <c r="Y6" s="20" t="n"/>
-      <c r="Z6" s="20" t="n"/>
-      <c r="AA6" s="22" t="n"/>
-      <c r="AB6" s="20" t="n"/>
-      <c r="AC6" s="20" t="n"/>
-      <c r="AD6" s="21" t="n">
+      <c r="K6" s="23" t="n"/>
+      <c r="L6" s="24" t="n">
+        <v>1012</v>
+      </c>
+      <c r="M6" s="24" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="N6" s="25" t="n"/>
+      <c r="O6" s="25" t="n"/>
+      <c r="P6" s="25" t="n"/>
+      <c r="Q6" s="25" t="n"/>
+      <c r="R6" s="25" t="n"/>
+      <c r="S6" s="25" t="n"/>
+      <c r="T6" s="25" t="n"/>
+      <c r="U6" s="25" t="n"/>
+      <c r="V6" s="23" t="n"/>
+      <c r="W6" s="25" t="n"/>
+      <c r="X6" s="25" t="n"/>
+      <c r="Y6" s="23" t="n"/>
+      <c r="Z6" s="23" t="n"/>
+      <c r="AA6" s="25" t="n"/>
+      <c r="AB6" s="23" t="n"/>
+      <c r="AC6" s="23" t="n"/>
+      <c r="AD6" s="22" t="n">
         <v>0.079</v>
       </c>
-      <c r="AE6" s="22" t="n"/>
-      <c r="AF6" s="22" t="n"/>
-      <c r="AG6" s="20" t="n"/>
+      <c r="AE6" s="25" t="n"/>
+      <c r="AF6" s="25" t="n"/>
+      <c r="AG6" s="23" t="n"/>
       <c r="AH6" s="13" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="n"/>
       <c r="B7" s="15" t="n"/>
       <c r="C7" s="15" t="n"/>
-      <c r="D7" s="19" t="n">
-        <v>47</v>
-      </c>
-      <c r="E7" s="20" t="n"/>
-      <c r="F7" s="20" t="n"/>
-      <c r="G7" s="20" t="n"/>
-      <c r="H7" s="20" t="n"/>
-      <c r="I7" s="20" t="n"/>
-      <c r="J7" s="21" t="n">
+      <c r="D7" s="20" t="n">
+        <v>69</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" s="22" t="n">
         <v>0.827</v>
       </c>
-      <c r="K7" s="20" t="n"/>
-      <c r="L7" s="20" t="n"/>
-      <c r="M7" s="20" t="n"/>
-      <c r="N7" s="22" t="n"/>
-      <c r="O7" s="22" t="n"/>
-      <c r="P7" s="22" t="n"/>
-      <c r="Q7" s="22" t="n"/>
-      <c r="R7" s="22" t="n"/>
-      <c r="S7" s="22" t="n"/>
-      <c r="T7" s="22" t="n"/>
+      <c r="K7" s="23" t="n"/>
+      <c r="L7" s="24" t="n">
+        <v>1012</v>
+      </c>
+      <c r="M7" s="24" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="N7" s="25" t="n"/>
+      <c r="O7" s="25" t="n"/>
+      <c r="P7" s="25" t="n"/>
+      <c r="Q7" s="25" t="n"/>
+      <c r="R7" s="25" t="n"/>
+      <c r="S7" s="25" t="n"/>
+      <c r="T7" s="25" t="n"/>
       <c r="U7" s="13" t="n"/>
-      <c r="V7" s="19" t="inlineStr">
-        <is>
-          <t>1,25</t>
-        </is>
-      </c>
-      <c r="W7" s="23">
+      <c r="V7" s="20" t="inlineStr">
+        <is>
+          <t>1,89</t>
+        </is>
+      </c>
+      <c r="W7" s="26">
         <f>V7*V8</f>
         <v/>
       </c>
-      <c r="X7" s="22" t="n"/>
-      <c r="Y7" s="20" t="n"/>
-      <c r="Z7" s="20" t="n"/>
-      <c r="AA7" s="22" t="n"/>
-      <c r="AB7" s="20" t="n"/>
-      <c r="AC7" s="20" t="n"/>
-      <c r="AD7" s="21" t="n">
+      <c r="X7" s="25" t="n"/>
+      <c r="Y7" s="23" t="n"/>
+      <c r="Z7" s="23" t="n"/>
+      <c r="AA7" s="25" t="n"/>
+      <c r="AB7" s="23" t="n"/>
+      <c r="AC7" s="23" t="n"/>
+      <c r="AD7" s="22" t="n">
         <v>0.079</v>
       </c>
-      <c r="AE7" s="22" t="n"/>
-      <c r="AF7" s="22" t="n"/>
+      <c r="AE7" s="25" t="n"/>
+      <c r="AF7" s="25" t="n"/>
       <c r="AH7" s="16" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="n"/>
       <c r="B8" s="15" t="n"/>
       <c r="C8" s="15" t="n"/>
-      <c r="D8" s="19" t="n">
-        <v>78</v>
-      </c>
-      <c r="E8" s="20" t="n"/>
-      <c r="F8" s="20" t="n"/>
-      <c r="G8" s="20" t="n"/>
-      <c r="H8" s="20" t="n"/>
-      <c r="I8" s="20" t="n"/>
-      <c r="J8" s="21" t="n">
+      <c r="D8" s="20" t="n">
+        <v>116</v>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" s="22" t="n">
         <v>0.827</v>
       </c>
-      <c r="K8" s="20" t="n"/>
-      <c r="L8" s="20" t="n"/>
-      <c r="M8" s="20" t="n"/>
-      <c r="N8" s="22" t="n"/>
-      <c r="O8" s="22" t="n"/>
-      <c r="P8" s="22" t="n"/>
-      <c r="Q8" s="22" t="n"/>
-      <c r="R8" s="22" t="n"/>
-      <c r="S8" s="22" t="n"/>
-      <c r="T8" s="22" t="n"/>
+      <c r="K8" s="23" t="n"/>
+      <c r="L8" s="24" t="n">
+        <v>1012</v>
+      </c>
+      <c r="M8" s="24" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="N8" s="25" t="n"/>
+      <c r="O8" s="25" t="n"/>
+      <c r="P8" s="25" t="n"/>
+      <c r="Q8" s="25" t="n"/>
+      <c r="R8" s="25" t="n"/>
+      <c r="S8" s="25" t="n"/>
+      <c r="T8" s="25" t="n"/>
       <c r="U8" s="13" t="n"/>
-      <c r="V8" s="19" t="inlineStr">
-        <is>
-          <t>1,25</t>
+      <c r="V8" s="20" t="inlineStr">
+        <is>
+          <t>1,91</t>
         </is>
       </c>
       <c r="W8" s="13" t="n"/>
@@ -1049,27 +1100,41 @@
       <c r="A9" s="16" t="n"/>
       <c r="B9" s="16" t="n"/>
       <c r="C9" s="16" t="n"/>
-      <c r="D9" s="19" t="n">
-        <v>109</v>
-      </c>
-      <c r="E9" s="20" t="n"/>
-      <c r="F9" s="20" t="n"/>
-      <c r="G9" s="20" t="n"/>
-      <c r="H9" s="20" t="n"/>
-      <c r="I9" s="20" t="n"/>
-      <c r="J9" s="21" t="n">
+      <c r="D9" s="20" t="n">
+        <v>162</v>
+      </c>
+      <c r="E9" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" s="22" t="n">
         <v>0.827</v>
       </c>
-      <c r="K9" s="20" t="n"/>
-      <c r="L9" s="20" t="n"/>
-      <c r="M9" s="20" t="n"/>
-      <c r="N9" s="22" t="n"/>
-      <c r="O9" s="22" t="n"/>
-      <c r="P9" s="22" t="n"/>
-      <c r="Q9" s="22" t="n"/>
-      <c r="R9" s="22" t="n"/>
-      <c r="S9" s="22" t="n"/>
-      <c r="T9" s="22" t="n"/>
+      <c r="K9" s="23" t="n"/>
+      <c r="L9" s="24" t="n">
+        <v>1012</v>
+      </c>
+      <c r="M9" s="24" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="N9" s="25" t="n"/>
+      <c r="O9" s="25" t="n"/>
+      <c r="P9" s="25" t="n"/>
+      <c r="Q9" s="25" t="n"/>
+      <c r="R9" s="25" t="n"/>
+      <c r="S9" s="25" t="n"/>
+      <c r="T9" s="25" t="n"/>
       <c r="U9" s="13" t="n"/>
       <c r="V9" s="13" t="n"/>
       <c r="W9" s="13" t="n"/>
@@ -1102,12 +1167,12 @@
       <c r="A11" s="13" t="n"/>
       <c r="B11" s="13" t="n"/>
       <c r="C11" s="13" t="n"/>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>RPU***</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t>Kai bus 2 linijos, RPU*** yra 2 linijos vidurinis taškas</t>
         </is>
@@ -1441,12 +1506,12 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>Ekopartneris</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>1,25 x 1,25</t>
+          <t>1,89 x 1,91</t>
         </is>
       </c>
       <c r="E6" s="11">
@@ -1595,7 +1660,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>Ekopartneris</t>
         </is>
       </c>
     </row>
@@ -1742,78 +1807,78 @@
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="27" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="D6" s="28" t="n"/>
-      <c r="E6" s="29" t="n"/>
-      <c r="F6" s="29" t="n"/>
-      <c r="G6" s="29" t="n"/>
-      <c r="H6" s="29" t="n"/>
-      <c r="I6" s="29" t="n"/>
-      <c r="J6" s="29" t="n"/>
-      <c r="K6" s="29" t="n"/>
-      <c r="L6" s="30" t="n"/>
-      <c r="M6" s="30" t="n"/>
-      <c r="N6" s="27" t="n"/>
-      <c r="O6" s="27" t="n">
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="n"/>
+      <c r="E6" s="32" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="32" t="n"/>
+      <c r="H6" s="32" t="n"/>
+      <c r="I6" s="32" t="n"/>
+      <c r="J6" s="32" t="n"/>
+      <c r="K6" s="32" t="n"/>
+      <c r="L6" s="33" t="n"/>
+      <c r="M6" s="33" t="n"/>
+      <c r="N6" s="30" t="n"/>
+      <c r="O6" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="P6" s="31" t="inlineStr">
+      <c r="P6" s="34" t="inlineStr">
         <is>
           <t>5 linijos, 1 filtras</t>
         </is>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="35" t="n"/>
-      <c r="B7" s="35" t="n"/>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="28" t="n"/>
-      <c r="E7" s="29" t="n"/>
-      <c r="F7" s="29" t="n"/>
-      <c r="G7" s="29" t="n"/>
-      <c r="H7" s="29" t="n"/>
-      <c r="I7" s="29" t="n"/>
-      <c r="J7" s="29" t="n"/>
-      <c r="K7" s="29" t="n"/>
-      <c r="L7" s="35" t="n"/>
-      <c r="M7" s="35" t="n"/>
-      <c r="N7" s="35" t="n"/>
-      <c r="O7" s="35" t="n"/>
-      <c r="P7" s="31" t="inlineStr">
+      <c r="A7" s="38" t="n"/>
+      <c r="B7" s="38" t="n"/>
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="31" t="n"/>
+      <c r="E7" s="32" t="n"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="32" t="n"/>
+      <c r="H7" s="32" t="n"/>
+      <c r="I7" s="32" t="n"/>
+      <c r="J7" s="32" t="n"/>
+      <c r="K7" s="32" t="n"/>
+      <c r="L7" s="38" t="n"/>
+      <c r="M7" s="38" t="n"/>
+      <c r="N7" s="38" t="n"/>
+      <c r="O7" s="38" t="n"/>
+      <c r="P7" s="34" t="inlineStr">
         <is>
           <t>5 linijos, 2 filtras</t>
         </is>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="36" t="n"/>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="28" t="n"/>
-      <c r="E8" s="29" t="n"/>
-      <c r="F8" s="29" t="n"/>
-      <c r="G8" s="29" t="n"/>
-      <c r="H8" s="29" t="n"/>
-      <c r="I8" s="29" t="n"/>
-      <c r="J8" s="29" t="n"/>
-      <c r="K8" s="29" t="n"/>
-      <c r="L8" s="36" t="n"/>
-      <c r="M8" s="36" t="n"/>
-      <c r="N8" s="36" t="n"/>
-      <c r="O8" s="36" t="n"/>
-      <c r="P8" s="31" t="inlineStr">
+      <c r="A8" s="39" t="n"/>
+      <c r="B8" s="39" t="n"/>
+      <c r="C8" s="39" t="n"/>
+      <c r="D8" s="31" t="n"/>
+      <c r="E8" s="32" t="n"/>
+      <c r="F8" s="32" t="n"/>
+      <c r="G8" s="32" t="n"/>
+      <c r="H8" s="32" t="n"/>
+      <c r="I8" s="32" t="n"/>
+      <c r="J8" s="32" t="n"/>
+      <c r="K8" s="32" t="n"/>
+      <c r="L8" s="39" t="n"/>
+      <c r="M8" s="39" t="n"/>
+      <c r="N8" s="39" t="n"/>
+      <c r="O8" s="39" t="n"/>
+      <c r="P8" s="34" t="inlineStr">
         <is>
           <t>5 linijos, 3 filtras</t>
         </is>
@@ -1970,255 +2035,255 @@
       <c r="O5" s="16" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="n">
+      <c r="A6" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="37" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="C6" s="38" t="n">
+      <c r="B6" s="40" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="C6" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="39" t="n"/>
-      <c r="E6" s="20" t="n"/>
-      <c r="F6" s="20" t="n"/>
-      <c r="G6" s="20" t="n"/>
-      <c r="H6" s="39" t="n"/>
-      <c r="I6" s="39" t="n"/>
-      <c r="J6" s="20" t="n"/>
-      <c r="K6" s="20" t="n"/>
-      <c r="L6" s="20" t="n"/>
-      <c r="M6" s="22" t="n"/>
-      <c r="N6" s="39" t="n"/>
-      <c r="O6" s="40" t="inlineStr">
+      <c r="D6" s="42" t="n"/>
+      <c r="E6" s="23" t="n"/>
+      <c r="F6" s="23" t="n"/>
+      <c r="G6" s="23" t="n"/>
+      <c r="H6" s="42" t="n"/>
+      <c r="I6" s="42" t="n"/>
+      <c r="J6" s="23" t="n"/>
+      <c r="K6" s="23" t="n"/>
+      <c r="L6" s="23" t="n"/>
+      <c r="M6" s="25" t="n"/>
+      <c r="N6" s="42" t="n"/>
+      <c r="O6" s="43" t="inlineStr">
         <is>
           <t>5 linijos, 3 filtrai</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="41" t="n"/>
-      <c r="B7" s="41" t="n"/>
-      <c r="C7" s="38" t="n">
+      <c r="A7" s="44" t="n"/>
+      <c r="B7" s="44" t="n"/>
+      <c r="C7" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="20" t="n"/>
-      <c r="F7" s="20" t="n"/>
-      <c r="G7" s="20" t="n"/>
-      <c r="H7" s="41" t="n"/>
-      <c r="I7" s="41" t="n"/>
-      <c r="J7" s="20" t="n"/>
-      <c r="K7" s="20" t="n"/>
-      <c r="L7" s="20" t="n"/>
-      <c r="M7" s="22" t="n"/>
-      <c r="N7" s="41" t="n"/>
+      <c r="D7" s="44" t="n"/>
+      <c r="E7" s="23" t="n"/>
+      <c r="F7" s="23" t="n"/>
+      <c r="G7" s="23" t="n"/>
+      <c r="H7" s="44" t="n"/>
+      <c r="I7" s="44" t="n"/>
+      <c r="J7" s="23" t="n"/>
+      <c r="K7" s="23" t="n"/>
+      <c r="L7" s="23" t="n"/>
+      <c r="M7" s="25" t="n"/>
+      <c r="N7" s="44" t="n"/>
       <c r="O7" s="13" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="41" t="n"/>
-      <c r="B8" s="41" t="n"/>
-      <c r="C8" s="38" t="n">
+      <c r="A8" s="44" t="n"/>
+      <c r="B8" s="44" t="n"/>
+      <c r="C8" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="41" t="n"/>
-      <c r="E8" s="20" t="n"/>
-      <c r="F8" s="20" t="n"/>
-      <c r="G8" s="20" t="n"/>
-      <c r="H8" s="41" t="n"/>
-      <c r="I8" s="41" t="n"/>
-      <c r="J8" s="20" t="n"/>
-      <c r="K8" s="20" t="n"/>
-      <c r="L8" s="20" t="n"/>
-      <c r="M8" s="22" t="n"/>
-      <c r="N8" s="41" t="n"/>
+      <c r="D8" s="44" t="n"/>
+      <c r="E8" s="23" t="n"/>
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="44" t="n"/>
+      <c r="I8" s="44" t="n"/>
+      <c r="J8" s="23" t="n"/>
+      <c r="K8" s="23" t="n"/>
+      <c r="L8" s="23" t="n"/>
+      <c r="M8" s="25" t="n"/>
+      <c r="N8" s="44" t="n"/>
       <c r="O8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="41" t="n"/>
-      <c r="B9" s="41" t="n"/>
-      <c r="C9" s="38" t="inlineStr">
+      <c r="A9" s="44" t="n"/>
+      <c r="B9" s="44" t="n"/>
+      <c r="C9" s="41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="41" t="n"/>
-      <c r="E9" s="20" t="n"/>
-      <c r="F9" s="20" t="n"/>
-      <c r="G9" s="20" t="n"/>
-      <c r="H9" s="41" t="n"/>
-      <c r="I9" s="41" t="n"/>
-      <c r="J9" s="20" t="n"/>
-      <c r="K9" s="20" t="n"/>
-      <c r="L9" s="20" t="n"/>
-      <c r="M9" s="22" t="n"/>
-      <c r="N9" s="41" t="n"/>
-      <c r="O9" s="42" t="inlineStr">
+      <c r="D9" s="44" t="n"/>
+      <c r="E9" s="23" t="n"/>
+      <c r="F9" s="23" t="n"/>
+      <c r="G9" s="23" t="n"/>
+      <c r="H9" s="44" t="n"/>
+      <c r="I9" s="44" t="n"/>
+      <c r="J9" s="23" t="n"/>
+      <c r="K9" s="23" t="n"/>
+      <c r="L9" s="23" t="n"/>
+      <c r="M9" s="25" t="n"/>
+      <c r="N9" s="44" t="n"/>
+      <c r="O9" s="45" t="inlineStr">
         <is>
           <t>Tuščiasis ėminys (mt)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="41" t="n"/>
-      <c r="B10" s="41" t="n"/>
+      <c r="A10" s="44" t="n"/>
+      <c r="B10" s="44" t="n"/>
       <c r="C10" s="13" t="n"/>
-      <c r="D10" s="41" t="n"/>
+      <c r="D10" s="44" t="n"/>
       <c r="E10" s="13" t="n"/>
       <c r="F10" s="13" t="n"/>
       <c r="G10" s="13" t="n"/>
-      <c r="H10" s="41" t="n"/>
-      <c r="I10" s="41" t="n"/>
+      <c r="H10" s="44" t="n"/>
+      <c r="I10" s="44" t="n"/>
       <c r="J10" s="13" t="n"/>
       <c r="K10" s="13" t="n"/>
       <c r="L10" s="13" t="n"/>
       <c r="M10" s="13" t="n"/>
-      <c r="N10" s="41" t="n"/>
+      <c r="N10" s="44" t="n"/>
       <c r="O10" s="13" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="41" t="n"/>
-      <c r="B11" s="41" t="n"/>
-      <c r="C11" s="38" t="inlineStr">
+      <c r="A11" s="44" t="n"/>
+      <c r="B11" s="44" t="n"/>
+      <c r="C11" s="41" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D11" s="41" t="n"/>
-      <c r="E11" s="20" t="n"/>
-      <c r="F11" s="20" t="n"/>
-      <c r="G11" s="20" t="n"/>
-      <c r="H11" s="41" t="n"/>
-      <c r="I11" s="41" t="n"/>
-      <c r="J11" s="20" t="n"/>
-      <c r="K11" s="20" t="n"/>
-      <c r="L11" s="20" t="n"/>
-      <c r="M11" s="22" t="n"/>
-      <c r="N11" s="41" t="n"/>
-      <c r="O11" s="42" t="inlineStr">
+      <c r="D11" s="44" t="n"/>
+      <c r="E11" s="23" t="n"/>
+      <c r="F11" s="23" t="n"/>
+      <c r="G11" s="23" t="n"/>
+      <c r="H11" s="44" t="n"/>
+      <c r="I11" s="44" t="n"/>
+      <c r="J11" s="23" t="n"/>
+      <c r="K11" s="23" t="n"/>
+      <c r="L11" s="23" t="n"/>
+      <c r="M11" s="25" t="n"/>
+      <c r="N11" s="44" t="n"/>
+      <c r="O11" s="45" t="inlineStr">
         <is>
           <t>Išplautos nuosėdos (mn)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="41" t="n"/>
-      <c r="B12" s="41" t="n"/>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="A12" s="44" t="n"/>
+      <c r="B12" s="44" t="n"/>
+      <c r="C12" s="41" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="D12" s="41" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="41" t="n"/>
-      <c r="I12" s="41" t="n"/>
-      <c r="J12" s="20" t="n"/>
-      <c r="K12" s="20" t="n"/>
-      <c r="L12" s="20" t="n"/>
-      <c r="M12" s="22" t="n"/>
-      <c r="N12" s="41" t="n"/>
-      <c r="O12" s="42" t="inlineStr">
+      <c r="D12" s="44" t="n"/>
+      <c r="E12" s="23" t="n"/>
+      <c r="F12" s="23" t="n"/>
+      <c r="G12" s="23" t="n"/>
+      <c r="H12" s="44" t="n"/>
+      <c r="I12" s="44" t="n"/>
+      <c r="J12" s="23" t="n"/>
+      <c r="K12" s="23" t="n"/>
+      <c r="L12" s="23" t="n"/>
+      <c r="M12" s="25" t="n"/>
+      <c r="N12" s="44" t="n"/>
+      <c r="O12" s="45" t="inlineStr">
         <is>
           <t>Išvalytos ėminių sistemos tuščiasis ėminys (mIt)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="41" t="n"/>
-      <c r="B13" s="41" t="n"/>
-      <c r="C13" s="38" t="inlineStr">
+      <c r="A13" s="44" t="n"/>
+      <c r="B13" s="44" t="n"/>
+      <c r="C13" s="41" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D13" s="41" t="n"/>
-      <c r="E13" s="20" t="n"/>
-      <c r="F13" s="20" t="n"/>
-      <c r="G13" s="20" t="n"/>
-      <c r="H13" s="41" t="n"/>
-      <c r="I13" s="41" t="n"/>
-      <c r="J13" s="20" t="n"/>
-      <c r="K13" s="20" t="n"/>
-      <c r="L13" s="20" t="n"/>
-      <c r="M13" s="22" t="n"/>
-      <c r="N13" s="41" t="n"/>
-      <c r="O13" s="42" t="inlineStr">
+      <c r="D13" s="44" t="n"/>
+      <c r="E13" s="23" t="n"/>
+      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="23" t="n"/>
+      <c r="H13" s="44" t="n"/>
+      <c r="I13" s="44" t="n"/>
+      <c r="J13" s="23" t="n"/>
+      <c r="K13" s="23" t="n"/>
+      <c r="L13" s="23" t="n"/>
+      <c r="M13" s="25" t="n"/>
+      <c r="N13" s="44" t="n"/>
+      <c r="O13" s="45" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt1)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="41" t="n"/>
-      <c r="B14" s="41" t="n"/>
-      <c r="C14" s="38" t="inlineStr">
+      <c r="A14" s="44" t="n"/>
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="41" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="D14" s="41" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
-      <c r="H14" s="41" t="n"/>
-      <c r="I14" s="41" t="n"/>
-      <c r="J14" s="20" t="n"/>
-      <c r="K14" s="20" t="n"/>
-      <c r="L14" s="20" t="n"/>
-      <c r="M14" s="22" t="n"/>
-      <c r="N14" s="41" t="n"/>
-      <c r="O14" s="42" t="inlineStr">
+      <c r="D14" s="44" t="n"/>
+      <c r="E14" s="23" t="n"/>
+      <c r="F14" s="23" t="n"/>
+      <c r="G14" s="23" t="n"/>
+      <c r="H14" s="44" t="n"/>
+      <c r="I14" s="44" t="n"/>
+      <c r="J14" s="23" t="n"/>
+      <c r="K14" s="23" t="n"/>
+      <c r="L14" s="23" t="n"/>
+      <c r="M14" s="25" t="n"/>
+      <c r="N14" s="44" t="n"/>
+      <c r="O14" s="45" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt2)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="41" t="n"/>
-      <c r="B15" s="41" t="n"/>
-      <c r="C15" s="38" t="inlineStr">
+      <c r="A15" s="44" t="n"/>
+      <c r="B15" s="44" t="n"/>
+      <c r="C15" s="41" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D15" s="41" t="n"/>
-      <c r="E15" s="20" t="n"/>
-      <c r="F15" s="20" t="n"/>
-      <c r="G15" s="20" t="n"/>
-      <c r="H15" s="41" t="n"/>
-      <c r="I15" s="41" t="n"/>
-      <c r="J15" s="20" t="n"/>
-      <c r="K15" s="20" t="n"/>
-      <c r="L15" s="20" t="n"/>
-      <c r="M15" s="22" t="n"/>
-      <c r="N15" s="41" t="n"/>
-      <c r="O15" s="42" t="inlineStr">
+      <c r="D15" s="44" t="n"/>
+      <c r="E15" s="23" t="n"/>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="23" t="n"/>
+      <c r="H15" s="44" t="n"/>
+      <c r="I15" s="44" t="n"/>
+      <c r="J15" s="23" t="n"/>
+      <c r="K15" s="23" t="n"/>
+      <c r="L15" s="23" t="n"/>
+      <c r="M15" s="25" t="n"/>
+      <c r="N15" s="44" t="n"/>
+      <c r="O15" s="45" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt3)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="43" t="n"/>
-      <c r="B16" s="43" t="n"/>
+      <c r="A16" s="46" t="n"/>
+      <c r="B16" s="46" t="n"/>
       <c r="C16" s="13" t="n"/>
-      <c r="D16" s="43" t="n"/>
+      <c r="D16" s="46" t="n"/>
       <c r="E16" s="13" t="n"/>
       <c r="F16" s="13" t="n"/>
       <c r="G16" s="13" t="n"/>
-      <c r="H16" s="43" t="n"/>
-      <c r="I16" s="43" t="n"/>
+      <c r="H16" s="46" t="n"/>
+      <c r="I16" s="46" t="n"/>
       <c r="J16" s="13" t="n"/>
       <c r="K16" s="13" t="n"/>
       <c r="L16" s="13" t="n"/>
-      <c r="M16" s="22" t="n"/>
-      <c r="N16" s="43" t="n"/>
-      <c r="O16" s="42" t="inlineStr">
+      <c r="M16" s="25" t="n"/>
+      <c r="N16" s="46" t="n"/>
+      <c r="O16" s="45" t="inlineStr">
         <is>
           <t>Tuščių indų ir išvalytos ėminių sistemos tuščiojo ėminio svorio pokytis (mItp)</t>
         </is>

--- a/Rezultatai.xlsx
+++ b/Rezultatai.xlsx
@@ -22,9 +22,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -228,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -276,6 +277,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -933,163 +946,163 @@
           <t>Ekopartneris</t>
         </is>
       </c>
-      <c r="D6" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="E6" s="21" t="n">
+      <c r="D6" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="E6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="21" t="n">
+      <c r="F6" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="21" t="n">
+      <c r="G6" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="21" t="n">
+      <c r="H6" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="I6" s="21" t="n">
+      <c r="I6" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="J6" s="22" t="n">
+      <c r="J6" s="26" t="n">
         <v>0.827</v>
       </c>
-      <c r="K6" s="23" t="n"/>
-      <c r="L6" s="24" t="n">
+      <c r="K6" s="27" t="n"/>
+      <c r="L6" s="28" t="n">
         <v>1012</v>
       </c>
-      <c r="M6" s="24" t="n">
+      <c r="M6" s="28" t="n">
         <v>-0.25</v>
       </c>
-      <c r="N6" s="25" t="n"/>
-      <c r="O6" s="25" t="n"/>
-      <c r="P6" s="25" t="n"/>
-      <c r="Q6" s="25" t="n"/>
-      <c r="R6" s="25" t="n"/>
-      <c r="S6" s="25" t="n"/>
-      <c r="T6" s="25" t="n"/>
-      <c r="U6" s="25" t="n"/>
-      <c r="V6" s="23" t="n"/>
-      <c r="W6" s="25" t="n"/>
-      <c r="X6" s="25" t="n"/>
-      <c r="Y6" s="23" t="n"/>
-      <c r="Z6" s="23" t="n"/>
-      <c r="AA6" s="25" t="n"/>
-      <c r="AB6" s="23" t="n"/>
-      <c r="AC6" s="23" t="n"/>
-      <c r="AD6" s="22" t="n">
+      <c r="N6" s="29" t="n"/>
+      <c r="O6" s="29" t="n"/>
+      <c r="P6" s="29" t="n"/>
+      <c r="Q6" s="29" t="n"/>
+      <c r="R6" s="29" t="n"/>
+      <c r="S6" s="29" t="n"/>
+      <c r="T6" s="29" t="n"/>
+      <c r="U6" s="29" t="n"/>
+      <c r="V6" s="27" t="n"/>
+      <c r="W6" s="29" t="n"/>
+      <c r="X6" s="29" t="n"/>
+      <c r="Y6" s="27" t="n"/>
+      <c r="Z6" s="27" t="n"/>
+      <c r="AA6" s="29" t="n"/>
+      <c r="AB6" s="27" t="n"/>
+      <c r="AC6" s="27" t="n"/>
+      <c r="AD6" s="26" t="n">
         <v>0.079</v>
       </c>
-      <c r="AE6" s="25" t="n"/>
-      <c r="AF6" s="25" t="n"/>
-      <c r="AG6" s="23" t="n"/>
+      <c r="AE6" s="29" t="n"/>
+      <c r="AF6" s="29" t="n"/>
+      <c r="AG6" s="27" t="n"/>
       <c r="AH6" s="13" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="n"/>
       <c r="B7" s="15" t="n"/>
       <c r="C7" s="15" t="n"/>
-      <c r="D7" s="20" t="n">
-        <v>69</v>
-      </c>
-      <c r="E7" s="21" t="n">
+      <c r="D7" s="24" t="n">
+        <v>58</v>
+      </c>
+      <c r="E7" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="21" t="n">
+      <c r="F7" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="21" t="n">
+      <c r="G7" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="21" t="n">
+      <c r="H7" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="I7" s="21" t="n">
+      <c r="I7" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="J7" s="22" t="n">
+      <c r="J7" s="26" t="n">
         <v>0.827</v>
       </c>
-      <c r="K7" s="23" t="n"/>
-      <c r="L7" s="24" t="n">
+      <c r="K7" s="27" t="n"/>
+      <c r="L7" s="28" t="n">
         <v>1012</v>
       </c>
-      <c r="M7" s="24" t="n">
+      <c r="M7" s="28" t="n">
         <v>-0.25</v>
       </c>
-      <c r="N7" s="25" t="n"/>
-      <c r="O7" s="25" t="n"/>
-      <c r="P7" s="25" t="n"/>
-      <c r="Q7" s="25" t="n"/>
-      <c r="R7" s="25" t="n"/>
-      <c r="S7" s="25" t="n"/>
-      <c r="T7" s="25" t="n"/>
+      <c r="N7" s="29" t="n"/>
+      <c r="O7" s="29" t="n"/>
+      <c r="P7" s="29" t="n"/>
+      <c r="Q7" s="29" t="n"/>
+      <c r="R7" s="29" t="n"/>
+      <c r="S7" s="29" t="n"/>
+      <c r="T7" s="29" t="n"/>
       <c r="U7" s="13" t="n"/>
-      <c r="V7" s="20" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="W7" s="26">
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>1,58</t>
+        </is>
+      </c>
+      <c r="W7" s="30">
         <f>V7*V8</f>
         <v/>
       </c>
-      <c r="X7" s="25" t="n"/>
-      <c r="Y7" s="23" t="n"/>
-      <c r="Z7" s="23" t="n"/>
-      <c r="AA7" s="25" t="n"/>
-      <c r="AB7" s="23" t="n"/>
-      <c r="AC7" s="23" t="n"/>
-      <c r="AD7" s="22" t="n">
+      <c r="X7" s="29" t="n"/>
+      <c r="Y7" s="27" t="n"/>
+      <c r="Z7" s="27" t="n"/>
+      <c r="AA7" s="29" t="n"/>
+      <c r="AB7" s="27" t="n"/>
+      <c r="AC7" s="27" t="n"/>
+      <c r="AD7" s="26" t="n">
         <v>0.079</v>
       </c>
-      <c r="AE7" s="25" t="n"/>
-      <c r="AF7" s="25" t="n"/>
+      <c r="AE7" s="29" t="n"/>
+      <c r="AF7" s="29" t="n"/>
       <c r="AH7" s="16" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="n"/>
       <c r="B8" s="15" t="n"/>
       <c r="C8" s="15" t="n"/>
-      <c r="D8" s="20" t="n">
-        <v>116</v>
-      </c>
-      <c r="E8" s="21" t="n">
+      <c r="D8" s="24" t="n">
+        <v>97</v>
+      </c>
+      <c r="E8" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="21" t="n">
+      <c r="F8" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="21" t="n">
+      <c r="G8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="21" t="n">
+      <c r="H8" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="I8" s="21" t="n">
+      <c r="I8" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="J8" s="22" t="n">
+      <c r="J8" s="26" t="n">
         <v>0.827</v>
       </c>
-      <c r="K8" s="23" t="n"/>
-      <c r="L8" s="24" t="n">
+      <c r="K8" s="27" t="n"/>
+      <c r="L8" s="28" t="n">
         <v>1012</v>
       </c>
-      <c r="M8" s="24" t="n">
+      <c r="M8" s="28" t="n">
         <v>-0.25</v>
       </c>
-      <c r="N8" s="25" t="n"/>
-      <c r="O8" s="25" t="n"/>
-      <c r="P8" s="25" t="n"/>
-      <c r="Q8" s="25" t="n"/>
-      <c r="R8" s="25" t="n"/>
-      <c r="S8" s="25" t="n"/>
-      <c r="T8" s="25" t="n"/>
+      <c r="N8" s="29" t="n"/>
+      <c r="O8" s="29" t="n"/>
+      <c r="P8" s="29" t="n"/>
+      <c r="Q8" s="29" t="n"/>
+      <c r="R8" s="29" t="n"/>
+      <c r="S8" s="29" t="n"/>
+      <c r="T8" s="29" t="n"/>
       <c r="U8" s="13" t="n"/>
-      <c r="V8" s="20" t="inlineStr">
-        <is>
-          <t>1,91</t>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>1,59</t>
         </is>
       </c>
       <c r="W8" s="13" t="n"/>
@@ -1100,41 +1113,41 @@
       <c r="A9" s="16" t="n"/>
       <c r="B9" s="16" t="n"/>
       <c r="C9" s="16" t="n"/>
-      <c r="D9" s="20" t="n">
-        <v>162</v>
-      </c>
-      <c r="E9" s="21" t="n">
+      <c r="D9" s="24" t="n">
+        <v>136</v>
+      </c>
+      <c r="E9" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="21" t="n">
+      <c r="F9" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="21" t="n">
+      <c r="G9" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="21" t="n">
+      <c r="H9" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="I9" s="21" t="n">
+      <c r="I9" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="J9" s="22" t="n">
+      <c r="J9" s="26" t="n">
         <v>0.827</v>
       </c>
-      <c r="K9" s="23" t="n"/>
-      <c r="L9" s="24" t="n">
+      <c r="K9" s="27" t="n"/>
+      <c r="L9" s="28" t="n">
         <v>1012</v>
       </c>
-      <c r="M9" s="24" t="n">
+      <c r="M9" s="28" t="n">
         <v>-0.25</v>
       </c>
-      <c r="N9" s="25" t="n"/>
-      <c r="O9" s="25" t="n"/>
-      <c r="P9" s="25" t="n"/>
-      <c r="Q9" s="25" t="n"/>
-      <c r="R9" s="25" t="n"/>
-      <c r="S9" s="25" t="n"/>
-      <c r="T9" s="25" t="n"/>
+      <c r="N9" s="29" t="n"/>
+      <c r="O9" s="29" t="n"/>
+      <c r="P9" s="29" t="n"/>
+      <c r="Q9" s="29" t="n"/>
+      <c r="R9" s="29" t="n"/>
+      <c r="S9" s="29" t="n"/>
+      <c r="T9" s="29" t="n"/>
       <c r="U9" s="13" t="n"/>
       <c r="V9" s="13" t="n"/>
       <c r="W9" s="13" t="n"/>
@@ -1167,12 +1180,12 @@
       <c r="A11" s="13" t="n"/>
       <c r="B11" s="13" t="n"/>
       <c r="C11" s="13" t="n"/>
-      <c r="D11" s="27" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>RPU***</t>
         </is>
       </c>
-      <c r="E11" s="28" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t>Kai bus 2 linijos, RPU*** yra 2 linijos vidurinis taškas</t>
         </is>
@@ -1511,28 +1524,67 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>1,89 x 1,91</t>
+          <t>1,58 x 1,59</t>
         </is>
       </c>
       <c r="E6" s="11">
         <f>'Greitis'!W7</f>
         <v/>
+      </c>
+      <c r="T6" s="20" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="U6" s="20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V6" s="21" t="n">
+        <v>40.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="n"/>
       <c r="B7" s="15" t="n"/>
       <c r="C7" s="15" t="n"/>
+      <c r="T7" s="20" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="U7" s="20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V7" s="21" t="n">
+        <v>39.8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="n"/>
       <c r="B8" s="15" t="n"/>
       <c r="C8" s="15" t="n"/>
+      <c r="T8" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="U8" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" s="21" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="n"/>
       <c r="B9" s="16" t="n"/>
       <c r="C9" s="16" t="n"/>
+      <c r="T9" s="22">
+        <f>AVERAGE(T6:T8)</f>
+        <v/>
+      </c>
+      <c r="U9" s="22">
+        <f>AVERAGE(U6:U8)</f>
+        <v/>
+      </c>
+      <c r="V9" s="23">
+        <f>AVERAGE(V6:V8)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1807,82 +1859,78 @@
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B6" s="37" t="n">
+      <c r="B6" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>Ekopartneris</t>
         </is>
       </c>
-      <c r="D6" s="31" t="n"/>
-      <c r="E6" s="32" t="n"/>
-      <c r="F6" s="32" t="n"/>
-      <c r="G6" s="32" t="n"/>
-      <c r="H6" s="32" t="n"/>
-      <c r="I6" s="32" t="n"/>
-      <c r="J6" s="32" t="n"/>
-      <c r="K6" s="32" t="n"/>
-      <c r="L6" s="33" t="n"/>
-      <c r="M6" s="33" t="n"/>
-      <c r="N6" s="30" t="n"/>
-      <c r="O6" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="P6" s="34" t="inlineStr">
+      <c r="D6" s="35" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="36" t="n"/>
+      <c r="J6" s="36" t="n"/>
+      <c r="K6" s="36" t="n"/>
+      <c r="L6" s="37" t="n"/>
+      <c r="M6" s="37" t="n"/>
+      <c r="N6" s="34" t="n"/>
+      <c r="O6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="38" t="inlineStr">
         <is>
           <t>5 linijos, 1 filtras</t>
         </is>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="38" t="n"/>
-      <c r="B7" s="38" t="n"/>
-      <c r="C7" s="38" t="n"/>
-      <c r="D7" s="31" t="n"/>
-      <c r="E7" s="32" t="n"/>
-      <c r="F7" s="32" t="n"/>
-      <c r="G7" s="32" t="n"/>
-      <c r="H7" s="32" t="n"/>
-      <c r="I7" s="32" t="n"/>
-      <c r="J7" s="32" t="n"/>
-      <c r="K7" s="32" t="n"/>
-      <c r="L7" s="38" t="n"/>
-      <c r="M7" s="38" t="n"/>
-      <c r="N7" s="38" t="n"/>
-      <c r="O7" s="38" t="n"/>
-      <c r="P7" s="34" t="inlineStr">
+      <c r="A7" s="42" t="n"/>
+      <c r="B7" s="42" t="n"/>
+      <c r="C7" s="42" t="n"/>
+      <c r="D7" s="35" t="n"/>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="n"/>
+      <c r="G7" s="36" t="n"/>
+      <c r="H7" s="36" t="n"/>
+      <c r="I7" s="36" t="n"/>
+      <c r="J7" s="36" t="n"/>
+      <c r="K7" s="36" t="n"/>
+      <c r="L7" s="42" t="n"/>
+      <c r="M7" s="42" t="n"/>
+      <c r="N7" s="42" t="n"/>
+      <c r="O7" s="42" t="n"/>
+      <c r="P7" s="38" t="inlineStr">
         <is>
           <t>5 linijos, 2 filtras</t>
         </is>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="39" t="n"/>
-      <c r="B8" s="39" t="n"/>
-      <c r="C8" s="39" t="n"/>
-      <c r="D8" s="31" t="n"/>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="32" t="n"/>
-      <c r="G8" s="32" t="n"/>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="32" t="n"/>
-      <c r="J8" s="32" t="n"/>
-      <c r="K8" s="32" t="n"/>
-      <c r="L8" s="39" t="n"/>
-      <c r="M8" s="39" t="n"/>
-      <c r="N8" s="39" t="n"/>
-      <c r="O8" s="39" t="n"/>
-      <c r="P8" s="34" t="inlineStr">
-        <is>
-          <t>5 linijos, 3 filtras</t>
-        </is>
-      </c>
+      <c r="A8" s="43" t="n"/>
+      <c r="B8" s="43" t="n"/>
+      <c r="C8" s="43" t="n"/>
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="36" t="n"/>
+      <c r="I8" s="36" t="n"/>
+      <c r="J8" s="36" t="n"/>
+      <c r="K8" s="36" t="n"/>
+      <c r="L8" s="43" t="n"/>
+      <c r="M8" s="43" t="n"/>
+      <c r="N8" s="43" t="n"/>
+      <c r="O8" s="43" t="n"/>
+      <c r="P8" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2035,255 +2083,253 @@
       <c r="O5" s="16" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="n">
+      <c r="A6" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>Ekopartneris</t>
         </is>
       </c>
-      <c r="C6" s="41" t="n">
+      <c r="C6" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="42" t="n"/>
-      <c r="E6" s="23" t="n"/>
-      <c r="F6" s="23" t="n"/>
-      <c r="G6" s="23" t="n"/>
-      <c r="H6" s="42" t="n"/>
-      <c r="I6" s="42" t="n"/>
-      <c r="J6" s="23" t="n"/>
-      <c r="K6" s="23" t="n"/>
-      <c r="L6" s="23" t="n"/>
-      <c r="M6" s="25" t="n"/>
-      <c r="N6" s="42" t="n"/>
-      <c r="O6" s="43" t="inlineStr">
-        <is>
-          <t>5 linijos, 3 filtrai</t>
+      <c r="D6" s="46" t="n"/>
+      <c r="E6" s="27" t="n"/>
+      <c r="F6" s="27" t="n"/>
+      <c r="G6" s="27" t="n"/>
+      <c r="H6" s="46" t="n"/>
+      <c r="I6" s="46" t="n"/>
+      <c r="J6" s="27" t="n"/>
+      <c r="K6" s="27" t="n"/>
+      <c r="L6" s="27" t="n"/>
+      <c r="M6" s="29" t="n"/>
+      <c r="N6" s="46" t="n"/>
+      <c r="O6" s="47" t="inlineStr">
+        <is>
+          <t>5 linijos, 2 filtrai</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="44" t="n"/>
-      <c r="B7" s="44" t="n"/>
-      <c r="C7" s="41" t="n">
+      <c r="A7" s="48" t="n"/>
+      <c r="B7" s="48" t="n"/>
+      <c r="C7" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="44" t="n"/>
-      <c r="E7" s="23" t="n"/>
-      <c r="F7" s="23" t="n"/>
-      <c r="G7" s="23" t="n"/>
-      <c r="H7" s="44" t="n"/>
-      <c r="I7" s="44" t="n"/>
-      <c r="J7" s="23" t="n"/>
-      <c r="K7" s="23" t="n"/>
-      <c r="L7" s="23" t="n"/>
-      <c r="M7" s="25" t="n"/>
-      <c r="N7" s="44" t="n"/>
+      <c r="D7" s="48" t="n"/>
+      <c r="E7" s="27" t="n"/>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="27" t="n"/>
+      <c r="H7" s="48" t="n"/>
+      <c r="I7" s="48" t="n"/>
+      <c r="J7" s="27" t="n"/>
+      <c r="K7" s="27" t="n"/>
+      <c r="L7" s="27" t="n"/>
+      <c r="M7" s="29" t="n"/>
+      <c r="N7" s="48" t="n"/>
       <c r="O7" s="13" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="44" t="n"/>
-      <c r="B8" s="44" t="n"/>
-      <c r="C8" s="41" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" s="44" t="n"/>
-      <c r="E8" s="23" t="n"/>
-      <c r="F8" s="23" t="n"/>
-      <c r="G8" s="23" t="n"/>
-      <c r="H8" s="44" t="n"/>
-      <c r="I8" s="44" t="n"/>
-      <c r="J8" s="23" t="n"/>
-      <c r="K8" s="23" t="n"/>
-      <c r="L8" s="23" t="n"/>
-      <c r="M8" s="25" t="n"/>
-      <c r="N8" s="44" t="n"/>
+      <c r="A8" s="48" t="n"/>
+      <c r="B8" s="48" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="48" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="13" t="n"/>
+      <c r="H8" s="48" t="n"/>
+      <c r="I8" s="48" t="n"/>
+      <c r="J8" s="13" t="n"/>
+      <c r="K8" s="13" t="n"/>
+      <c r="L8" s="13" t="n"/>
+      <c r="M8" s="29" t="n"/>
+      <c r="N8" s="48" t="n"/>
       <c r="O8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="44" t="n"/>
-      <c r="B9" s="44" t="n"/>
-      <c r="C9" s="41" t="inlineStr">
+      <c r="A9" s="48" t="n"/>
+      <c r="B9" s="48" t="n"/>
+      <c r="C9" s="45" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="44" t="n"/>
-      <c r="E9" s="23" t="n"/>
-      <c r="F9" s="23" t="n"/>
-      <c r="G9" s="23" t="n"/>
-      <c r="H9" s="44" t="n"/>
-      <c r="I9" s="44" t="n"/>
-      <c r="J9" s="23" t="n"/>
-      <c r="K9" s="23" t="n"/>
-      <c r="L9" s="23" t="n"/>
-      <c r="M9" s="25" t="n"/>
-      <c r="N9" s="44" t="n"/>
-      <c r="O9" s="45" t="inlineStr">
+      <c r="D9" s="48" t="n"/>
+      <c r="E9" s="27" t="n"/>
+      <c r="F9" s="27" t="n"/>
+      <c r="G9" s="27" t="n"/>
+      <c r="H9" s="48" t="n"/>
+      <c r="I9" s="48" t="n"/>
+      <c r="J9" s="27" t="n"/>
+      <c r="K9" s="27" t="n"/>
+      <c r="L9" s="27" t="n"/>
+      <c r="M9" s="29" t="n"/>
+      <c r="N9" s="48" t="n"/>
+      <c r="O9" s="49" t="inlineStr">
         <is>
           <t>Tuščiasis ėminys (mt)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="44" t="n"/>
-      <c r="B10" s="44" t="n"/>
+      <c r="A10" s="48" t="n"/>
+      <c r="B10" s="48" t="n"/>
       <c r="C10" s="13" t="n"/>
-      <c r="D10" s="44" t="n"/>
+      <c r="D10" s="48" t="n"/>
       <c r="E10" s="13" t="n"/>
       <c r="F10" s="13" t="n"/>
       <c r="G10" s="13" t="n"/>
-      <c r="H10" s="44" t="n"/>
-      <c r="I10" s="44" t="n"/>
+      <c r="H10" s="48" t="n"/>
+      <c r="I10" s="48" t="n"/>
       <c r="J10" s="13" t="n"/>
       <c r="K10" s="13" t="n"/>
       <c r="L10" s="13" t="n"/>
       <c r="M10" s="13" t="n"/>
-      <c r="N10" s="44" t="n"/>
+      <c r="N10" s="48" t="n"/>
       <c r="O10" s="13" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="44" t="n"/>
-      <c r="B11" s="44" t="n"/>
-      <c r="C11" s="41" t="inlineStr">
+      <c r="A11" s="48" t="n"/>
+      <c r="B11" s="48" t="n"/>
+      <c r="C11" s="45" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D11" s="44" t="n"/>
-      <c r="E11" s="23" t="n"/>
-      <c r="F11" s="23" t="n"/>
-      <c r="G11" s="23" t="n"/>
-      <c r="H11" s="44" t="n"/>
-      <c r="I11" s="44" t="n"/>
-      <c r="J11" s="23" t="n"/>
-      <c r="K11" s="23" t="n"/>
-      <c r="L11" s="23" t="n"/>
-      <c r="M11" s="25" t="n"/>
-      <c r="N11" s="44" t="n"/>
-      <c r="O11" s="45" t="inlineStr">
+      <c r="D11" s="48" t="n"/>
+      <c r="E11" s="27" t="n"/>
+      <c r="F11" s="27" t="n"/>
+      <c r="G11" s="27" t="n"/>
+      <c r="H11" s="48" t="n"/>
+      <c r="I11" s="48" t="n"/>
+      <c r="J11" s="27" t="n"/>
+      <c r="K11" s="27" t="n"/>
+      <c r="L11" s="27" t="n"/>
+      <c r="M11" s="29" t="n"/>
+      <c r="N11" s="48" t="n"/>
+      <c r="O11" s="49" t="inlineStr">
         <is>
           <t>Išplautos nuosėdos (mn)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="44" t="n"/>
-      <c r="B12" s="44" t="n"/>
-      <c r="C12" s="41" t="inlineStr">
+      <c r="A12" s="48" t="n"/>
+      <c r="B12" s="48" t="n"/>
+      <c r="C12" s="45" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="D12" s="44" t="n"/>
-      <c r="E12" s="23" t="n"/>
-      <c r="F12" s="23" t="n"/>
-      <c r="G12" s="23" t="n"/>
-      <c r="H12" s="44" t="n"/>
-      <c r="I12" s="44" t="n"/>
-      <c r="J12" s="23" t="n"/>
-      <c r="K12" s="23" t="n"/>
-      <c r="L12" s="23" t="n"/>
-      <c r="M12" s="25" t="n"/>
-      <c r="N12" s="44" t="n"/>
-      <c r="O12" s="45" t="inlineStr">
+      <c r="D12" s="48" t="n"/>
+      <c r="E12" s="27" t="n"/>
+      <c r="F12" s="27" t="n"/>
+      <c r="G12" s="27" t="n"/>
+      <c r="H12" s="48" t="n"/>
+      <c r="I12" s="48" t="n"/>
+      <c r="J12" s="27" t="n"/>
+      <c r="K12" s="27" t="n"/>
+      <c r="L12" s="27" t="n"/>
+      <c r="M12" s="29" t="n"/>
+      <c r="N12" s="48" t="n"/>
+      <c r="O12" s="49" t="inlineStr">
         <is>
           <t>Išvalytos ėminių sistemos tuščiasis ėminys (mIt)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="44" t="n"/>
-      <c r="B13" s="44" t="n"/>
-      <c r="C13" s="41" t="inlineStr">
+      <c r="A13" s="48" t="n"/>
+      <c r="B13" s="48" t="n"/>
+      <c r="C13" s="45" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D13" s="44" t="n"/>
-      <c r="E13" s="23" t="n"/>
-      <c r="F13" s="23" t="n"/>
-      <c r="G13" s="23" t="n"/>
-      <c r="H13" s="44" t="n"/>
-      <c r="I13" s="44" t="n"/>
-      <c r="J13" s="23" t="n"/>
-      <c r="K13" s="23" t="n"/>
-      <c r="L13" s="23" t="n"/>
-      <c r="M13" s="25" t="n"/>
-      <c r="N13" s="44" t="n"/>
-      <c r="O13" s="45" t="inlineStr">
+      <c r="D13" s="48" t="n"/>
+      <c r="E13" s="27" t="n"/>
+      <c r="F13" s="27" t="n"/>
+      <c r="G13" s="27" t="n"/>
+      <c r="H13" s="48" t="n"/>
+      <c r="I13" s="48" t="n"/>
+      <c r="J13" s="27" t="n"/>
+      <c r="K13" s="27" t="n"/>
+      <c r="L13" s="27" t="n"/>
+      <c r="M13" s="29" t="n"/>
+      <c r="N13" s="48" t="n"/>
+      <c r="O13" s="49" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt1)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="44" t="n"/>
-      <c r="B14" s="44" t="n"/>
-      <c r="C14" s="41" t="inlineStr">
+      <c r="A14" s="48" t="n"/>
+      <c r="B14" s="48" t="n"/>
+      <c r="C14" s="45" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="D14" s="44" t="n"/>
-      <c r="E14" s="23" t="n"/>
-      <c r="F14" s="23" t="n"/>
-      <c r="G14" s="23" t="n"/>
-      <c r="H14" s="44" t="n"/>
-      <c r="I14" s="44" t="n"/>
-      <c r="J14" s="23" t="n"/>
-      <c r="K14" s="23" t="n"/>
-      <c r="L14" s="23" t="n"/>
-      <c r="M14" s="25" t="n"/>
-      <c r="N14" s="44" t="n"/>
-      <c r="O14" s="45" t="inlineStr">
+      <c r="D14" s="48" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="27" t="n"/>
+      <c r="H14" s="48" t="n"/>
+      <c r="I14" s="48" t="n"/>
+      <c r="J14" s="27" t="n"/>
+      <c r="K14" s="27" t="n"/>
+      <c r="L14" s="27" t="n"/>
+      <c r="M14" s="29" t="n"/>
+      <c r="N14" s="48" t="n"/>
+      <c r="O14" s="49" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt2)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="44" t="n"/>
-      <c r="B15" s="44" t="n"/>
-      <c r="C15" s="41" t="inlineStr">
+      <c r="A15" s="48" t="n"/>
+      <c r="B15" s="48" t="n"/>
+      <c r="C15" s="45" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D15" s="44" t="n"/>
-      <c r="E15" s="23" t="n"/>
-      <c r="F15" s="23" t="n"/>
-      <c r="G15" s="23" t="n"/>
-      <c r="H15" s="44" t="n"/>
-      <c r="I15" s="44" t="n"/>
-      <c r="J15" s="23" t="n"/>
-      <c r="K15" s="23" t="n"/>
-      <c r="L15" s="23" t="n"/>
-      <c r="M15" s="25" t="n"/>
-      <c r="N15" s="44" t="n"/>
-      <c r="O15" s="45" t="inlineStr">
+      <c r="D15" s="48" t="n"/>
+      <c r="E15" s="27" t="n"/>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="27" t="n"/>
+      <c r="H15" s="48" t="n"/>
+      <c r="I15" s="48" t="n"/>
+      <c r="J15" s="27" t="n"/>
+      <c r="K15" s="27" t="n"/>
+      <c r="L15" s="27" t="n"/>
+      <c r="M15" s="29" t="n"/>
+      <c r="N15" s="48" t="n"/>
+      <c r="O15" s="49" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt3)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="46" t="n"/>
-      <c r="B16" s="46" t="n"/>
+      <c r="A16" s="50" t="n"/>
+      <c r="B16" s="50" t="n"/>
       <c r="C16" s="13" t="n"/>
-      <c r="D16" s="46" t="n"/>
+      <c r="D16" s="50" t="n"/>
       <c r="E16" s="13" t="n"/>
       <c r="F16" s="13" t="n"/>
       <c r="G16" s="13" t="n"/>
-      <c r="H16" s="46" t="n"/>
-      <c r="I16" s="46" t="n"/>
+      <c r="H16" s="50" t="n"/>
+      <c r="I16" s="50" t="n"/>
       <c r="J16" s="13" t="n"/>
       <c r="K16" s="13" t="n"/>
       <c r="L16" s="13" t="n"/>
-      <c r="M16" s="25" t="n"/>
-      <c r="N16" s="46" t="n"/>
-      <c r="O16" s="45" t="inlineStr">
+      <c r="M16" s="29" t="n"/>
+      <c r="N16" s="50" t="n"/>
+      <c r="O16" s="49" t="inlineStr">
         <is>
           <t>Tuščių indų ir išvalytos ėminių sistemos tuščiojo ėminio svorio pokytis (mItp)</t>
         </is>

--- a/Rezultatai.xlsx
+++ b/Rezultatai.xlsx
@@ -1884,7 +1884,7 @@
       <c r="M6" s="37" t="n"/>
       <c r="N6" s="34" t="n"/>
       <c r="O6" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P6" s="38" t="inlineStr">
         <is>
@@ -1930,7 +1930,11 @@
       <c r="M8" s="43" t="n"/>
       <c r="N8" s="43" t="n"/>
       <c r="O8" s="43" t="n"/>
-      <c r="P8" s="35" t="n"/>
+      <c r="P8" s="38" t="inlineStr">
+        <is>
+          <t>5 linijos, 3 filtras</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2107,7 +2111,7 @@
       <c r="N6" s="46" t="n"/>
       <c r="O6" s="47" t="inlineStr">
         <is>
-          <t>5 linijos, 2 filtrai</t>
+          <t>5 linijos, 3 filtrai</t>
         </is>
       </c>
     </row>
@@ -2133,16 +2137,18 @@
     <row r="8">
       <c r="A8" s="48" t="n"/>
       <c r="B8" s="48" t="n"/>
-      <c r="C8" s="13" t="n"/>
+      <c r="C8" s="45" t="n">
+        <v>3</v>
+      </c>
       <c r="D8" s="48" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="13" t="n"/>
+      <c r="E8" s="27" t="n"/>
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="27" t="n"/>
       <c r="H8" s="48" t="n"/>
       <c r="I8" s="48" t="n"/>
-      <c r="J8" s="13" t="n"/>
-      <c r="K8" s="13" t="n"/>
-      <c r="L8" s="13" t="n"/>
+      <c r="J8" s="27" t="n"/>
+      <c r="K8" s="27" t="n"/>
+      <c r="L8" s="27" t="n"/>
       <c r="M8" s="29" t="n"/>
       <c r="N8" s="48" t="n"/>
       <c r="O8" s="13" t="n"/>

--- a/Rezultatai.xlsx
+++ b/Rezultatai.xlsx
@@ -1336,7 +1336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AA9"/>
+  <dimension ref="A2:Y41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1364,8 +1364,6 @@
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -1494,17 +1492,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>Srauto greitis ortakyje wor (m/s)</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
           <t>Izokinetiškumas (0,95-1,15)</t>
-        </is>
-      </c>
-      <c r="AA5" s="3" t="inlineStr">
-        <is>
-          <t>Pito vamzdelio koeficientas, K</t>
         </is>
       </c>
     </row>
@@ -1539,6 +1527,9 @@
       </c>
       <c r="V6" s="21" t="n">
         <v>40.2</v>
+      </c>
+      <c r="X6" s="19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1554,6 +1545,9 @@
       <c r="V7" s="21" t="n">
         <v>39.8</v>
       </c>
+      <c r="X7" s="19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="n"/>
@@ -1567,6 +1561,9 @@
       </c>
       <c r="V8" s="21" t="n">
         <v>40</v>
+      </c>
+      <c r="X8" s="19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1584,6 +1581,89 @@
       <c r="V9" s="23">
         <f>AVERAGE(V6:V8)</f>
         <v/>
+      </c>
+      <c r="X9" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="X14" s="19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="X15" s="19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="X16" s="19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="X17" s="19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="X22" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="X23" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="X24" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="X25" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="X30" s="19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="X31" s="19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="X32" s="19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="X33" s="19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="X38" s="19" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="X39" s="19" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="X40" s="19" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="X41" s="19" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Rezultatai.xlsx
+++ b/Rezultatai.xlsx
@@ -45,7 +45,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -68,6 +68,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFF00"/>
         <bgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000B0F0"/>
+        <bgColor rgb="0000B0F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -230,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -369,10 +375,45 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -391,11 +432,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1448,7 +1484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:Y121"/>
+  <dimension ref="A2:Y123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1609,7 +1645,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="54" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
@@ -1617,1340 +1653,2472 @@
       <c r="B6" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="55" t="inlineStr">
         <is>
           <t>Ekopartneris</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="56" t="inlineStr">
         <is>
           <t>1,58 x 1,59</t>
         </is>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="57">
         <f>'Greitis'!W7</f>
         <v/>
       </c>
-      <c r="J6" s="31" t="n">
+      <c r="F6" s="34" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="34" t="n"/>
+      <c r="I6" s="34" t="n"/>
+      <c r="J6" s="58" t="n">
         <v>111</v>
       </c>
-      <c r="K6" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N6" s="1" t="n">
+      <c r="K6" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="36" t="n"/>
+      <c r="M6" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" s="40" t="n">
         <v>112</v>
       </c>
-      <c r="O6" s="31" t="n">
+      <c r="O6" s="58" t="n">
         <v>113</v>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="P6" s="34" t="n"/>
+      <c r="Q6" s="34" t="n"/>
+      <c r="R6" s="59" t="n"/>
+      <c r="S6" s="59" t="inlineStr">
         <is>
           <t>1 filtras, 1 linija</t>
         </is>
       </c>
-      <c r="T6" s="27" t="n">
+      <c r="T6" s="60" t="n">
         <v>10.02</v>
       </c>
-      <c r="U6" s="27" t="n">
+      <c r="U6" s="60" t="n">
         <v>4.1</v>
       </c>
-      <c r="V6" s="28" t="n">
+      <c r="V6" s="58" t="n">
         <v>40.2</v>
       </c>
-      <c r="X6" s="25" t="n">
-        <v>1</v>
-      </c>
+      <c r="X6" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="34" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="17" t="n"/>
       <c r="B7" s="17" t="n"/>
       <c r="C7" s="18" t="n"/>
-      <c r="J7" s="31" t="n">
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="36" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="34" t="n"/>
+      <c r="J7" s="58" t="n">
         <v>111</v>
       </c>
-      <c r="K7" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" s="1" t="n">
+      <c r="K7" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="36" t="n"/>
+      <c r="M7" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" s="40" t="n">
         <v>112</v>
       </c>
-      <c r="O7" s="31" t="n">
+      <c r="O7" s="58" t="n">
         <v>113</v>
       </c>
-      <c r="T7" s="27" t="n">
+      <c r="P7" s="34" t="n"/>
+      <c r="Q7" s="34" t="n"/>
+      <c r="R7" s="17" t="n"/>
+      <c r="S7" s="17" t="n"/>
+      <c r="T7" s="60" t="n">
         <v>9.98</v>
       </c>
-      <c r="U7" s="27" t="n">
+      <c r="U7" s="60" t="n">
         <v>3.9</v>
       </c>
-      <c r="V7" s="28" t="n">
+      <c r="V7" s="58" t="n">
         <v>39.8</v>
       </c>
-      <c r="X7" s="25" t="n">
-        <v>1</v>
-      </c>
+      <c r="X7" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="34" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="17" t="n"/>
       <c r="B8" s="17" t="n"/>
       <c r="C8" s="18" t="n"/>
-      <c r="J8" s="31" t="n">
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="34" t="n"/>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="34" t="n"/>
+      <c r="I8" s="34" t="n"/>
+      <c r="J8" s="58" t="n">
         <v>111</v>
       </c>
-      <c r="K8" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N8" s="1" t="n">
+      <c r="K8" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="36" t="n"/>
+      <c r="M8" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N8" s="40" t="n">
         <v>112</v>
       </c>
-      <c r="O8" s="31" t="n">
+      <c r="O8" s="58" t="n">
         <v>113</v>
       </c>
-      <c r="T8" s="27" t="n">
+      <c r="P8" s="34" t="n"/>
+      <c r="Q8" s="34" t="n"/>
+      <c r="R8" s="17" t="n"/>
+      <c r="S8" s="17" t="n"/>
+      <c r="T8" s="60" t="n">
         <v>10</v>
       </c>
-      <c r="U8" s="27" t="n">
+      <c r="U8" s="60" t="n">
         <v>4</v>
       </c>
-      <c r="V8" s="28" t="n">
+      <c r="V8" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="X8" s="25" t="n">
-        <v>1</v>
-      </c>
+      <c r="X8" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="34" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="19" t="n"/>
       <c r="B9" s="19" t="n"/>
       <c r="C9" s="20" t="n"/>
-      <c r="J9" s="31" t="n">
+      <c r="D9" s="19" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="34" t="n"/>
+      <c r="J9" s="58" t="n">
         <v>111</v>
       </c>
-      <c r="K9" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" s="1" t="n">
+      <c r="K9" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="36" t="n"/>
+      <c r="M9" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" s="40" t="n">
         <v>112</v>
       </c>
-      <c r="O9" s="31" t="n">
+      <c r="O9" s="58" t="n">
         <v>113</v>
       </c>
-      <c r="T9" s="29">
+      <c r="P9" s="34" t="n"/>
+      <c r="Q9" s="34" t="n"/>
+      <c r="R9" s="19" t="n"/>
+      <c r="S9" s="19" t="n"/>
+      <c r="T9" s="66">
         <f>AVERAGE(T6:T8)</f>
         <v/>
       </c>
-      <c r="U9" s="29">
+      <c r="U9" s="66">
         <f>AVERAGE(U6:U8)</f>
         <v/>
       </c>
-      <c r="V9" s="30">
+      <c r="V9" s="67">
         <f>AVERAGE(V6:V8)</f>
         <v/>
       </c>
-      <c r="X9" s="25" t="n">
-        <v>1</v>
+      <c r="X9" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="34" t="n"/>
+    </row>
+    <row r="10">
+      <c r="L10" s="36" t="n"/>
+      <c r="M10" s="36" t="n"/>
+      <c r="N10" s="36" t="n"/>
+      <c r="T10" s="12" t="inlineStr">
+        <is>
+          <t>O2iš, (%) vidurkis</t>
+        </is>
+      </c>
+      <c r="U10" s="12" t="inlineStr">
+        <is>
+          <t>CO2iš, (%) vidurkis</t>
+        </is>
+      </c>
+      <c r="V10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> tor vidurkis, °C</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vm, m3</t>
+        </is>
+      </c>
+      <c r="M11" s="12" t="inlineStr">
+        <is>
+          <t>Suma t, min</t>
+        </is>
+      </c>
+      <c r="N11" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis Vo (l/min)</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="J14" s="31" t="n">
+      <c r="A14" s="68" t="n"/>
+      <c r="B14" s="68" t="n"/>
+      <c r="C14" s="68" t="n"/>
+      <c r="D14" s="69" t="n"/>
+      <c r="E14" s="69" t="n"/>
+      <c r="F14" s="34" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="34" t="n"/>
+      <c r="I14" s="34" t="n"/>
+      <c r="J14" s="58" t="n">
         <v>121</v>
       </c>
-      <c r="K14" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N14" s="1" t="n">
+      <c r="K14" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="36" t="n"/>
+      <c r="M14" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" s="40" t="n">
         <v>122</v>
       </c>
-      <c r="O14" s="31" t="n">
+      <c r="O14" s="58" t="n">
         <v>123</v>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="P14" s="34" t="n"/>
+      <c r="Q14" s="34" t="n"/>
+      <c r="R14" s="69" t="n"/>
+      <c r="S14" s="59" t="inlineStr">
         <is>
           <t>1 filtras, 2 linija</t>
         </is>
       </c>
-      <c r="X14" s="25" t="n">
+      <c r="X14" s="61" t="n">
         <v>2</v>
       </c>
+      <c r="Y14" s="34" t="n"/>
     </row>
     <row r="15">
-      <c r="J15" s="31" t="n">
+      <c r="C15" s="68" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="34" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="34" t="n"/>
+      <c r="I15" s="34" t="n"/>
+      <c r="J15" s="58" t="n">
         <v>121</v>
       </c>
-      <c r="K15" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N15" s="1" t="n">
+      <c r="K15" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="36" t="n"/>
+      <c r="M15" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N15" s="40" t="n">
         <v>122</v>
       </c>
-      <c r="O15" s="31" t="n">
+      <c r="O15" s="58" t="n">
         <v>123</v>
       </c>
-      <c r="X15" s="25" t="n">
+      <c r="P15" s="34" t="n"/>
+      <c r="Q15" s="34" t="n"/>
+      <c r="R15" s="17" t="n"/>
+      <c r="S15" s="17" t="n"/>
+      <c r="X15" s="61" t="n">
         <v>2</v>
       </c>
+      <c r="Y15" s="34" t="n"/>
     </row>
     <row r="16">
-      <c r="J16" s="31" t="n">
+      <c r="C16" s="68" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="34" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="34" t="n"/>
+      <c r="I16" s="34" t="n"/>
+      <c r="J16" s="58" t="n">
         <v>121</v>
       </c>
-      <c r="K16" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N16" s="1" t="n">
+      <c r="K16" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="36" t="n"/>
+      <c r="M16" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" s="40" t="n">
         <v>122</v>
       </c>
-      <c r="O16" s="31" t="n">
+      <c r="O16" s="58" t="n">
         <v>123</v>
       </c>
-      <c r="X16" s="25" t="n">
+      <c r="P16" s="34" t="n"/>
+      <c r="Q16" s="34" t="n"/>
+      <c r="R16" s="17" t="n"/>
+      <c r="S16" s="17" t="n"/>
+      <c r="X16" s="61" t="n">
         <v>2</v>
       </c>
+      <c r="Y16" s="34" t="n"/>
     </row>
     <row r="17">
-      <c r="J17" s="31" t="n">
+      <c r="C17" s="68" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="34" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="34" t="n"/>
+      <c r="I17" s="34" t="n"/>
+      <c r="J17" s="58" t="n">
         <v>121</v>
       </c>
-      <c r="K17" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N17" s="1" t="n">
+      <c r="K17" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="36" t="n"/>
+      <c r="M17" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" s="40" t="n">
         <v>122</v>
       </c>
-      <c r="O17" s="31" t="n">
+      <c r="O17" s="58" t="n">
         <v>123</v>
       </c>
-      <c r="X17" s="25" t="n">
+      <c r="P17" s="34" t="n"/>
+      <c r="Q17" s="34" t="n"/>
+      <c r="R17" s="19" t="n"/>
+      <c r="S17" s="19" t="n"/>
+      <c r="X17" s="61" t="n">
         <v>2</v>
       </c>
+      <c r="Y17" s="34" t="n"/>
+    </row>
+    <row r="18">
+      <c r="L18" s="36" t="n"/>
+      <c r="M18" s="36" t="n"/>
+      <c r="N18" s="36" t="n"/>
+    </row>
+    <row r="19">
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vm, m3</t>
+        </is>
+      </c>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>Suma t, min</t>
+        </is>
+      </c>
+      <c r="N19" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis Vo (l/min)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="J22" s="31" t="n">
+      <c r="A22" s="68" t="n"/>
+      <c r="B22" s="68" t="n"/>
+      <c r="C22" s="68" t="n"/>
+      <c r="D22" s="69" t="n"/>
+      <c r="E22" s="69" t="n"/>
+      <c r="F22" s="34" t="n"/>
+      <c r="G22" s="36" t="n"/>
+      <c r="H22" s="34" t="n"/>
+      <c r="I22" s="34" t="n"/>
+      <c r="J22" s="58" t="n">
         <v>131</v>
       </c>
-      <c r="K22" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N22" s="1" t="n">
+      <c r="K22" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="36" t="n"/>
+      <c r="M22" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N22" s="40" t="n">
         <v>132</v>
       </c>
-      <c r="O22" s="31" t="n">
+      <c r="O22" s="58" t="n">
         <v>133</v>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="P22" s="34" t="n"/>
+      <c r="Q22" s="34" t="n"/>
+      <c r="R22" s="69" t="n"/>
+      <c r="S22" s="59" t="inlineStr">
         <is>
           <t>1 filtras, 3 linija</t>
         </is>
       </c>
-      <c r="X22" s="25" t="n">
-        <v>3</v>
-      </c>
+      <c r="X22" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y22" s="34" t="n"/>
     </row>
     <row r="23">
-      <c r="J23" s="31" t="n">
+      <c r="C23" s="68" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="34" t="n"/>
+      <c r="G23" s="36" t="n"/>
+      <c r="H23" s="34" t="n"/>
+      <c r="I23" s="34" t="n"/>
+      <c r="J23" s="58" t="n">
         <v>131</v>
       </c>
-      <c r="K23" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N23" s="1" t="n">
+      <c r="K23" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="36" t="n"/>
+      <c r="M23" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N23" s="40" t="n">
         <v>132</v>
       </c>
-      <c r="O23" s="31" t="n">
+      <c r="O23" s="58" t="n">
         <v>133</v>
       </c>
-      <c r="X23" s="25" t="n">
-        <v>3</v>
-      </c>
+      <c r="P23" s="34" t="n"/>
+      <c r="Q23" s="34" t="n"/>
+      <c r="R23" s="17" t="n"/>
+      <c r="S23" s="17" t="n"/>
+      <c r="X23" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="34" t="n"/>
     </row>
     <row r="24">
-      <c r="J24" s="31" t="n">
+      <c r="C24" s="68" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="34" t="n"/>
+      <c r="G24" s="36" t="n"/>
+      <c r="H24" s="34" t="n"/>
+      <c r="I24" s="34" t="n"/>
+      <c r="J24" s="58" t="n">
         <v>131</v>
       </c>
-      <c r="K24" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N24" s="1" t="n">
+      <c r="K24" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="36" t="n"/>
+      <c r="M24" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N24" s="40" t="n">
         <v>132</v>
       </c>
-      <c r="O24" s="31" t="n">
+      <c r="O24" s="58" t="n">
         <v>133</v>
       </c>
-      <c r="X24" s="25" t="n">
-        <v>3</v>
-      </c>
+      <c r="P24" s="34" t="n"/>
+      <c r="Q24" s="34" t="n"/>
+      <c r="R24" s="17" t="n"/>
+      <c r="S24" s="17" t="n"/>
+      <c r="X24" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y24" s="34" t="n"/>
     </row>
     <row r="25">
-      <c r="J25" s="31" t="n">
+      <c r="C25" s="68" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="34" t="n"/>
+      <c r="G25" s="36" t="n"/>
+      <c r="H25" s="34" t="n"/>
+      <c r="I25" s="34" t="n"/>
+      <c r="J25" s="58" t="n">
         <v>131</v>
       </c>
-      <c r="K25" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N25" s="1" t="n">
+      <c r="K25" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="36" t="n"/>
+      <c r="M25" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N25" s="40" t="n">
         <v>132</v>
       </c>
-      <c r="O25" s="31" t="n">
+      <c r="O25" s="58" t="n">
         <v>133</v>
       </c>
-      <c r="X25" s="25" t="n">
-        <v>3</v>
+      <c r="P25" s="34" t="n"/>
+      <c r="Q25" s="34" t="n"/>
+      <c r="R25" s="19" t="n"/>
+      <c r="S25" s="19" t="n"/>
+      <c r="X25" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y25" s="34" t="n"/>
+    </row>
+    <row r="26">
+      <c r="L26" s="36" t="n"/>
+      <c r="M26" s="36" t="n"/>
+      <c r="N26" s="36" t="n"/>
+    </row>
+    <row r="27">
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vm, m3</t>
+        </is>
+      </c>
+      <c r="M27" s="12" t="inlineStr">
+        <is>
+          <t>Suma t, min</t>
+        </is>
+      </c>
+      <c r="N27" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis Vo (l/min)</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="J30" s="31" t="n">
+      <c r="A30" s="68" t="n"/>
+      <c r="B30" s="68" t="n"/>
+      <c r="C30" s="68" t="n"/>
+      <c r="D30" s="69" t="n"/>
+      <c r="E30" s="69" t="n"/>
+      <c r="F30" s="34" t="n"/>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="34" t="n"/>
+      <c r="I30" s="34" t="n"/>
+      <c r="J30" s="58" t="n">
         <v>141</v>
       </c>
-      <c r="K30" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N30" s="1" t="n">
+      <c r="K30" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="36" t="n"/>
+      <c r="M30" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N30" s="40" t="n">
         <v>142</v>
       </c>
-      <c r="O30" s="31" t="n">
+      <c r="O30" s="58" t="n">
         <v>143</v>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="P30" s="34" t="n"/>
+      <c r="Q30" s="34" t="n"/>
+      <c r="R30" s="69" t="n"/>
+      <c r="S30" s="59" t="inlineStr">
         <is>
           <t>1 filtras, 4 linija</t>
         </is>
       </c>
-      <c r="X30" s="25" t="n">
+      <c r="X30" s="61" t="n">
         <v>4</v>
       </c>
+      <c r="Y30" s="34" t="n"/>
     </row>
     <row r="31">
-      <c r="J31" s="31" t="n">
+      <c r="C31" s="68" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="34" t="n"/>
+      <c r="G31" s="36" t="n"/>
+      <c r="H31" s="34" t="n"/>
+      <c r="I31" s="34" t="n"/>
+      <c r="J31" s="58" t="n">
         <v>141</v>
       </c>
-      <c r="K31" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N31" s="1" t="n">
+      <c r="K31" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="36" t="n"/>
+      <c r="M31" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N31" s="40" t="n">
         <v>142</v>
       </c>
-      <c r="O31" s="31" t="n">
+      <c r="O31" s="58" t="n">
         <v>143</v>
       </c>
-      <c r="X31" s="25" t="n">
+      <c r="P31" s="34" t="n"/>
+      <c r="Q31" s="34" t="n"/>
+      <c r="R31" s="17" t="n"/>
+      <c r="S31" s="17" t="n"/>
+      <c r="X31" s="61" t="n">
         <v>4</v>
       </c>
+      <c r="Y31" s="34" t="n"/>
     </row>
     <row r="32">
-      <c r="J32" s="31" t="n">
+      <c r="C32" s="68" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="34" t="n"/>
+      <c r="G32" s="36" t="n"/>
+      <c r="H32" s="34" t="n"/>
+      <c r="I32" s="34" t="n"/>
+      <c r="J32" s="58" t="n">
         <v>141</v>
       </c>
-      <c r="K32" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N32" s="1" t="n">
+      <c r="K32" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="36" t="n"/>
+      <c r="M32" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N32" s="40" t="n">
         <v>142</v>
       </c>
-      <c r="O32" s="31" t="n">
+      <c r="O32" s="58" t="n">
         <v>143</v>
       </c>
-      <c r="X32" s="25" t="n">
+      <c r="P32" s="34" t="n"/>
+      <c r="Q32" s="34" t="n"/>
+      <c r="R32" s="17" t="n"/>
+      <c r="S32" s="17" t="n"/>
+      <c r="X32" s="61" t="n">
         <v>4</v>
       </c>
+      <c r="Y32" s="34" t="n"/>
     </row>
     <row r="33">
-      <c r="J33" s="31" t="n">
+      <c r="C33" s="68" t="n"/>
+      <c r="D33" s="19" t="n"/>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="34" t="n"/>
+      <c r="G33" s="36" t="n"/>
+      <c r="H33" s="34" t="n"/>
+      <c r="I33" s="34" t="n"/>
+      <c r="J33" s="58" t="n">
         <v>141</v>
       </c>
-      <c r="K33" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N33" s="1" t="n">
+      <c r="K33" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="36" t="n"/>
+      <c r="M33" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N33" s="40" t="n">
         <v>142</v>
       </c>
-      <c r="O33" s="31" t="n">
+      <c r="O33" s="58" t="n">
         <v>143</v>
       </c>
-      <c r="X33" s="25" t="n">
+      <c r="P33" s="34" t="n"/>
+      <c r="Q33" s="34" t="n"/>
+      <c r="R33" s="19" t="n"/>
+      <c r="S33" s="19" t="n"/>
+      <c r="X33" s="61" t="n">
         <v>4</v>
       </c>
+      <c r="Y33" s="34" t="n"/>
+    </row>
+    <row r="34">
+      <c r="L34" s="36" t="n"/>
+      <c r="M34" s="36" t="n"/>
+      <c r="N34" s="36" t="n"/>
+    </row>
+    <row r="35">
+      <c r="L35" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vm, m3</t>
+        </is>
+      </c>
+      <c r="M35" s="12" t="inlineStr">
+        <is>
+          <t>Suma t, min</t>
+        </is>
+      </c>
+      <c r="N35" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis Vo (l/min)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="J38" s="31" t="n">
+      <c r="A38" s="68" t="n"/>
+      <c r="B38" s="68" t="n"/>
+      <c r="C38" s="68" t="n"/>
+      <c r="D38" s="69" t="n"/>
+      <c r="E38" s="69" t="n"/>
+      <c r="F38" s="34" t="n"/>
+      <c r="G38" s="36" t="n"/>
+      <c r="H38" s="34" t="n"/>
+      <c r="I38" s="34" t="n"/>
+      <c r="J38" s="58" t="n">
         <v>151</v>
       </c>
-      <c r="K38" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M38" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N38" s="1" t="n">
+      <c r="K38" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="36" t="n"/>
+      <c r="M38" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N38" s="40" t="n">
         <v>152</v>
       </c>
-      <c r="O38" s="31" t="n">
+      <c r="O38" s="58" t="n">
         <v>153</v>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="P38" s="34" t="n"/>
+      <c r="Q38" s="34" t="n"/>
+      <c r="R38" s="69" t="n"/>
+      <c r="S38" s="59" t="inlineStr">
         <is>
           <t>1 filtras, 5 linija</t>
         </is>
       </c>
-      <c r="X38" s="25" t="n">
+      <c r="X38" s="61" t="n">
         <v>5</v>
       </c>
+      <c r="Y38" s="34" t="n"/>
     </row>
     <row r="39">
-      <c r="J39" s="31" t="n">
+      <c r="C39" s="68" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="34" t="n"/>
+      <c r="G39" s="36" t="n"/>
+      <c r="H39" s="34" t="n"/>
+      <c r="I39" s="34" t="n"/>
+      <c r="J39" s="58" t="n">
         <v>151</v>
       </c>
-      <c r="K39" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N39" s="1" t="n">
+      <c r="K39" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="36" t="n"/>
+      <c r="M39" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N39" s="40" t="n">
         <v>152</v>
       </c>
-      <c r="O39" s="31" t="n">
+      <c r="O39" s="58" t="n">
         <v>153</v>
       </c>
-      <c r="X39" s="25" t="n">
+      <c r="P39" s="34" t="n"/>
+      <c r="Q39" s="34" t="n"/>
+      <c r="R39" s="17" t="n"/>
+      <c r="S39" s="17" t="n"/>
+      <c r="X39" s="61" t="n">
         <v>5</v>
       </c>
+      <c r="Y39" s="34" t="n"/>
     </row>
     <row r="40">
-      <c r="J40" s="31" t="n">
+      <c r="C40" s="68" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="34" t="n"/>
+      <c r="G40" s="36" t="n"/>
+      <c r="H40" s="34" t="n"/>
+      <c r="I40" s="34" t="n"/>
+      <c r="J40" s="58" t="n">
         <v>151</v>
       </c>
-      <c r="K40" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M40" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N40" s="1" t="n">
+      <c r="K40" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="36" t="n"/>
+      <c r="M40" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N40" s="40" t="n">
         <v>152</v>
       </c>
-      <c r="O40" s="31" t="n">
+      <c r="O40" s="58" t="n">
         <v>153</v>
       </c>
-      <c r="X40" s="25" t="n">
+      <c r="P40" s="34" t="n"/>
+      <c r="Q40" s="34" t="n"/>
+      <c r="R40" s="17" t="n"/>
+      <c r="S40" s="17" t="n"/>
+      <c r="X40" s="61" t="n">
         <v>5</v>
       </c>
+      <c r="Y40" s="34" t="n"/>
     </row>
     <row r="41">
-      <c r="J41" s="31" t="n">
+      <c r="C41" s="68" t="n"/>
+      <c r="D41" s="19" t="n"/>
+      <c r="E41" s="19" t="n"/>
+      <c r="F41" s="34" t="n"/>
+      <c r="G41" s="36" t="n"/>
+      <c r="H41" s="34" t="n"/>
+      <c r="I41" s="34" t="n"/>
+      <c r="J41" s="58" t="n">
         <v>151</v>
       </c>
-      <c r="K41" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M41" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N41" s="1" t="n">
+      <c r="K41" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="36" t="n"/>
+      <c r="M41" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N41" s="40" t="n">
         <v>152</v>
       </c>
-      <c r="O41" s="31" t="n">
+      <c r="O41" s="58" t="n">
         <v>153</v>
       </c>
-      <c r="X41" s="25" t="n">
+      <c r="P41" s="34" t="n"/>
+      <c r="Q41" s="34" t="n"/>
+      <c r="R41" s="19" t="n"/>
+      <c r="S41" s="19" t="n"/>
+      <c r="X41" s="61" t="n">
         <v>5</v>
       </c>
+      <c r="Y41" s="34" t="n"/>
+    </row>
+    <row r="42">
+      <c r="L42" s="36" t="n"/>
+      <c r="M42" s="36" t="n"/>
+      <c r="N42" s="36" t="n"/>
+    </row>
+    <row r="43">
+      <c r="L43" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vm, m3</t>
+        </is>
+      </c>
+      <c r="M43" s="12" t="inlineStr">
+        <is>
+          <t>Suma t, min</t>
+        </is>
+      </c>
+      <c r="N43" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis Vo (l/min)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="J46" s="31" t="n">
+      <c r="A46" s="68" t="n"/>
+      <c r="B46" s="68" t="n"/>
+      <c r="C46" s="68" t="n"/>
+      <c r="D46" s="69" t="n"/>
+      <c r="E46" s="69" t="n"/>
+      <c r="F46" s="34" t="n"/>
+      <c r="G46" s="36" t="n"/>
+      <c r="H46" s="34" t="n"/>
+      <c r="I46" s="34" t="n"/>
+      <c r="J46" s="58" t="n">
         <v>211</v>
       </c>
-      <c r="K46" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M46" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N46" s="1" t="n">
+      <c r="K46" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="36" t="n"/>
+      <c r="M46" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N46" s="40" t="n">
         <v>212</v>
       </c>
-      <c r="O46" s="31" t="n">
+      <c r="O46" s="58" t="n">
         <v>213</v>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="P46" s="34" t="n"/>
+      <c r="Q46" s="34" t="n"/>
+      <c r="R46" s="69" t="n"/>
+      <c r="S46" s="59" t="inlineStr">
         <is>
           <t>2 filtras, 1 linija</t>
         </is>
       </c>
-      <c r="X46" s="25" t="n">
-        <v>1</v>
-      </c>
+      <c r="X46" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y46" s="34" t="n"/>
     </row>
     <row r="47">
-      <c r="J47" s="31" t="n">
+      <c r="C47" s="68" t="n"/>
+      <c r="D47" s="17" t="n"/>
+      <c r="E47" s="17" t="n"/>
+      <c r="F47" s="34" t="n"/>
+      <c r="G47" s="36" t="n"/>
+      <c r="H47" s="34" t="n"/>
+      <c r="I47" s="34" t="n"/>
+      <c r="J47" s="58" t="n">
         <v>211</v>
       </c>
-      <c r="K47" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M47" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N47" s="1" t="n">
+      <c r="K47" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" s="36" t="n"/>
+      <c r="M47" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N47" s="40" t="n">
         <v>212</v>
       </c>
-      <c r="O47" s="31" t="n">
+      <c r="O47" s="58" t="n">
         <v>213</v>
       </c>
-      <c r="X47" s="25" t="n">
-        <v>1</v>
-      </c>
+      <c r="P47" s="34" t="n"/>
+      <c r="Q47" s="34" t="n"/>
+      <c r="R47" s="17" t="n"/>
+      <c r="S47" s="17" t="n"/>
+      <c r="X47" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y47" s="34" t="n"/>
     </row>
     <row r="48">
-      <c r="J48" s="31" t="n">
+      <c r="C48" s="68" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="34" t="n"/>
+      <c r="G48" s="36" t="n"/>
+      <c r="H48" s="34" t="n"/>
+      <c r="I48" s="34" t="n"/>
+      <c r="J48" s="58" t="n">
         <v>211</v>
       </c>
-      <c r="K48" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N48" s="1" t="n">
+      <c r="K48" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" s="36" t="n"/>
+      <c r="M48" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N48" s="40" t="n">
         <v>212</v>
       </c>
-      <c r="O48" s="31" t="n">
+      <c r="O48" s="58" t="n">
         <v>213</v>
       </c>
-      <c r="X48" s="25" t="n">
-        <v>1</v>
-      </c>
+      <c r="P48" s="34" t="n"/>
+      <c r="Q48" s="34" t="n"/>
+      <c r="R48" s="17" t="n"/>
+      <c r="S48" s="17" t="n"/>
+      <c r="X48" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y48" s="34" t="n"/>
     </row>
     <row r="49">
-      <c r="J49" s="31" t="n">
+      <c r="C49" s="68" t="n"/>
+      <c r="D49" s="19" t="n"/>
+      <c r="E49" s="19" t="n"/>
+      <c r="F49" s="34" t="n"/>
+      <c r="G49" s="36" t="n"/>
+      <c r="H49" s="34" t="n"/>
+      <c r="I49" s="34" t="n"/>
+      <c r="J49" s="58" t="n">
         <v>211</v>
       </c>
-      <c r="K49" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M49" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N49" s="1" t="n">
+      <c r="K49" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" s="36" t="n"/>
+      <c r="M49" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N49" s="40" t="n">
         <v>212</v>
       </c>
-      <c r="O49" s="31" t="n">
+      <c r="O49" s="58" t="n">
         <v>213</v>
       </c>
-      <c r="X49" s="25" t="n">
-        <v>1</v>
+      <c r="P49" s="34" t="n"/>
+      <c r="Q49" s="34" t="n"/>
+      <c r="R49" s="19" t="n"/>
+      <c r="S49" s="19" t="n"/>
+      <c r="X49" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y49" s="34" t="n"/>
+    </row>
+    <row r="50">
+      <c r="L50" s="36" t="n"/>
+      <c r="M50" s="36" t="n"/>
+      <c r="N50" s="36" t="n"/>
+    </row>
+    <row r="51">
+      <c r="L51" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vm, m3</t>
+        </is>
+      </c>
+      <c r="M51" s="12" t="inlineStr">
+        <is>
+          <t>Suma t, min</t>
+        </is>
+      </c>
+      <c r="N51" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis Vo (l/min)</t>
+        </is>
       </c>
     </row>
     <row r="54">
-      <c r="J54" s="31" t="n">
+      <c r="A54" s="68" t="n"/>
+      <c r="B54" s="68" t="n"/>
+      <c r="C54" s="68" t="n"/>
+      <c r="D54" s="69" t="n"/>
+      <c r="E54" s="69" t="n"/>
+      <c r="F54" s="34" t="n"/>
+      <c r="G54" s="36" t="n"/>
+      <c r="H54" s="34" t="n"/>
+      <c r="I54" s="34" t="n"/>
+      <c r="J54" s="58" t="n">
         <v>221</v>
       </c>
-      <c r="K54" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M54" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N54" s="1" t="n">
+      <c r="K54" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" s="36" t="n"/>
+      <c r="M54" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N54" s="40" t="n">
         <v>222</v>
       </c>
-      <c r="O54" s="31" t="n">
+      <c r="O54" s="58" t="n">
         <v>223</v>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="P54" s="34" t="n"/>
+      <c r="Q54" s="34" t="n"/>
+      <c r="R54" s="69" t="n"/>
+      <c r="S54" s="59" t="inlineStr">
         <is>
           <t>2 filtras, 2 linija</t>
         </is>
       </c>
-      <c r="X54" s="25" t="n">
+      <c r="X54" s="61" t="n">
         <v>2</v>
       </c>
+      <c r="Y54" s="34" t="n"/>
     </row>
     <row r="55">
-      <c r="J55" s="31" t="n">
+      <c r="C55" s="68" t="n"/>
+      <c r="D55" s="17" t="n"/>
+      <c r="E55" s="17" t="n"/>
+      <c r="F55" s="34" t="n"/>
+      <c r="G55" s="36" t="n"/>
+      <c r="H55" s="34" t="n"/>
+      <c r="I55" s="34" t="n"/>
+      <c r="J55" s="58" t="n">
         <v>221</v>
       </c>
-      <c r="K55" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M55" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N55" s="1" t="n">
+      <c r="K55" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" s="36" t="n"/>
+      <c r="M55" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N55" s="40" t="n">
         <v>222</v>
       </c>
-      <c r="O55" s="31" t="n">
+      <c r="O55" s="58" t="n">
         <v>223</v>
       </c>
-      <c r="X55" s="25" t="n">
+      <c r="P55" s="34" t="n"/>
+      <c r="Q55" s="34" t="n"/>
+      <c r="R55" s="17" t="n"/>
+      <c r="S55" s="17" t="n"/>
+      <c r="X55" s="61" t="n">
         <v>2</v>
       </c>
+      <c r="Y55" s="34" t="n"/>
     </row>
     <row r="56">
-      <c r="J56" s="31" t="n">
+      <c r="C56" s="68" t="n"/>
+      <c r="D56" s="17" t="n"/>
+      <c r="E56" s="17" t="n"/>
+      <c r="F56" s="34" t="n"/>
+      <c r="G56" s="36" t="n"/>
+      <c r="H56" s="34" t="n"/>
+      <c r="I56" s="34" t="n"/>
+      <c r="J56" s="58" t="n">
         <v>221</v>
       </c>
-      <c r="K56" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M56" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N56" s="1" t="n">
+      <c r="K56" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" s="36" t="n"/>
+      <c r="M56" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N56" s="40" t="n">
         <v>222</v>
       </c>
-      <c r="O56" s="31" t="n">
+      <c r="O56" s="58" t="n">
         <v>223</v>
       </c>
-      <c r="X56" s="25" t="n">
+      <c r="P56" s="34" t="n"/>
+      <c r="Q56" s="34" t="n"/>
+      <c r="R56" s="17" t="n"/>
+      <c r="S56" s="17" t="n"/>
+      <c r="X56" s="61" t="n">
         <v>2</v>
       </c>
+      <c r="Y56" s="34" t="n"/>
     </row>
     <row r="57">
-      <c r="J57" s="31" t="n">
+      <c r="C57" s="68" t="n"/>
+      <c r="D57" s="19" t="n"/>
+      <c r="E57" s="19" t="n"/>
+      <c r="F57" s="34" t="n"/>
+      <c r="G57" s="36" t="n"/>
+      <c r="H57" s="34" t="n"/>
+      <c r="I57" s="34" t="n"/>
+      <c r="J57" s="58" t="n">
         <v>221</v>
       </c>
-      <c r="K57" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N57" s="1" t="n">
+      <c r="K57" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" s="36" t="n"/>
+      <c r="M57" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N57" s="40" t="n">
         <v>222</v>
       </c>
-      <c r="O57" s="31" t="n">
+      <c r="O57" s="58" t="n">
         <v>223</v>
       </c>
-      <c r="X57" s="25" t="n">
+      <c r="P57" s="34" t="n"/>
+      <c r="Q57" s="34" t="n"/>
+      <c r="R57" s="19" t="n"/>
+      <c r="S57" s="19" t="n"/>
+      <c r="X57" s="61" t="n">
         <v>2</v>
       </c>
+      <c r="Y57" s="34" t="n"/>
+    </row>
+    <row r="58">
+      <c r="L58" s="36" t="n"/>
+      <c r="M58" s="36" t="n"/>
+      <c r="N58" s="36" t="n"/>
+    </row>
+    <row r="59">
+      <c r="L59" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vm, m3</t>
+        </is>
+      </c>
+      <c r="M59" s="12" t="inlineStr">
+        <is>
+          <t>Suma t, min</t>
+        </is>
+      </c>
+      <c r="N59" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis Vo (l/min)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="J62" s="31" t="n">
+      <c r="A62" s="68" t="n"/>
+      <c r="B62" s="68" t="n"/>
+      <c r="C62" s="68" t="n"/>
+      <c r="D62" s="69" t="n"/>
+      <c r="E62" s="69" t="n"/>
+      <c r="F62" s="34" t="n"/>
+      <c r="G62" s="36" t="n"/>
+      <c r="H62" s="34" t="n"/>
+      <c r="I62" s="34" t="n"/>
+      <c r="J62" s="58" t="n">
         <v>231</v>
       </c>
-      <c r="K62" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M62" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N62" s="1" t="n">
+      <c r="K62" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" s="36" t="n"/>
+      <c r="M62" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N62" s="40" t="n">
         <v>232</v>
       </c>
-      <c r="O62" s="31" t="n">
+      <c r="O62" s="58" t="n">
         <v>233</v>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="P62" s="34" t="n"/>
+      <c r="Q62" s="34" t="n"/>
+      <c r="R62" s="69" t="n"/>
+      <c r="S62" s="59" t="inlineStr">
         <is>
           <t>2 filtras, 3 linija</t>
         </is>
       </c>
-      <c r="X62" s="25" t="n">
-        <v>3</v>
-      </c>
+      <c r="X62" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y62" s="34" t="n"/>
     </row>
     <row r="63">
-      <c r="J63" s="31" t="n">
+      <c r="C63" s="68" t="n"/>
+      <c r="D63" s="17" t="n"/>
+      <c r="E63" s="17" t="n"/>
+      <c r="F63" s="34" t="n"/>
+      <c r="G63" s="36" t="n"/>
+      <c r="H63" s="34" t="n"/>
+      <c r="I63" s="34" t="n"/>
+      <c r="J63" s="58" t="n">
         <v>231</v>
       </c>
-      <c r="K63" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M63" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N63" s="1" t="n">
+      <c r="K63" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" s="36" t="n"/>
+      <c r="M63" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N63" s="40" t="n">
         <v>232</v>
       </c>
-      <c r="O63" s="31" t="n">
+      <c r="O63" s="58" t="n">
         <v>233</v>
       </c>
-      <c r="X63" s="25" t="n">
-        <v>3</v>
-      </c>
+      <c r="P63" s="34" t="n"/>
+      <c r="Q63" s="34" t="n"/>
+      <c r="R63" s="17" t="n"/>
+      <c r="S63" s="17" t="n"/>
+      <c r="X63" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y63" s="34" t="n"/>
     </row>
     <row r="64">
-      <c r="J64" s="31" t="n">
+      <c r="C64" s="68" t="n"/>
+      <c r="D64" s="17" t="n"/>
+      <c r="E64" s="17" t="n"/>
+      <c r="F64" s="34" t="n"/>
+      <c r="G64" s="36" t="n"/>
+      <c r="H64" s="34" t="n"/>
+      <c r="I64" s="34" t="n"/>
+      <c r="J64" s="58" t="n">
         <v>231</v>
       </c>
-      <c r="K64" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M64" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N64" s="1" t="n">
+      <c r="K64" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" s="36" t="n"/>
+      <c r="M64" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N64" s="40" t="n">
         <v>232</v>
       </c>
-      <c r="O64" s="31" t="n">
+      <c r="O64" s="58" t="n">
         <v>233</v>
       </c>
-      <c r="X64" s="25" t="n">
-        <v>3</v>
-      </c>
+      <c r="P64" s="34" t="n"/>
+      <c r="Q64" s="34" t="n"/>
+      <c r="R64" s="17" t="n"/>
+      <c r="S64" s="17" t="n"/>
+      <c r="X64" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y64" s="34" t="n"/>
     </row>
     <row r="65">
-      <c r="J65" s="31" t="n">
+      <c r="C65" s="68" t="n"/>
+      <c r="D65" s="19" t="n"/>
+      <c r="E65" s="19" t="n"/>
+      <c r="F65" s="34" t="n"/>
+      <c r="G65" s="36" t="n"/>
+      <c r="H65" s="34" t="n"/>
+      <c r="I65" s="34" t="n"/>
+      <c r="J65" s="58" t="n">
         <v>231</v>
       </c>
-      <c r="K65" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M65" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N65" s="1" t="n">
+      <c r="K65" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" s="36" t="n"/>
+      <c r="M65" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N65" s="40" t="n">
         <v>232</v>
       </c>
-      <c r="O65" s="31" t="n">
+      <c r="O65" s="58" t="n">
         <v>233</v>
       </c>
-      <c r="X65" s="25" t="n">
-        <v>3</v>
+      <c r="P65" s="34" t="n"/>
+      <c r="Q65" s="34" t="n"/>
+      <c r="R65" s="19" t="n"/>
+      <c r="S65" s="19" t="n"/>
+      <c r="X65" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y65" s="34" t="n"/>
+    </row>
+    <row r="66">
+      <c r="L66" s="36" t="n"/>
+      <c r="M66" s="36" t="n"/>
+      <c r="N66" s="36" t="n"/>
+    </row>
+    <row r="67">
+      <c r="L67" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vm, m3</t>
+        </is>
+      </c>
+      <c r="M67" s="12" t="inlineStr">
+        <is>
+          <t>Suma t, min</t>
+        </is>
+      </c>
+      <c r="N67" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis Vo (l/min)</t>
+        </is>
       </c>
     </row>
     <row r="70">
-      <c r="J70" s="31" t="n">
+      <c r="A70" s="68" t="n"/>
+      <c r="B70" s="68" t="n"/>
+      <c r="C70" s="68" t="n"/>
+      <c r="D70" s="69" t="n"/>
+      <c r="E70" s="69" t="n"/>
+      <c r="F70" s="34" t="n"/>
+      <c r="G70" s="36" t="n"/>
+      <c r="H70" s="34" t="n"/>
+      <c r="I70" s="34" t="n"/>
+      <c r="J70" s="58" t="n">
         <v>241</v>
       </c>
-      <c r="K70" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M70" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N70" s="1" t="n">
+      <c r="K70" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="36" t="n"/>
+      <c r="M70" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N70" s="40" t="n">
         <v>242</v>
       </c>
-      <c r="O70" s="31" t="n">
+      <c r="O70" s="58" t="n">
         <v>243</v>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="P70" s="34" t="n"/>
+      <c r="Q70" s="34" t="n"/>
+      <c r="R70" s="69" t="n"/>
+      <c r="S70" s="59" t="inlineStr">
         <is>
           <t>2 filtras, 4 linija</t>
         </is>
       </c>
-      <c r="X70" s="25" t="n">
+      <c r="X70" s="61" t="n">
         <v>4</v>
       </c>
+      <c r="Y70" s="34" t="n"/>
     </row>
     <row r="71">
-      <c r="J71" s="31" t="n">
+      <c r="C71" s="68" t="n"/>
+      <c r="D71" s="17" t="n"/>
+      <c r="E71" s="17" t="n"/>
+      <c r="F71" s="34" t="n"/>
+      <c r="G71" s="36" t="n"/>
+      <c r="H71" s="34" t="n"/>
+      <c r="I71" s="34" t="n"/>
+      <c r="J71" s="58" t="n">
         <v>241</v>
       </c>
-      <c r="K71" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M71" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N71" s="1" t="n">
+      <c r="K71" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" s="36" t="n"/>
+      <c r="M71" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N71" s="40" t="n">
         <v>242</v>
       </c>
-      <c r="O71" s="31" t="n">
+      <c r="O71" s="58" t="n">
         <v>243</v>
       </c>
-      <c r="X71" s="25" t="n">
+      <c r="P71" s="34" t="n"/>
+      <c r="Q71" s="34" t="n"/>
+      <c r="R71" s="17" t="n"/>
+      <c r="S71" s="17" t="n"/>
+      <c r="X71" s="61" t="n">
         <v>4</v>
       </c>
+      <c r="Y71" s="34" t="n"/>
     </row>
     <row r="72">
-      <c r="J72" s="31" t="n">
+      <c r="C72" s="68" t="n"/>
+      <c r="D72" s="17" t="n"/>
+      <c r="E72" s="17" t="n"/>
+      <c r="F72" s="34" t="n"/>
+      <c r="G72" s="36" t="n"/>
+      <c r="H72" s="34" t="n"/>
+      <c r="I72" s="34" t="n"/>
+      <c r="J72" s="58" t="n">
         <v>241</v>
       </c>
-      <c r="K72" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M72" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N72" s="1" t="n">
+      <c r="K72" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" s="36" t="n"/>
+      <c r="M72" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N72" s="40" t="n">
         <v>242</v>
       </c>
-      <c r="O72" s="31" t="n">
+      <c r="O72" s="58" t="n">
         <v>243</v>
       </c>
-      <c r="X72" s="25" t="n">
+      <c r="P72" s="34" t="n"/>
+      <c r="Q72" s="34" t="n"/>
+      <c r="R72" s="17" t="n"/>
+      <c r="S72" s="17" t="n"/>
+      <c r="X72" s="61" t="n">
         <v>4</v>
       </c>
+      <c r="Y72" s="34" t="n"/>
     </row>
     <row r="73">
-      <c r="J73" s="31" t="n">
+      <c r="C73" s="68" t="n"/>
+      <c r="D73" s="19" t="n"/>
+      <c r="E73" s="19" t="n"/>
+      <c r="F73" s="34" t="n"/>
+      <c r="G73" s="36" t="n"/>
+      <c r="H73" s="34" t="n"/>
+      <c r="I73" s="34" t="n"/>
+      <c r="J73" s="58" t="n">
         <v>241</v>
       </c>
-      <c r="K73" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M73" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N73" s="1" t="n">
+      <c r="K73" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" s="36" t="n"/>
+      <c r="M73" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N73" s="40" t="n">
         <v>242</v>
       </c>
-      <c r="O73" s="31" t="n">
+      <c r="O73" s="58" t="n">
         <v>243</v>
       </c>
-      <c r="X73" s="25" t="n">
+      <c r="P73" s="34" t="n"/>
+      <c r="Q73" s="34" t="n"/>
+      <c r="R73" s="19" t="n"/>
+      <c r="S73" s="19" t="n"/>
+      <c r="X73" s="61" t="n">
         <v>4</v>
       </c>
+      <c r="Y73" s="34" t="n"/>
+    </row>
+    <row r="74">
+      <c r="L74" s="36" t="n"/>
+      <c r="M74" s="36" t="n"/>
+      <c r="N74" s="36" t="n"/>
+    </row>
+    <row r="75">
+      <c r="L75" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vm, m3</t>
+        </is>
+      </c>
+      <c r="M75" s="12" t="inlineStr">
+        <is>
+          <t>Suma t, min</t>
+        </is>
+      </c>
+      <c r="N75" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis Vo (l/min)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="J78" s="31" t="n">
+      <c r="A78" s="68" t="n"/>
+      <c r="B78" s="68" t="n"/>
+      <c r="C78" s="68" t="n"/>
+      <c r="D78" s="69" t="n"/>
+      <c r="E78" s="69" t="n"/>
+      <c r="F78" s="34" t="n"/>
+      <c r="G78" s="36" t="n"/>
+      <c r="H78" s="34" t="n"/>
+      <c r="I78" s="34" t="n"/>
+      <c r="J78" s="58" t="n">
         <v>251</v>
       </c>
-      <c r="K78" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M78" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N78" s="1" t="n">
+      <c r="K78" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" s="36" t="n"/>
+      <c r="M78" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N78" s="40" t="n">
         <v>252</v>
       </c>
-      <c r="O78" s="31" t="n">
+      <c r="O78" s="58" t="n">
         <v>253</v>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="P78" s="34" t="n"/>
+      <c r="Q78" s="34" t="n"/>
+      <c r="R78" s="69" t="n"/>
+      <c r="S78" s="59" t="inlineStr">
         <is>
           <t>2 filtras, 5 linija</t>
         </is>
       </c>
-      <c r="X78" s="25" t="n">
+      <c r="X78" s="61" t="n">
         <v>5</v>
       </c>
+      <c r="Y78" s="34" t="n"/>
     </row>
     <row r="79">
-      <c r="J79" s="31" t="n">
+      <c r="C79" s="68" t="n"/>
+      <c r="D79" s="17" t="n"/>
+      <c r="E79" s="17" t="n"/>
+      <c r="F79" s="34" t="n"/>
+      <c r="G79" s="36" t="n"/>
+      <c r="H79" s="34" t="n"/>
+      <c r="I79" s="34" t="n"/>
+      <c r="J79" s="58" t="n">
         <v>251</v>
       </c>
-      <c r="K79" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M79" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N79" s="1" t="n">
+      <c r="K79" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" s="36" t="n"/>
+      <c r="M79" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N79" s="40" t="n">
         <v>252</v>
       </c>
-      <c r="O79" s="31" t="n">
+      <c r="O79" s="58" t="n">
         <v>253</v>
       </c>
-      <c r="X79" s="25" t="n">
+      <c r="P79" s="34" t="n"/>
+      <c r="Q79" s="34" t="n"/>
+      <c r="R79" s="17" t="n"/>
+      <c r="S79" s="17" t="n"/>
+      <c r="X79" s="61" t="n">
         <v>5</v>
       </c>
+      <c r="Y79" s="34" t="n"/>
     </row>
     <row r="80">
-      <c r="J80" s="31" t="n">
+      <c r="C80" s="68" t="n"/>
+      <c r="D80" s="17" t="n"/>
+      <c r="E80" s="17" t="n"/>
+      <c r="F80" s="34" t="n"/>
+      <c r="G80" s="36" t="n"/>
+      <c r="H80" s="34" t="n"/>
+      <c r="I80" s="34" t="n"/>
+      <c r="J80" s="58" t="n">
         <v>251</v>
       </c>
-      <c r="K80" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M80" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N80" s="1" t="n">
+      <c r="K80" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" s="36" t="n"/>
+      <c r="M80" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N80" s="40" t="n">
         <v>252</v>
       </c>
-      <c r="O80" s="31" t="n">
+      <c r="O80" s="58" t="n">
         <v>253</v>
       </c>
-      <c r="X80" s="25" t="n">
+      <c r="P80" s="34" t="n"/>
+      <c r="Q80" s="34" t="n"/>
+      <c r="R80" s="17" t="n"/>
+      <c r="S80" s="17" t="n"/>
+      <c r="X80" s="61" t="n">
         <v>5</v>
       </c>
+      <c r="Y80" s="34" t="n"/>
     </row>
     <row r="81">
-      <c r="J81" s="31" t="n">
+      <c r="C81" s="68" t="n"/>
+      <c r="D81" s="19" t="n"/>
+      <c r="E81" s="19" t="n"/>
+      <c r="F81" s="34" t="n"/>
+      <c r="G81" s="36" t="n"/>
+      <c r="H81" s="34" t="n"/>
+      <c r="I81" s="34" t="n"/>
+      <c r="J81" s="58" t="n">
         <v>251</v>
       </c>
-      <c r="K81" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M81" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N81" s="1" t="n">
+      <c r="K81" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" s="36" t="n"/>
+      <c r="M81" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N81" s="40" t="n">
         <v>252</v>
       </c>
-      <c r="O81" s="31" t="n">
+      <c r="O81" s="58" t="n">
         <v>253</v>
       </c>
-      <c r="X81" s="25" t="n">
+      <c r="P81" s="34" t="n"/>
+      <c r="Q81" s="34" t="n"/>
+      <c r="R81" s="19" t="n"/>
+      <c r="S81" s="19" t="n"/>
+      <c r="X81" s="61" t="n">
         <v>5</v>
       </c>
+      <c r="Y81" s="34" t="n"/>
+    </row>
+    <row r="82">
+      <c r="L82" s="36" t="n"/>
+      <c r="M82" s="36" t="n"/>
+      <c r="N82" s="36" t="n"/>
+    </row>
+    <row r="83">
+      <c r="L83" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vm, m3</t>
+        </is>
+      </c>
+      <c r="M83" s="12" t="inlineStr">
+        <is>
+          <t>Suma t, min</t>
+        </is>
+      </c>
+      <c r="N83" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis Vo (l/min)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="J86" s="31" t="n">
+      <c r="A86" s="68" t="n"/>
+      <c r="B86" s="68" t="n"/>
+      <c r="C86" s="68" t="n"/>
+      <c r="D86" s="69" t="n"/>
+      <c r="E86" s="69" t="n"/>
+      <c r="F86" s="34" t="n"/>
+      <c r="G86" s="36" t="n"/>
+      <c r="H86" s="34" t="n"/>
+      <c r="I86" s="34" t="n"/>
+      <c r="J86" s="58" t="n">
         <v>311</v>
       </c>
-      <c r="K86" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M86" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N86" s="1" t="n">
+      <c r="K86" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" s="36" t="n"/>
+      <c r="M86" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N86" s="40" t="n">
         <v>312</v>
       </c>
-      <c r="O86" s="31" t="n">
+      <c r="O86" s="58" t="n">
         <v>313</v>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="P86" s="34" t="n"/>
+      <c r="Q86" s="34" t="n"/>
+      <c r="R86" s="69" t="n"/>
+      <c r="S86" s="59" t="inlineStr">
         <is>
           <t>3 filtras, 1 linija</t>
         </is>
       </c>
-      <c r="X86" s="25" t="n">
-        <v>1</v>
-      </c>
+      <c r="X86" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y86" s="34" t="n"/>
     </row>
     <row r="87">
-      <c r="J87" s="31" t="n">
+      <c r="C87" s="68" t="n"/>
+      <c r="D87" s="17" t="n"/>
+      <c r="E87" s="17" t="n"/>
+      <c r="F87" s="34" t="n"/>
+      <c r="G87" s="36" t="n"/>
+      <c r="H87" s="34" t="n"/>
+      <c r="I87" s="34" t="n"/>
+      <c r="J87" s="58" t="n">
         <v>311</v>
       </c>
-      <c r="K87" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M87" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N87" s="1" t="n">
+      <c r="K87" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" s="36" t="n"/>
+      <c r="M87" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N87" s="40" t="n">
         <v>312</v>
       </c>
-      <c r="O87" s="31" t="n">
+      <c r="O87" s="58" t="n">
         <v>313</v>
       </c>
-      <c r="X87" s="25" t="n">
-        <v>1</v>
-      </c>
+      <c r="P87" s="34" t="n"/>
+      <c r="Q87" s="34" t="n"/>
+      <c r="R87" s="17" t="n"/>
+      <c r="S87" s="17" t="n"/>
+      <c r="X87" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y87" s="34" t="n"/>
     </row>
     <row r="88">
-      <c r="J88" s="31" t="n">
+      <c r="C88" s="68" t="n"/>
+      <c r="D88" s="17" t="n"/>
+      <c r="E88" s="17" t="n"/>
+      <c r="F88" s="34" t="n"/>
+      <c r="G88" s="36" t="n"/>
+      <c r="H88" s="34" t="n"/>
+      <c r="I88" s="34" t="n"/>
+      <c r="J88" s="58" t="n">
         <v>311</v>
       </c>
-      <c r="K88" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M88" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N88" s="1" t="n">
+      <c r="K88" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" s="36" t="n"/>
+      <c r="M88" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N88" s="40" t="n">
         <v>312</v>
       </c>
-      <c r="O88" s="31" t="n">
+      <c r="O88" s="58" t="n">
         <v>313</v>
       </c>
-      <c r="X88" s="25" t="n">
-        <v>1</v>
-      </c>
+      <c r="P88" s="34" t="n"/>
+      <c r="Q88" s="34" t="n"/>
+      <c r="R88" s="17" t="n"/>
+      <c r="S88" s="17" t="n"/>
+      <c r="X88" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y88" s="34" t="n"/>
     </row>
     <row r="89">
-      <c r="J89" s="31" t="n">
+      <c r="C89" s="68" t="n"/>
+      <c r="D89" s="19" t="n"/>
+      <c r="E89" s="19" t="n"/>
+      <c r="F89" s="34" t="n"/>
+      <c r="G89" s="36" t="n"/>
+      <c r="H89" s="34" t="n"/>
+      <c r="I89" s="34" t="n"/>
+      <c r="J89" s="58" t="n">
         <v>311</v>
       </c>
-      <c r="K89" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M89" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N89" s="1" t="n">
+      <c r="K89" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" s="36" t="n"/>
+      <c r="M89" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N89" s="40" t="n">
         <v>312</v>
       </c>
-      <c r="O89" s="31" t="n">
+      <c r="O89" s="58" t="n">
         <v>313</v>
       </c>
-      <c r="X89" s="25" t="n">
-        <v>1</v>
+      <c r="P89" s="34" t="n"/>
+      <c r="Q89" s="34" t="n"/>
+      <c r="R89" s="19" t="n"/>
+      <c r="S89" s="19" t="n"/>
+      <c r="X89" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y89" s="34" t="n"/>
+    </row>
+    <row r="90">
+      <c r="L90" s="36" t="n"/>
+      <c r="M90" s="36" t="n"/>
+      <c r="N90" s="36" t="n"/>
+    </row>
+    <row r="91">
+      <c r="L91" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vm, m3</t>
+        </is>
+      </c>
+      <c r="M91" s="12" t="inlineStr">
+        <is>
+          <t>Suma t, min</t>
+        </is>
+      </c>
+      <c r="N91" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis Vo (l/min)</t>
+        </is>
       </c>
     </row>
     <row r="94">
-      <c r="J94" s="31" t="n">
+      <c r="A94" s="68" t="n"/>
+      <c r="B94" s="68" t="n"/>
+      <c r="C94" s="68" t="n"/>
+      <c r="D94" s="69" t="n"/>
+      <c r="E94" s="69" t="n"/>
+      <c r="F94" s="34" t="n"/>
+      <c r="G94" s="36" t="n"/>
+      <c r="H94" s="34" t="n"/>
+      <c r="I94" s="34" t="n"/>
+      <c r="J94" s="58" t="n">
         <v>321</v>
       </c>
-      <c r="K94" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M94" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N94" s="1" t="n">
+      <c r="K94" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" s="36" t="n"/>
+      <c r="M94" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N94" s="40" t="n">
         <v>322</v>
       </c>
-      <c r="O94" s="31" t="n">
+      <c r="O94" s="58" t="n">
         <v>323</v>
       </c>
-      <c r="S94" t="inlineStr">
+      <c r="P94" s="34" t="n"/>
+      <c r="Q94" s="34" t="n"/>
+      <c r="R94" s="69" t="n"/>
+      <c r="S94" s="59" t="inlineStr">
         <is>
           <t>3 filtras, 2 linija</t>
         </is>
       </c>
-      <c r="X94" s="25" t="n">
+      <c r="X94" s="61" t="n">
         <v>2</v>
       </c>
+      <c r="Y94" s="34" t="n"/>
     </row>
     <row r="95">
-      <c r="J95" s="31" t="n">
+      <c r="C95" s="68" t="n"/>
+      <c r="D95" s="17" t="n"/>
+      <c r="E95" s="17" t="n"/>
+      <c r="F95" s="34" t="n"/>
+      <c r="G95" s="36" t="n"/>
+      <c r="H95" s="34" t="n"/>
+      <c r="I95" s="34" t="n"/>
+      <c r="J95" s="58" t="n">
         <v>321</v>
       </c>
-      <c r="K95" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M95" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N95" s="1" t="n">
+      <c r="K95" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" s="36" t="n"/>
+      <c r="M95" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N95" s="40" t="n">
         <v>322</v>
       </c>
-      <c r="O95" s="31" t="n">
+      <c r="O95" s="58" t="n">
         <v>323</v>
       </c>
-      <c r="X95" s="25" t="n">
+      <c r="P95" s="34" t="n"/>
+      <c r="Q95" s="34" t="n"/>
+      <c r="R95" s="17" t="n"/>
+      <c r="S95" s="17" t="n"/>
+      <c r="X95" s="61" t="n">
         <v>2</v>
       </c>
+      <c r="Y95" s="34" t="n"/>
     </row>
     <row r="96">
-      <c r="J96" s="31" t="n">
+      <c r="C96" s="68" t="n"/>
+      <c r="D96" s="17" t="n"/>
+      <c r="E96" s="17" t="n"/>
+      <c r="F96" s="34" t="n"/>
+      <c r="G96" s="36" t="n"/>
+      <c r="H96" s="34" t="n"/>
+      <c r="I96" s="34" t="n"/>
+      <c r="J96" s="58" t="n">
         <v>321</v>
       </c>
-      <c r="K96" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M96" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N96" s="1" t="n">
+      <c r="K96" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" s="36" t="n"/>
+      <c r="M96" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N96" s="40" t="n">
         <v>322</v>
       </c>
-      <c r="O96" s="31" t="n">
+      <c r="O96" s="58" t="n">
         <v>323</v>
       </c>
-      <c r="X96" s="25" t="n">
+      <c r="P96" s="34" t="n"/>
+      <c r="Q96" s="34" t="n"/>
+      <c r="R96" s="17" t="n"/>
+      <c r="S96" s="17" t="n"/>
+      <c r="X96" s="61" t="n">
         <v>2</v>
       </c>
+      <c r="Y96" s="34" t="n"/>
     </row>
     <row r="97">
-      <c r="J97" s="31" t="n">
+      <c r="C97" s="68" t="n"/>
+      <c r="D97" s="19" t="n"/>
+      <c r="E97" s="19" t="n"/>
+      <c r="F97" s="34" t="n"/>
+      <c r="G97" s="36" t="n"/>
+      <c r="H97" s="34" t="n"/>
+      <c r="I97" s="34" t="n"/>
+      <c r="J97" s="58" t="n">
         <v>321</v>
       </c>
-      <c r="K97" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M97" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N97" s="1" t="n">
+      <c r="K97" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" s="36" t="n"/>
+      <c r="M97" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N97" s="40" t="n">
         <v>322</v>
       </c>
-      <c r="O97" s="31" t="n">
+      <c r="O97" s="58" t="n">
         <v>323</v>
       </c>
-      <c r="X97" s="25" t="n">
+      <c r="P97" s="34" t="n"/>
+      <c r="Q97" s="34" t="n"/>
+      <c r="R97" s="19" t="n"/>
+      <c r="S97" s="19" t="n"/>
+      <c r="X97" s="61" t="n">
         <v>2</v>
       </c>
+      <c r="Y97" s="34" t="n"/>
+    </row>
+    <row r="98">
+      <c r="L98" s="36" t="n"/>
+      <c r="M98" s="36" t="n"/>
+      <c r="N98" s="36" t="n"/>
+    </row>
+    <row r="99">
+      <c r="L99" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vm, m3</t>
+        </is>
+      </c>
+      <c r="M99" s="12" t="inlineStr">
+        <is>
+          <t>Suma t, min</t>
+        </is>
+      </c>
+      <c r="N99" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis Vo (l/min)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="J102" s="31" t="n">
+      <c r="A102" s="68" t="n"/>
+      <c r="B102" s="68" t="n"/>
+      <c r="C102" s="68" t="n"/>
+      <c r="D102" s="69" t="n"/>
+      <c r="E102" s="69" t="n"/>
+      <c r="F102" s="34" t="n"/>
+      <c r="G102" s="36" t="n"/>
+      <c r="H102" s="34" t="n"/>
+      <c r="I102" s="34" t="n"/>
+      <c r="J102" s="58" t="n">
         <v>331</v>
       </c>
-      <c r="K102" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M102" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N102" s="1" t="n">
+      <c r="K102" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L102" s="36" t="n"/>
+      <c r="M102" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N102" s="40" t="n">
         <v>332</v>
       </c>
-      <c r="O102" s="31" t="n">
+      <c r="O102" s="58" t="n">
         <v>333</v>
       </c>
-      <c r="S102" t="inlineStr">
+      <c r="P102" s="34" t="n"/>
+      <c r="Q102" s="34" t="n"/>
+      <c r="R102" s="69" t="n"/>
+      <c r="S102" s="59" t="inlineStr">
         <is>
           <t>3 filtras, 3 linija</t>
         </is>
       </c>
-      <c r="X102" s="25" t="n">
-        <v>3</v>
-      </c>
+      <c r="X102" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="34" t="n"/>
     </row>
     <row r="103">
-      <c r="J103" s="31" t="n">
+      <c r="C103" s="68" t="n"/>
+      <c r="D103" s="17" t="n"/>
+      <c r="E103" s="17" t="n"/>
+      <c r="F103" s="34" t="n"/>
+      <c r="G103" s="36" t="n"/>
+      <c r="H103" s="34" t="n"/>
+      <c r="I103" s="34" t="n"/>
+      <c r="J103" s="58" t="n">
         <v>331</v>
       </c>
-      <c r="K103" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M103" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N103" s="1" t="n">
+      <c r="K103" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L103" s="36" t="n"/>
+      <c r="M103" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N103" s="40" t="n">
         <v>332</v>
       </c>
-      <c r="O103" s="31" t="n">
+      <c r="O103" s="58" t="n">
         <v>333</v>
       </c>
-      <c r="X103" s="25" t="n">
-        <v>3</v>
-      </c>
+      <c r="P103" s="34" t="n"/>
+      <c r="Q103" s="34" t="n"/>
+      <c r="R103" s="17" t="n"/>
+      <c r="S103" s="17" t="n"/>
+      <c r="X103" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y103" s="34" t="n"/>
     </row>
     <row r="104">
-      <c r="J104" s="31" t="n">
+      <c r="C104" s="68" t="n"/>
+      <c r="D104" s="17" t="n"/>
+      <c r="E104" s="17" t="n"/>
+      <c r="F104" s="34" t="n"/>
+      <c r="G104" s="36" t="n"/>
+      <c r="H104" s="34" t="n"/>
+      <c r="I104" s="34" t="n"/>
+      <c r="J104" s="58" t="n">
         <v>331</v>
       </c>
-      <c r="K104" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M104" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N104" s="1" t="n">
+      <c r="K104" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" s="36" t="n"/>
+      <c r="M104" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N104" s="40" t="n">
         <v>332</v>
       </c>
-      <c r="O104" s="31" t="n">
+      <c r="O104" s="58" t="n">
         <v>333</v>
       </c>
-      <c r="X104" s="25" t="n">
-        <v>3</v>
-      </c>
+      <c r="P104" s="34" t="n"/>
+      <c r="Q104" s="34" t="n"/>
+      <c r="R104" s="17" t="n"/>
+      <c r="S104" s="17" t="n"/>
+      <c r="X104" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y104" s="34" t="n"/>
     </row>
     <row r="105">
-      <c r="J105" s="31" t="n">
+      <c r="C105" s="68" t="n"/>
+      <c r="D105" s="19" t="n"/>
+      <c r="E105" s="19" t="n"/>
+      <c r="F105" s="34" t="n"/>
+      <c r="G105" s="36" t="n"/>
+      <c r="H105" s="34" t="n"/>
+      <c r="I105" s="34" t="n"/>
+      <c r="J105" s="58" t="n">
         <v>331</v>
       </c>
-      <c r="K105" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M105" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N105" s="1" t="n">
+      <c r="K105" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L105" s="36" t="n"/>
+      <c r="M105" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N105" s="40" t="n">
         <v>332</v>
       </c>
-      <c r="O105" s="31" t="n">
+      <c r="O105" s="58" t="n">
         <v>333</v>
       </c>
-      <c r="X105" s="25" t="n">
-        <v>3</v>
+      <c r="P105" s="34" t="n"/>
+      <c r="Q105" s="34" t="n"/>
+      <c r="R105" s="19" t="n"/>
+      <c r="S105" s="19" t="n"/>
+      <c r="X105" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y105" s="34" t="n"/>
+    </row>
+    <row r="106">
+      <c r="L106" s="36" t="n"/>
+      <c r="M106" s="36" t="n"/>
+      <c r="N106" s="36" t="n"/>
+    </row>
+    <row r="107">
+      <c r="L107" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vm, m3</t>
+        </is>
+      </c>
+      <c r="M107" s="12" t="inlineStr">
+        <is>
+          <t>Suma t, min</t>
+        </is>
+      </c>
+      <c r="N107" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis Vo (l/min)</t>
+        </is>
       </c>
     </row>
     <row r="110">
-      <c r="J110" s="31" t="n">
+      <c r="A110" s="68" t="n"/>
+      <c r="B110" s="68" t="n"/>
+      <c r="C110" s="68" t="n"/>
+      <c r="D110" s="69" t="n"/>
+      <c r="E110" s="69" t="n"/>
+      <c r="F110" s="34" t="n"/>
+      <c r="G110" s="36" t="n"/>
+      <c r="H110" s="34" t="n"/>
+      <c r="I110" s="34" t="n"/>
+      <c r="J110" s="58" t="n">
         <v>341</v>
       </c>
-      <c r="K110" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M110" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N110" s="1" t="n">
+      <c r="K110" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" s="36" t="n"/>
+      <c r="M110" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N110" s="40" t="n">
         <v>342</v>
       </c>
-      <c r="O110" s="31" t="n">
+      <c r="O110" s="58" t="n">
         <v>343</v>
       </c>
-      <c r="S110" t="inlineStr">
+      <c r="P110" s="34" t="n"/>
+      <c r="Q110" s="34" t="n"/>
+      <c r="R110" s="69" t="n"/>
+      <c r="S110" s="59" t="inlineStr">
         <is>
           <t>3 filtras, 4 linija</t>
         </is>
       </c>
-      <c r="X110" s="25" t="n">
+      <c r="X110" s="61" t="n">
         <v>4</v>
       </c>
+      <c r="Y110" s="34" t="n"/>
     </row>
     <row r="111">
-      <c r="J111" s="31" t="n">
+      <c r="C111" s="68" t="n"/>
+      <c r="D111" s="17" t="n"/>
+      <c r="E111" s="17" t="n"/>
+      <c r="F111" s="34" t="n"/>
+      <c r="G111" s="36" t="n"/>
+      <c r="H111" s="34" t="n"/>
+      <c r="I111" s="34" t="n"/>
+      <c r="J111" s="58" t="n">
         <v>341</v>
       </c>
-      <c r="K111" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M111" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N111" s="1" t="n">
+      <c r="K111" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" s="36" t="n"/>
+      <c r="M111" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N111" s="40" t="n">
         <v>342</v>
       </c>
-      <c r="O111" s="31" t="n">
+      <c r="O111" s="58" t="n">
         <v>343</v>
       </c>
-      <c r="X111" s="25" t="n">
+      <c r="P111" s="34" t="n"/>
+      <c r="Q111" s="34" t="n"/>
+      <c r="R111" s="17" t="n"/>
+      <c r="S111" s="17" t="n"/>
+      <c r="X111" s="61" t="n">
         <v>4</v>
       </c>
+      <c r="Y111" s="34" t="n"/>
     </row>
     <row r="112">
-      <c r="J112" s="31" t="n">
+      <c r="C112" s="68" t="n"/>
+      <c r="D112" s="17" t="n"/>
+      <c r="E112" s="17" t="n"/>
+      <c r="F112" s="34" t="n"/>
+      <c r="G112" s="36" t="n"/>
+      <c r="H112" s="34" t="n"/>
+      <c r="I112" s="34" t="n"/>
+      <c r="J112" s="58" t="n">
         <v>341</v>
       </c>
-      <c r="K112" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M112" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N112" s="1" t="n">
+      <c r="K112" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" s="36" t="n"/>
+      <c r="M112" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N112" s="40" t="n">
         <v>342</v>
       </c>
-      <c r="O112" s="31" t="n">
+      <c r="O112" s="58" t="n">
         <v>343</v>
       </c>
-      <c r="X112" s="25" t="n">
+      <c r="P112" s="34" t="n"/>
+      <c r="Q112" s="34" t="n"/>
+      <c r="R112" s="17" t="n"/>
+      <c r="S112" s="17" t="n"/>
+      <c r="X112" s="61" t="n">
         <v>4</v>
       </c>
+      <c r="Y112" s="34" t="n"/>
     </row>
     <row r="113">
-      <c r="J113" s="31" t="n">
+      <c r="C113" s="68" t="n"/>
+      <c r="D113" s="19" t="n"/>
+      <c r="E113" s="19" t="n"/>
+      <c r="F113" s="34" t="n"/>
+      <c r="G113" s="36" t="n"/>
+      <c r="H113" s="34" t="n"/>
+      <c r="I113" s="34" t="n"/>
+      <c r="J113" s="58" t="n">
         <v>341</v>
       </c>
-      <c r="K113" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M113" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N113" s="1" t="n">
+      <c r="K113" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L113" s="36" t="n"/>
+      <c r="M113" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N113" s="40" t="n">
         <v>342</v>
       </c>
-      <c r="O113" s="31" t="n">
+      <c r="O113" s="58" t="n">
         <v>343</v>
       </c>
-      <c r="X113" s="25" t="n">
+      <c r="P113" s="34" t="n"/>
+      <c r="Q113" s="34" t="n"/>
+      <c r="R113" s="19" t="n"/>
+      <c r="S113" s="19" t="n"/>
+      <c r="X113" s="61" t="n">
         <v>4</v>
       </c>
+      <c r="Y113" s="34" t="n"/>
+    </row>
+    <row r="114">
+      <c r="L114" s="36" t="n"/>
+      <c r="M114" s="36" t="n"/>
+      <c r="N114" s="36" t="n"/>
+    </row>
+    <row r="115">
+      <c r="L115" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vm, m3</t>
+        </is>
+      </c>
+      <c r="M115" s="12" t="inlineStr">
+        <is>
+          <t>Suma t, min</t>
+        </is>
+      </c>
+      <c r="N115" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis Vo (l/min)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="J118" s="31" t="n">
+      <c r="A118" s="68" t="n"/>
+      <c r="B118" s="68" t="n"/>
+      <c r="C118" s="68" t="n"/>
+      <c r="D118" s="69" t="n"/>
+      <c r="E118" s="69" t="n"/>
+      <c r="F118" s="34" t="n"/>
+      <c r="G118" s="36" t="n"/>
+      <c r="H118" s="34" t="n"/>
+      <c r="I118" s="34" t="n"/>
+      <c r="J118" s="58" t="n">
         <v>351</v>
       </c>
-      <c r="K118" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M118" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N118" s="1" t="n">
+      <c r="K118" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L118" s="36" t="n"/>
+      <c r="M118" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N118" s="40" t="n">
         <v>352</v>
       </c>
-      <c r="O118" s="31" t="n">
+      <c r="O118" s="58" t="n">
         <v>353</v>
       </c>
-      <c r="S118" t="inlineStr">
+      <c r="P118" s="34" t="n"/>
+      <c r="Q118" s="34" t="n"/>
+      <c r="R118" s="69" t="n"/>
+      <c r="S118" s="59" t="inlineStr">
         <is>
           <t>3 filtras, 5 linija</t>
         </is>
       </c>
-      <c r="X118" s="25" t="n">
+      <c r="X118" s="61" t="n">
         <v>5</v>
       </c>
+      <c r="Y118" s="34" t="n"/>
     </row>
     <row r="119">
-      <c r="J119" s="31" t="n">
+      <c r="C119" s="68" t="n"/>
+      <c r="D119" s="17" t="n"/>
+      <c r="E119" s="17" t="n"/>
+      <c r="F119" s="34" t="n"/>
+      <c r="G119" s="36" t="n"/>
+      <c r="H119" s="34" t="n"/>
+      <c r="I119" s="34" t="n"/>
+      <c r="J119" s="58" t="n">
         <v>351</v>
       </c>
-      <c r="K119" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M119" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N119" s="1" t="n">
+      <c r="K119" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L119" s="36" t="n"/>
+      <c r="M119" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N119" s="40" t="n">
         <v>352</v>
       </c>
-      <c r="O119" s="31" t="n">
+      <c r="O119" s="58" t="n">
         <v>353</v>
       </c>
-      <c r="X119" s="25" t="n">
+      <c r="P119" s="34" t="n"/>
+      <c r="Q119" s="34" t="n"/>
+      <c r="R119" s="17" t="n"/>
+      <c r="S119" s="17" t="n"/>
+      <c r="X119" s="61" t="n">
         <v>5</v>
       </c>
+      <c r="Y119" s="34" t="n"/>
     </row>
     <row r="120">
-      <c r="J120" s="31" t="n">
+      <c r="C120" s="68" t="n"/>
+      <c r="D120" s="17" t="n"/>
+      <c r="E120" s="17" t="n"/>
+      <c r="F120" s="34" t="n"/>
+      <c r="G120" s="36" t="n"/>
+      <c r="H120" s="34" t="n"/>
+      <c r="I120" s="34" t="n"/>
+      <c r="J120" s="58" t="n">
         <v>351</v>
       </c>
-      <c r="K120" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M120" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N120" s="1" t="n">
+      <c r="K120" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L120" s="36" t="n"/>
+      <c r="M120" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N120" s="40" t="n">
         <v>352</v>
       </c>
-      <c r="O120" s="31" t="n">
+      <c r="O120" s="58" t="n">
         <v>353</v>
       </c>
-      <c r="X120" s="25" t="n">
+      <c r="P120" s="34" t="n"/>
+      <c r="Q120" s="34" t="n"/>
+      <c r="R120" s="17" t="n"/>
+      <c r="S120" s="17" t="n"/>
+      <c r="X120" s="61" t="n">
         <v>5</v>
       </c>
+      <c r="Y120" s="34" t="n"/>
     </row>
     <row r="121">
-      <c r="J121" s="31" t="n">
+      <c r="C121" s="68" t="n"/>
+      <c r="D121" s="19" t="n"/>
+      <c r="E121" s="19" t="n"/>
+      <c r="F121" s="34" t="n"/>
+      <c r="G121" s="36" t="n"/>
+      <c r="H121" s="34" t="n"/>
+      <c r="I121" s="34" t="n"/>
+      <c r="J121" s="58" t="n">
         <v>351</v>
       </c>
-      <c r="K121" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M121" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N121" s="1" t="n">
+      <c r="K121" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L121" s="36" t="n"/>
+      <c r="M121" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N121" s="40" t="n">
         <v>352</v>
       </c>
-      <c r="O121" s="31" t="n">
+      <c r="O121" s="58" t="n">
         <v>353</v>
       </c>
-      <c r="X121" s="25" t="n">
+      <c r="P121" s="34" t="n"/>
+      <c r="Q121" s="34" t="n"/>
+      <c r="R121" s="19" t="n"/>
+      <c r="S121" s="19" t="n"/>
+      <c r="X121" s="61" t="n">
         <v>5</v>
+      </c>
+      <c r="Y121" s="34" t="n"/>
+    </row>
+    <row r="122">
+      <c r="L122" s="36" t="n"/>
+      <c r="M122" s="36" t="n"/>
+      <c r="N122" s="36" t="n"/>
+    </row>
+    <row r="123">
+      <c r="L123" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vm, m3</t>
+        </is>
+      </c>
+      <c r="M123" s="12" t="inlineStr">
+        <is>
+          <t>Suma t, min</t>
+        </is>
+      </c>
+      <c r="N123" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis Vo (l/min)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3222,12 +4390,12 @@
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="54" t="inlineStr">
+      <c r="A6" s="70" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B6" s="54" t="n">
+      <c r="B6" s="70" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="55" t="inlineStr">
@@ -3235,21 +4403,21 @@
           <t>Ekopartneris</t>
         </is>
       </c>
-      <c r="D6" s="56" t="n"/>
-      <c r="E6" s="56" t="n"/>
-      <c r="F6" s="56" t="n"/>
-      <c r="G6" s="56" t="n"/>
-      <c r="H6" s="57" t="n"/>
-      <c r="I6" s="56" t="n"/>
-      <c r="J6" s="56" t="n"/>
-      <c r="K6" s="57" t="n"/>
-      <c r="L6" s="57" t="n"/>
-      <c r="M6" s="58" t="n"/>
-      <c r="N6" s="59" t="n"/>
-      <c r="O6" s="60" t="n">
-        <v>3</v>
-      </c>
-      <c r="P6" s="61" t="inlineStr">
+      <c r="D6" s="71" t="n"/>
+      <c r="E6" s="71" t="n"/>
+      <c r="F6" s="71" t="n"/>
+      <c r="G6" s="71" t="n"/>
+      <c r="H6" s="72" t="n"/>
+      <c r="I6" s="71" t="n"/>
+      <c r="J6" s="71" t="n"/>
+      <c r="K6" s="72" t="n"/>
+      <c r="L6" s="72" t="n"/>
+      <c r="M6" s="73" t="n"/>
+      <c r="N6" s="74" t="n"/>
+      <c r="O6" s="75" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" s="76" t="inlineStr">
         <is>
           <t>5 linijos, 1 filtras</t>
         </is>
@@ -3259,19 +4427,19 @@
       <c r="A7" s="21" t="n"/>
       <c r="B7" s="21" t="n"/>
       <c r="C7" s="18" t="n"/>
-      <c r="D7" s="56" t="n"/>
-      <c r="E7" s="56" t="n"/>
-      <c r="F7" s="56" t="n"/>
-      <c r="G7" s="56" t="n"/>
-      <c r="H7" s="57" t="n"/>
-      <c r="I7" s="56" t="n"/>
-      <c r="J7" s="56" t="n"/>
-      <c r="K7" s="57" t="n"/>
-      <c r="L7" s="57" t="n"/>
-      <c r="M7" s="64" t="n"/>
-      <c r="N7" s="62" t="n"/>
+      <c r="D7" s="71" t="n"/>
+      <c r="E7" s="71" t="n"/>
+      <c r="F7" s="71" t="n"/>
+      <c r="G7" s="71" t="n"/>
+      <c r="H7" s="72" t="n"/>
+      <c r="I7" s="71" t="n"/>
+      <c r="J7" s="71" t="n"/>
+      <c r="K7" s="72" t="n"/>
+      <c r="L7" s="72" t="n"/>
+      <c r="M7" s="79" t="n"/>
+      <c r="N7" s="77" t="n"/>
       <c r="O7" s="44" t="n"/>
-      <c r="P7" s="61" t="inlineStr">
+      <c r="P7" s="76" t="inlineStr">
         <is>
           <t>5 linijos, 2 filtras</t>
         </is>
@@ -3281,19 +4449,19 @@
       <c r="A8" s="22" t="n"/>
       <c r="B8" s="22" t="n"/>
       <c r="C8" s="20" t="n"/>
-      <c r="D8" s="56" t="n"/>
-      <c r="E8" s="56" t="n"/>
-      <c r="F8" s="56" t="n"/>
-      <c r="G8" s="56" t="n"/>
-      <c r="H8" s="57" t="n"/>
-      <c r="I8" s="56" t="n"/>
-      <c r="J8" s="56" t="n"/>
-      <c r="K8" s="57" t="n"/>
-      <c r="L8" s="57" t="n"/>
-      <c r="M8" s="65" t="n"/>
-      <c r="N8" s="63" t="n"/>
+      <c r="D8" s="71" t="n"/>
+      <c r="E8" s="71" t="n"/>
+      <c r="F8" s="71" t="n"/>
+      <c r="G8" s="71" t="n"/>
+      <c r="H8" s="72" t="n"/>
+      <c r="I8" s="71" t="n"/>
+      <c r="J8" s="71" t="n"/>
+      <c r="K8" s="72" t="n"/>
+      <c r="L8" s="72" t="n"/>
+      <c r="M8" s="80" t="n"/>
+      <c r="N8" s="78" t="n"/>
       <c r="O8" s="44" t="n"/>
-      <c r="P8" s="61" t="inlineStr">
+      <c r="P8" s="76" t="inlineStr">
         <is>
           <t>5 linijos, 3 filtras</t>
         </is>
@@ -3445,10 +4613,10 @@
       <c r="O5" s="20" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="66" t="n">
+      <c r="A6" s="54" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="66" t="inlineStr">
+      <c r="B6" s="54" t="inlineStr">
         <is>
           <t>Ekopartneris</t>
         </is>
@@ -3456,18 +4624,18 @@
       <c r="C6" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="67" t="n"/>
+      <c r="D6" s="69" t="n"/>
       <c r="E6" s="37" t="n"/>
       <c r="F6" s="37" t="n"/>
       <c r="G6" s="37" t="n"/>
-      <c r="H6" s="67" t="n"/>
-      <c r="I6" s="68" t="n"/>
+      <c r="H6" s="69" t="n"/>
+      <c r="I6" s="59" t="n"/>
       <c r="J6" s="37" t="n"/>
       <c r="K6" s="37" t="n"/>
       <c r="L6" s="37" t="n"/>
       <c r="M6" s="36" t="n"/>
-      <c r="N6" s="68" t="n"/>
-      <c r="O6" s="69" t="inlineStr">
+      <c r="N6" s="59" t="n"/>
+      <c r="O6" s="81" t="inlineStr">
         <is>
           <t>5 linijos, 3 filtrai</t>
         </is>
@@ -3530,7 +4698,7 @@
       <c r="L9" s="37" t="n"/>
       <c r="M9" s="36" t="n"/>
       <c r="N9" s="17" t="n"/>
-      <c r="O9" s="70" t="inlineStr">
+      <c r="O9" s="82" t="inlineStr">
         <is>
           <t>Tuščiasis ėminys (mt)</t>
         </is>
@@ -3572,7 +4740,7 @@
       <c r="L11" s="37" t="n"/>
       <c r="M11" s="36" t="n"/>
       <c r="N11" s="17" t="n"/>
-      <c r="O11" s="70" t="inlineStr">
+      <c r="O11" s="82" t="inlineStr">
         <is>
           <t>Išplautos nuosėdos (mn)</t>
         </is>
@@ -3597,7 +4765,7 @@
       <c r="L12" s="37" t="n"/>
       <c r="M12" s="36" t="n"/>
       <c r="N12" s="17" t="n"/>
-      <c r="O12" s="70" t="inlineStr">
+      <c r="O12" s="82" t="inlineStr">
         <is>
           <t>Išvalytos ėminių sistemos tuščiasis ėminys (mIt)</t>
         </is>
@@ -3622,7 +4790,7 @@
       <c r="L13" s="37" t="n"/>
       <c r="M13" s="36" t="n"/>
       <c r="N13" s="17" t="n"/>
-      <c r="O13" s="70" t="inlineStr">
+      <c r="O13" s="82" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt1)</t>
         </is>
@@ -3647,7 +4815,7 @@
       <c r="L14" s="37" t="n"/>
       <c r="M14" s="36" t="n"/>
       <c r="N14" s="17" t="n"/>
-      <c r="O14" s="70" t="inlineStr">
+      <c r="O14" s="82" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt2)</t>
         </is>
@@ -3672,7 +4840,7 @@
       <c r="L15" s="37" t="n"/>
       <c r="M15" s="36" t="n"/>
       <c r="N15" s="17" t="n"/>
-      <c r="O15" s="70" t="inlineStr">
+      <c r="O15" s="82" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt3)</t>
         </is>
@@ -3693,7 +4861,7 @@
       <c r="L16" s="13" t="n"/>
       <c r="M16" s="36" t="n"/>
       <c r="N16" s="19" t="n"/>
-      <c r="O16" s="70" t="inlineStr">
+      <c r="O16" s="82" t="inlineStr">
         <is>
           <t>Tuščių indų ir išvalytos ėminių sistemos tuščiojo ėminio svorio pokytis (mItp)</t>
         </is>
@@ -3769,291 +4937,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumentas" ma:contentTypeID="0x010100BAB57CF81AE55C4698AAD22D302297F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Kurkite naują dokumentą." ma:contentTypeScope="" ma:versionID="49ab401eb4052690d2a2629974c22fd6">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="453e7e53-5eb2-45cf-b2ab-34c867e554b8" xmlns:ns3="aa0d983d-359a-438c-9953-3af1a8ac0831" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab9969d50e0b13c63bc5bd0499c928dc" ns2:_="" ns3:_="">
-    <xsd:import namespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8"/>
-    <xsd:import namespace="aa0d983d-359a-438c-9953-3af1a8ac0831"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="453e7e53-5eb2-45cf-b2ab-34c867e554b8" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="11" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="15" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="16" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Vaizdų žymės" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="993cf2ba-b7a7-49f7-97d1-76e12a88c412" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="23" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="aa0d983d-359a-438c-9953-3af1a8ac0831" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{82c4fa3c-500e-4213-91e5-1b9e2014ea63}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="aa0d983d-359a-438c-9953-3af1a8ac0831">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="21" nillable="true" ma:displayName="Bendrinama su" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="22" nillable="true" ma:displayName="Bendrinta su išsamia informacija" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Turinio tipas"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Antraštė"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="453e7e53-5eb2-45cf-b2ab-34c867e554b8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="aa0d983d-359a-438c-9953-3af1a8ac0831" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E37D55A-15C8-4903-A8FD-EE2F5DBC632A}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3937C6DD-134E-4BCD-9F41-E129244DFC87}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BFE8EC0-DB58-4BAD-84D0-3A9E4C6B158D}"/>
 </file>
--- a/Rezultatai.xlsx
+++ b/Rezultatai.xlsx
@@ -236,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -411,8 +411,20 @@
     <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1484,7 +1496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:Y123"/>
+  <dimension ref="A2:Y126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1882,11 +1894,21 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="68" t="n"/>
-      <c r="B14" s="68" t="n"/>
-      <c r="C14" s="68" t="n"/>
-      <c r="D14" s="69" t="n"/>
-      <c r="E14" s="69" t="n"/>
+      <c r="A14" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B14" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D14" s="68" t="n"/>
+      <c r="E14" s="68" t="n"/>
       <c r="F14" s="34" t="n"/>
       <c r="G14" s="36" t="n"/>
       <c r="H14" s="34" t="n"/>
@@ -1909,7 +1931,7 @@
       </c>
       <c r="P14" s="34" t="n"/>
       <c r="Q14" s="34" t="n"/>
-      <c r="R14" s="69" t="n"/>
+      <c r="R14" s="68" t="n"/>
       <c r="S14" s="59" t="inlineStr">
         <is>
           <t>1 filtras, 2 linija</t>
@@ -1921,7 +1943,9 @@
       <c r="Y14" s="34" t="n"/>
     </row>
     <row r="15">
-      <c r="C15" s="68" t="n"/>
+      <c r="A15" s="17" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="18" t="n"/>
       <c r="D15" s="17" t="n"/>
       <c r="E15" s="17" t="n"/>
       <c r="F15" s="34" t="n"/>
@@ -1954,7 +1978,9 @@
       <c r="Y15" s="34" t="n"/>
     </row>
     <row r="16">
-      <c r="C16" s="68" t="n"/>
+      <c r="A16" s="17" t="n"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="18" t="n"/>
       <c r="D16" s="17" t="n"/>
       <c r="E16" s="17" t="n"/>
       <c r="F16" s="34" t="n"/>
@@ -1987,7 +2013,9 @@
       <c r="Y16" s="34" t="n"/>
     </row>
     <row r="17">
-      <c r="C17" s="68" t="n"/>
+      <c r="A17" s="19" t="n"/>
+      <c r="B17" s="19" t="n"/>
+      <c r="C17" s="20" t="n"/>
       <c r="D17" s="19" t="n"/>
       <c r="E17" s="19" t="n"/>
       <c r="F17" s="34" t="n"/>
@@ -2042,11 +2070,21 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="68" t="n"/>
-      <c r="B22" s="68" t="n"/>
-      <c r="C22" s="68" t="n"/>
-      <c r="D22" s="69" t="n"/>
-      <c r="E22" s="69" t="n"/>
+      <c r="A22" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B22" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D22" s="68" t="n"/>
+      <c r="E22" s="68" t="n"/>
       <c r="F22" s="34" t="n"/>
       <c r="G22" s="36" t="n"/>
       <c r="H22" s="34" t="n"/>
@@ -2069,7 +2107,7 @@
       </c>
       <c r="P22" s="34" t="n"/>
       <c r="Q22" s="34" t="n"/>
-      <c r="R22" s="69" t="n"/>
+      <c r="R22" s="68" t="n"/>
       <c r="S22" s="59" t="inlineStr">
         <is>
           <t>1 filtras, 3 linija</t>
@@ -2081,7 +2119,9 @@
       <c r="Y22" s="34" t="n"/>
     </row>
     <row r="23">
-      <c r="C23" s="68" t="n"/>
+      <c r="A23" s="17" t="n"/>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="18" t="n"/>
       <c r="D23" s="17" t="n"/>
       <c r="E23" s="17" t="n"/>
       <c r="F23" s="34" t="n"/>
@@ -2114,7 +2154,9 @@
       <c r="Y23" s="34" t="n"/>
     </row>
     <row r="24">
-      <c r="C24" s="68" t="n"/>
+      <c r="A24" s="17" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="18" t="n"/>
       <c r="D24" s="17" t="n"/>
       <c r="E24" s="17" t="n"/>
       <c r="F24" s="34" t="n"/>
@@ -2147,7 +2189,9 @@
       <c r="Y24" s="34" t="n"/>
     </row>
     <row r="25">
-      <c r="C25" s="68" t="n"/>
+      <c r="A25" s="19" t="n"/>
+      <c r="B25" s="19" t="n"/>
+      <c r="C25" s="20" t="n"/>
       <c r="D25" s="19" t="n"/>
       <c r="E25" s="19" t="n"/>
       <c r="F25" s="34" t="n"/>
@@ -2202,11 +2246,21 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="68" t="n"/>
-      <c r="B30" s="68" t="n"/>
-      <c r="C30" s="68" t="n"/>
-      <c r="D30" s="69" t="n"/>
-      <c r="E30" s="69" t="n"/>
+      <c r="A30" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B30" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D30" s="68" t="n"/>
+      <c r="E30" s="68" t="n"/>
       <c r="F30" s="34" t="n"/>
       <c r="G30" s="36" t="n"/>
       <c r="H30" s="34" t="n"/>
@@ -2229,7 +2283,7 @@
       </c>
       <c r="P30" s="34" t="n"/>
       <c r="Q30" s="34" t="n"/>
-      <c r="R30" s="69" t="n"/>
+      <c r="R30" s="68" t="n"/>
       <c r="S30" s="59" t="inlineStr">
         <is>
           <t>1 filtras, 4 linija</t>
@@ -2241,7 +2295,9 @@
       <c r="Y30" s="34" t="n"/>
     </row>
     <row r="31">
-      <c r="C31" s="68" t="n"/>
+      <c r="A31" s="17" t="n"/>
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="18" t="n"/>
       <c r="D31" s="17" t="n"/>
       <c r="E31" s="17" t="n"/>
       <c r="F31" s="34" t="n"/>
@@ -2274,7 +2330,9 @@
       <c r="Y31" s="34" t="n"/>
     </row>
     <row r="32">
-      <c r="C32" s="68" t="n"/>
+      <c r="A32" s="17" t="n"/>
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="18" t="n"/>
       <c r="D32" s="17" t="n"/>
       <c r="E32" s="17" t="n"/>
       <c r="F32" s="34" t="n"/>
@@ -2307,7 +2365,9 @@
       <c r="Y32" s="34" t="n"/>
     </row>
     <row r="33">
-      <c r="C33" s="68" t="n"/>
+      <c r="A33" s="19" t="n"/>
+      <c r="B33" s="19" t="n"/>
+      <c r="C33" s="20" t="n"/>
       <c r="D33" s="19" t="n"/>
       <c r="E33" s="19" t="n"/>
       <c r="F33" s="34" t="n"/>
@@ -2362,11 +2422,21 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="68" t="n"/>
-      <c r="B38" s="68" t="n"/>
-      <c r="C38" s="68" t="n"/>
-      <c r="D38" s="69" t="n"/>
-      <c r="E38" s="69" t="n"/>
+      <c r="A38" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B38" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D38" s="68" t="n"/>
+      <c r="E38" s="68" t="n"/>
       <c r="F38" s="34" t="n"/>
       <c r="G38" s="36" t="n"/>
       <c r="H38" s="34" t="n"/>
@@ -2389,7 +2459,7 @@
       </c>
       <c r="P38" s="34" t="n"/>
       <c r="Q38" s="34" t="n"/>
-      <c r="R38" s="69" t="n"/>
+      <c r="R38" s="68" t="n"/>
       <c r="S38" s="59" t="inlineStr">
         <is>
           <t>1 filtras, 5 linija</t>
@@ -2401,7 +2471,9 @@
       <c r="Y38" s="34" t="n"/>
     </row>
     <row r="39">
-      <c r="C39" s="68" t="n"/>
+      <c r="A39" s="17" t="n"/>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="18" t="n"/>
       <c r="D39" s="17" t="n"/>
       <c r="E39" s="17" t="n"/>
       <c r="F39" s="34" t="n"/>
@@ -2434,7 +2506,9 @@
       <c r="Y39" s="34" t="n"/>
     </row>
     <row r="40">
-      <c r="C40" s="68" t="n"/>
+      <c r="A40" s="17" t="n"/>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="18" t="n"/>
       <c r="D40" s="17" t="n"/>
       <c r="E40" s="17" t="n"/>
       <c r="F40" s="34" t="n"/>
@@ -2467,7 +2541,9 @@
       <c r="Y40" s="34" t="n"/>
     </row>
     <row r="41">
-      <c r="C41" s="68" t="n"/>
+      <c r="A41" s="19" t="n"/>
+      <c r="B41" s="19" t="n"/>
+      <c r="C41" s="20" t="n"/>
       <c r="D41" s="19" t="n"/>
       <c r="E41" s="19" t="n"/>
       <c r="F41" s="34" t="n"/>
@@ -2522,11 +2598,21 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="68" t="n"/>
-      <c r="B46" s="68" t="n"/>
-      <c r="C46" s="68" t="n"/>
-      <c r="D46" s="69" t="n"/>
-      <c r="E46" s="69" t="n"/>
+      <c r="A46" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B46" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D46" s="68" t="n"/>
+      <c r="E46" s="68" t="n"/>
       <c r="F46" s="34" t="n"/>
       <c r="G46" s="36" t="n"/>
       <c r="H46" s="34" t="n"/>
@@ -2549,7 +2635,7 @@
       </c>
       <c r="P46" s="34" t="n"/>
       <c r="Q46" s="34" t="n"/>
-      <c r="R46" s="69" t="n"/>
+      <c r="R46" s="68" t="n"/>
       <c r="S46" s="59" t="inlineStr">
         <is>
           <t>2 filtras, 1 linija</t>
@@ -2561,7 +2647,9 @@
       <c r="Y46" s="34" t="n"/>
     </row>
     <row r="47">
-      <c r="C47" s="68" t="n"/>
+      <c r="A47" s="17" t="n"/>
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="18" t="n"/>
       <c r="D47" s="17" t="n"/>
       <c r="E47" s="17" t="n"/>
       <c r="F47" s="34" t="n"/>
@@ -2594,7 +2682,9 @@
       <c r="Y47" s="34" t="n"/>
     </row>
     <row r="48">
-      <c r="C48" s="68" t="n"/>
+      <c r="A48" s="17" t="n"/>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="18" t="n"/>
       <c r="D48" s="17" t="n"/>
       <c r="E48" s="17" t="n"/>
       <c r="F48" s="34" t="n"/>
@@ -2627,7 +2717,9 @@
       <c r="Y48" s="34" t="n"/>
     </row>
     <row r="49">
-      <c r="C49" s="68" t="n"/>
+      <c r="A49" s="19" t="n"/>
+      <c r="B49" s="19" t="n"/>
+      <c r="C49" s="20" t="n"/>
       <c r="D49" s="19" t="n"/>
       <c r="E49" s="19" t="n"/>
       <c r="F49" s="34" t="n"/>
@@ -2682,11 +2774,21 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="68" t="n"/>
-      <c r="B54" s="68" t="n"/>
-      <c r="C54" s="68" t="n"/>
-      <c r="D54" s="69" t="n"/>
-      <c r="E54" s="69" t="n"/>
+      <c r="A54" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B54" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C54" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D54" s="68" t="n"/>
+      <c r="E54" s="68" t="n"/>
       <c r="F54" s="34" t="n"/>
       <c r="G54" s="36" t="n"/>
       <c r="H54" s="34" t="n"/>
@@ -2709,7 +2811,7 @@
       </c>
       <c r="P54" s="34" t="n"/>
       <c r="Q54" s="34" t="n"/>
-      <c r="R54" s="69" t="n"/>
+      <c r="R54" s="68" t="n"/>
       <c r="S54" s="59" t="inlineStr">
         <is>
           <t>2 filtras, 2 linija</t>
@@ -2721,7 +2823,9 @@
       <c r="Y54" s="34" t="n"/>
     </row>
     <row r="55">
-      <c r="C55" s="68" t="n"/>
+      <c r="A55" s="17" t="n"/>
+      <c r="B55" s="17" t="n"/>
+      <c r="C55" s="18" t="n"/>
       <c r="D55" s="17" t="n"/>
       <c r="E55" s="17" t="n"/>
       <c r="F55" s="34" t="n"/>
@@ -2754,7 +2858,9 @@
       <c r="Y55" s="34" t="n"/>
     </row>
     <row r="56">
-      <c r="C56" s="68" t="n"/>
+      <c r="A56" s="17" t="n"/>
+      <c r="B56" s="17" t="n"/>
+      <c r="C56" s="18" t="n"/>
       <c r="D56" s="17" t="n"/>
       <c r="E56" s="17" t="n"/>
       <c r="F56" s="34" t="n"/>
@@ -2787,7 +2893,9 @@
       <c r="Y56" s="34" t="n"/>
     </row>
     <row r="57">
-      <c r="C57" s="68" t="n"/>
+      <c r="A57" s="19" t="n"/>
+      <c r="B57" s="19" t="n"/>
+      <c r="C57" s="20" t="n"/>
       <c r="D57" s="19" t="n"/>
       <c r="E57" s="19" t="n"/>
       <c r="F57" s="34" t="n"/>
@@ -2842,11 +2950,21 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="68" t="n"/>
-      <c r="B62" s="68" t="n"/>
-      <c r="C62" s="68" t="n"/>
-      <c r="D62" s="69" t="n"/>
-      <c r="E62" s="69" t="n"/>
+      <c r="A62" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B62" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C62" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D62" s="68" t="n"/>
+      <c r="E62" s="68" t="n"/>
       <c r="F62" s="34" t="n"/>
       <c r="G62" s="36" t="n"/>
       <c r="H62" s="34" t="n"/>
@@ -2869,7 +2987,7 @@
       </c>
       <c r="P62" s="34" t="n"/>
       <c r="Q62" s="34" t="n"/>
-      <c r="R62" s="69" t="n"/>
+      <c r="R62" s="68" t="n"/>
       <c r="S62" s="59" t="inlineStr">
         <is>
           <t>2 filtras, 3 linija</t>
@@ -2881,7 +2999,9 @@
       <c r="Y62" s="34" t="n"/>
     </row>
     <row r="63">
-      <c r="C63" s="68" t="n"/>
+      <c r="A63" s="17" t="n"/>
+      <c r="B63" s="17" t="n"/>
+      <c r="C63" s="18" t="n"/>
       <c r="D63" s="17" t="n"/>
       <c r="E63" s="17" t="n"/>
       <c r="F63" s="34" t="n"/>
@@ -2914,7 +3034,9 @@
       <c r="Y63" s="34" t="n"/>
     </row>
     <row r="64">
-      <c r="C64" s="68" t="n"/>
+      <c r="A64" s="17" t="n"/>
+      <c r="B64" s="17" t="n"/>
+      <c r="C64" s="18" t="n"/>
       <c r="D64" s="17" t="n"/>
       <c r="E64" s="17" t="n"/>
       <c r="F64" s="34" t="n"/>
@@ -2947,7 +3069,9 @@
       <c r="Y64" s="34" t="n"/>
     </row>
     <row r="65">
-      <c r="C65" s="68" t="n"/>
+      <c r="A65" s="19" t="n"/>
+      <c r="B65" s="19" t="n"/>
+      <c r="C65" s="20" t="n"/>
       <c r="D65" s="19" t="n"/>
       <c r="E65" s="19" t="n"/>
       <c r="F65" s="34" t="n"/>
@@ -3002,11 +3126,21 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="68" t="n"/>
-      <c r="B70" s="68" t="n"/>
-      <c r="C70" s="68" t="n"/>
-      <c r="D70" s="69" t="n"/>
-      <c r="E70" s="69" t="n"/>
+      <c r="A70" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B70" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C70" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D70" s="68" t="n"/>
+      <c r="E70" s="68" t="n"/>
       <c r="F70" s="34" t="n"/>
       <c r="G70" s="36" t="n"/>
       <c r="H70" s="34" t="n"/>
@@ -3029,7 +3163,7 @@
       </c>
       <c r="P70" s="34" t="n"/>
       <c r="Q70" s="34" t="n"/>
-      <c r="R70" s="69" t="n"/>
+      <c r="R70" s="68" t="n"/>
       <c r="S70" s="59" t="inlineStr">
         <is>
           <t>2 filtras, 4 linija</t>
@@ -3041,7 +3175,9 @@
       <c r="Y70" s="34" t="n"/>
     </row>
     <row r="71">
-      <c r="C71" s="68" t="n"/>
+      <c r="A71" s="17" t="n"/>
+      <c r="B71" s="17" t="n"/>
+      <c r="C71" s="18" t="n"/>
       <c r="D71" s="17" t="n"/>
       <c r="E71" s="17" t="n"/>
       <c r="F71" s="34" t="n"/>
@@ -3074,7 +3210,9 @@
       <c r="Y71" s="34" t="n"/>
     </row>
     <row r="72">
-      <c r="C72" s="68" t="n"/>
+      <c r="A72" s="17" t="n"/>
+      <c r="B72" s="17" t="n"/>
+      <c r="C72" s="18" t="n"/>
       <c r="D72" s="17" t="n"/>
       <c r="E72" s="17" t="n"/>
       <c r="F72" s="34" t="n"/>
@@ -3107,7 +3245,9 @@
       <c r="Y72" s="34" t="n"/>
     </row>
     <row r="73">
-      <c r="C73" s="68" t="n"/>
+      <c r="A73" s="19" t="n"/>
+      <c r="B73" s="19" t="n"/>
+      <c r="C73" s="20" t="n"/>
       <c r="D73" s="19" t="n"/>
       <c r="E73" s="19" t="n"/>
       <c r="F73" s="34" t="n"/>
@@ -3162,11 +3302,21 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="68" t="n"/>
-      <c r="B78" s="68" t="n"/>
-      <c r="C78" s="68" t="n"/>
-      <c r="D78" s="69" t="n"/>
-      <c r="E78" s="69" t="n"/>
+      <c r="A78" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B78" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C78" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D78" s="68" t="n"/>
+      <c r="E78" s="68" t="n"/>
       <c r="F78" s="34" t="n"/>
       <c r="G78" s="36" t="n"/>
       <c r="H78" s="34" t="n"/>
@@ -3189,7 +3339,7 @@
       </c>
       <c r="P78" s="34" t="n"/>
       <c r="Q78" s="34" t="n"/>
-      <c r="R78" s="69" t="n"/>
+      <c r="R78" s="68" t="n"/>
       <c r="S78" s="59" t="inlineStr">
         <is>
           <t>2 filtras, 5 linija</t>
@@ -3201,7 +3351,9 @@
       <c r="Y78" s="34" t="n"/>
     </row>
     <row r="79">
-      <c r="C79" s="68" t="n"/>
+      <c r="A79" s="17" t="n"/>
+      <c r="B79" s="17" t="n"/>
+      <c r="C79" s="18" t="n"/>
       <c r="D79" s="17" t="n"/>
       <c r="E79" s="17" t="n"/>
       <c r="F79" s="34" t="n"/>
@@ -3234,7 +3386,9 @@
       <c r="Y79" s="34" t="n"/>
     </row>
     <row r="80">
-      <c r="C80" s="68" t="n"/>
+      <c r="A80" s="17" t="n"/>
+      <c r="B80" s="17" t="n"/>
+      <c r="C80" s="18" t="n"/>
       <c r="D80" s="17" t="n"/>
       <c r="E80" s="17" t="n"/>
       <c r="F80" s="34" t="n"/>
@@ -3267,7 +3421,9 @@
       <c r="Y80" s="34" t="n"/>
     </row>
     <row r="81">
-      <c r="C81" s="68" t="n"/>
+      <c r="A81" s="19" t="n"/>
+      <c r="B81" s="19" t="n"/>
+      <c r="C81" s="20" t="n"/>
       <c r="D81" s="19" t="n"/>
       <c r="E81" s="19" t="n"/>
       <c r="F81" s="34" t="n"/>
@@ -3322,11 +3478,21 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="68" t="n"/>
-      <c r="B86" s="68" t="n"/>
-      <c r="C86" s="68" t="n"/>
-      <c r="D86" s="69" t="n"/>
-      <c r="E86" s="69" t="n"/>
+      <c r="A86" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B86" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C86" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D86" s="68" t="n"/>
+      <c r="E86" s="68" t="n"/>
       <c r="F86" s="34" t="n"/>
       <c r="G86" s="36" t="n"/>
       <c r="H86" s="34" t="n"/>
@@ -3349,7 +3515,7 @@
       </c>
       <c r="P86" s="34" t="n"/>
       <c r="Q86" s="34" t="n"/>
-      <c r="R86" s="69" t="n"/>
+      <c r="R86" s="68" t="n"/>
       <c r="S86" s="59" t="inlineStr">
         <is>
           <t>3 filtras, 1 linija</t>
@@ -3361,7 +3527,9 @@
       <c r="Y86" s="34" t="n"/>
     </row>
     <row r="87">
-      <c r="C87" s="68" t="n"/>
+      <c r="A87" s="17" t="n"/>
+      <c r="B87" s="17" t="n"/>
+      <c r="C87" s="18" t="n"/>
       <c r="D87" s="17" t="n"/>
       <c r="E87" s="17" t="n"/>
       <c r="F87" s="34" t="n"/>
@@ -3394,7 +3562,9 @@
       <c r="Y87" s="34" t="n"/>
     </row>
     <row r="88">
-      <c r="C88" s="68" t="n"/>
+      <c r="A88" s="17" t="n"/>
+      <c r="B88" s="17" t="n"/>
+      <c r="C88" s="18" t="n"/>
       <c r="D88" s="17" t="n"/>
       <c r="E88" s="17" t="n"/>
       <c r="F88" s="34" t="n"/>
@@ -3427,7 +3597,9 @@
       <c r="Y88" s="34" t="n"/>
     </row>
     <row r="89">
-      <c r="C89" s="68" t="n"/>
+      <c r="A89" s="19" t="n"/>
+      <c r="B89" s="19" t="n"/>
+      <c r="C89" s="20" t="n"/>
       <c r="D89" s="19" t="n"/>
       <c r="E89" s="19" t="n"/>
       <c r="F89" s="34" t="n"/>
@@ -3482,11 +3654,21 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="68" t="n"/>
-      <c r="B94" s="68" t="n"/>
-      <c r="C94" s="68" t="n"/>
-      <c r="D94" s="69" t="n"/>
-      <c r="E94" s="69" t="n"/>
+      <c r="A94" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B94" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C94" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D94" s="68" t="n"/>
+      <c r="E94" s="68" t="n"/>
       <c r="F94" s="34" t="n"/>
       <c r="G94" s="36" t="n"/>
       <c r="H94" s="34" t="n"/>
@@ -3509,7 +3691,7 @@
       </c>
       <c r="P94" s="34" t="n"/>
       <c r="Q94" s="34" t="n"/>
-      <c r="R94" s="69" t="n"/>
+      <c r="R94" s="68" t="n"/>
       <c r="S94" s="59" t="inlineStr">
         <is>
           <t>3 filtras, 2 linija</t>
@@ -3521,7 +3703,9 @@
       <c r="Y94" s="34" t="n"/>
     </row>
     <row r="95">
-      <c r="C95" s="68" t="n"/>
+      <c r="A95" s="17" t="n"/>
+      <c r="B95" s="17" t="n"/>
+      <c r="C95" s="18" t="n"/>
       <c r="D95" s="17" t="n"/>
       <c r="E95" s="17" t="n"/>
       <c r="F95" s="34" t="n"/>
@@ -3554,7 +3738,9 @@
       <c r="Y95" s="34" t="n"/>
     </row>
     <row r="96">
-      <c r="C96" s="68" t="n"/>
+      <c r="A96" s="17" t="n"/>
+      <c r="B96" s="17" t="n"/>
+      <c r="C96" s="18" t="n"/>
       <c r="D96" s="17" t="n"/>
       <c r="E96" s="17" t="n"/>
       <c r="F96" s="34" t="n"/>
@@ -3587,7 +3773,9 @@
       <c r="Y96" s="34" t="n"/>
     </row>
     <row r="97">
-      <c r="C97" s="68" t="n"/>
+      <c r="A97" s="19" t="n"/>
+      <c r="B97" s="19" t="n"/>
+      <c r="C97" s="20" t="n"/>
       <c r="D97" s="19" t="n"/>
       <c r="E97" s="19" t="n"/>
       <c r="F97" s="34" t="n"/>
@@ -3642,11 +3830,21 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="68" t="n"/>
-      <c r="B102" s="68" t="n"/>
-      <c r="C102" s="68" t="n"/>
-      <c r="D102" s="69" t="n"/>
-      <c r="E102" s="69" t="n"/>
+      <c r="A102" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B102" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C102" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D102" s="68" t="n"/>
+      <c r="E102" s="68" t="n"/>
       <c r="F102" s="34" t="n"/>
       <c r="G102" s="36" t="n"/>
       <c r="H102" s="34" t="n"/>
@@ -3669,7 +3867,7 @@
       </c>
       <c r="P102" s="34" t="n"/>
       <c r="Q102" s="34" t="n"/>
-      <c r="R102" s="69" t="n"/>
+      <c r="R102" s="68" t="n"/>
       <c r="S102" s="59" t="inlineStr">
         <is>
           <t>3 filtras, 3 linija</t>
@@ -3681,7 +3879,9 @@
       <c r="Y102" s="34" t="n"/>
     </row>
     <row r="103">
-      <c r="C103" s="68" t="n"/>
+      <c r="A103" s="17" t="n"/>
+      <c r="B103" s="17" t="n"/>
+      <c r="C103" s="18" t="n"/>
       <c r="D103" s="17" t="n"/>
       <c r="E103" s="17" t="n"/>
       <c r="F103" s="34" t="n"/>
@@ -3714,7 +3914,9 @@
       <c r="Y103" s="34" t="n"/>
     </row>
     <row r="104">
-      <c r="C104" s="68" t="n"/>
+      <c r="A104" s="17" t="n"/>
+      <c r="B104" s="17" t="n"/>
+      <c r="C104" s="18" t="n"/>
       <c r="D104" s="17" t="n"/>
       <c r="E104" s="17" t="n"/>
       <c r="F104" s="34" t="n"/>
@@ -3747,7 +3949,9 @@
       <c r="Y104" s="34" t="n"/>
     </row>
     <row r="105">
-      <c r="C105" s="68" t="n"/>
+      <c r="A105" s="19" t="n"/>
+      <c r="B105" s="19" t="n"/>
+      <c r="C105" s="20" t="n"/>
       <c r="D105" s="19" t="n"/>
       <c r="E105" s="19" t="n"/>
       <c r="F105" s="34" t="n"/>
@@ -3802,11 +4006,21 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="68" t="n"/>
-      <c r="B110" s="68" t="n"/>
-      <c r="C110" s="68" t="n"/>
-      <c r="D110" s="69" t="n"/>
-      <c r="E110" s="69" t="n"/>
+      <c r="A110" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B110" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C110" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D110" s="68" t="n"/>
+      <c r="E110" s="68" t="n"/>
       <c r="F110" s="34" t="n"/>
       <c r="G110" s="36" t="n"/>
       <c r="H110" s="34" t="n"/>
@@ -3829,7 +4043,7 @@
       </c>
       <c r="P110" s="34" t="n"/>
       <c r="Q110" s="34" t="n"/>
-      <c r="R110" s="69" t="n"/>
+      <c r="R110" s="68" t="n"/>
       <c r="S110" s="59" t="inlineStr">
         <is>
           <t>3 filtras, 4 linija</t>
@@ -3841,7 +4055,9 @@
       <c r="Y110" s="34" t="n"/>
     </row>
     <row r="111">
-      <c r="C111" s="68" t="n"/>
+      <c r="A111" s="17" t="n"/>
+      <c r="B111" s="17" t="n"/>
+      <c r="C111" s="18" t="n"/>
       <c r="D111" s="17" t="n"/>
       <c r="E111" s="17" t="n"/>
       <c r="F111" s="34" t="n"/>
@@ -3874,7 +4090,9 @@
       <c r="Y111" s="34" t="n"/>
     </row>
     <row r="112">
-      <c r="C112" s="68" t="n"/>
+      <c r="A112" s="17" t="n"/>
+      <c r="B112" s="17" t="n"/>
+      <c r="C112" s="18" t="n"/>
       <c r="D112" s="17" t="n"/>
       <c r="E112" s="17" t="n"/>
       <c r="F112" s="34" t="n"/>
@@ -3907,7 +4125,9 @@
       <c r="Y112" s="34" t="n"/>
     </row>
     <row r="113">
-      <c r="C113" s="68" t="n"/>
+      <c r="A113" s="19" t="n"/>
+      <c r="B113" s="19" t="n"/>
+      <c r="C113" s="20" t="n"/>
       <c r="D113" s="19" t="n"/>
       <c r="E113" s="19" t="n"/>
       <c r="F113" s="34" t="n"/>
@@ -3962,11 +4182,21 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="68" t="n"/>
-      <c r="B118" s="68" t="n"/>
-      <c r="C118" s="68" t="n"/>
-      <c r="D118" s="69" t="n"/>
-      <c r="E118" s="69" t="n"/>
+      <c r="A118" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B118" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C118" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D118" s="68" t="n"/>
+      <c r="E118" s="68" t="n"/>
       <c r="F118" s="34" t="n"/>
       <c r="G118" s="36" t="n"/>
       <c r="H118" s="34" t="n"/>
@@ -3989,7 +4219,7 @@
       </c>
       <c r="P118" s="34" t="n"/>
       <c r="Q118" s="34" t="n"/>
-      <c r="R118" s="69" t="n"/>
+      <c r="R118" s="68" t="n"/>
       <c r="S118" s="59" t="inlineStr">
         <is>
           <t>3 filtras, 5 linija</t>
@@ -4001,7 +4231,9 @@
       <c r="Y118" s="34" t="n"/>
     </row>
     <row r="119">
-      <c r="C119" s="68" t="n"/>
+      <c r="A119" s="17" t="n"/>
+      <c r="B119" s="17" t="n"/>
+      <c r="C119" s="18" t="n"/>
       <c r="D119" s="17" t="n"/>
       <c r="E119" s="17" t="n"/>
       <c r="F119" s="34" t="n"/>
@@ -4034,7 +4266,9 @@
       <c r="Y119" s="34" t="n"/>
     </row>
     <row r="120">
-      <c r="C120" s="68" t="n"/>
+      <c r="A120" s="17" t="n"/>
+      <c r="B120" s="17" t="n"/>
+      <c r="C120" s="18" t="n"/>
       <c r="D120" s="17" t="n"/>
       <c r="E120" s="17" t="n"/>
       <c r="F120" s="34" t="n"/>
@@ -4067,7 +4301,9 @@
       <c r="Y120" s="34" t="n"/>
     </row>
     <row r="121">
-      <c r="C121" s="68" t="n"/>
+      <c r="A121" s="19" t="n"/>
+      <c r="B121" s="19" t="n"/>
+      <c r="C121" s="20" t="n"/>
       <c r="D121" s="19" t="n"/>
       <c r="E121" s="19" t="n"/>
       <c r="F121" s="34" t="n"/>
@@ -4121,10 +4357,40 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="M125" s="69" t="n"/>
+      <c r="N125" s="69" t="n"/>
+    </row>
+    <row r="126">
+      <c r="M126" s="12" t="inlineStr">
+        <is>
+          <t>Viso suma t, min</t>
+        </is>
+      </c>
+      <c r="N126" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vidurkių vidurkis Vo vid (l/min) </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="16">
     <mergeCell ref="A2:V2"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="C70:C73"/>
+    <mergeCell ref="C102:C105"/>
+    <mergeCell ref="C118:C121"/>
+    <mergeCell ref="C78:C81"/>
+    <mergeCell ref="C94:C97"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="C30:C33"/>
     <mergeCell ref="C6:C9"/>
+    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="C54:C57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4136,7 +4402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:N9"/>
+  <dimension ref="A2:N126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4235,39 +4501,1401 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="54" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="54" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="55" t="inlineStr">
         <is>
           <t>Ekopartneris</t>
         </is>
       </c>
+      <c r="D6" s="34" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="70" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="34" t="n"/>
+      <c r="I6" s="36" t="n"/>
+      <c r="J6" s="36" t="n"/>
+      <c r="K6" s="36" t="n"/>
+      <c r="L6" s="70" t="n"/>
+      <c r="M6" s="68" t="n"/>
+      <c r="N6" s="68" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="17" t="n"/>
       <c r="B7" s="17" t="n"/>
       <c r="C7" s="18" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="36" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="36" t="n"/>
+      <c r="J7" s="36" t="n"/>
+      <c r="K7" s="36" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="17" t="n"/>
       <c r="B8" s="17" t="n"/>
       <c r="C8" s="18" t="n"/>
+      <c r="D8" s="34" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="34" t="n"/>
+      <c r="I8" s="36" t="n"/>
+      <c r="J8" s="36" t="n"/>
+      <c r="K8" s="36" t="n"/>
+      <c r="L8" s="17" t="n"/>
+      <c r="M8" s="17" t="n"/>
+      <c r="N8" s="17" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="19" t="n"/>
       <c r="B9" s="19" t="n"/>
       <c r="C9" s="20" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="36" t="n"/>
+      <c r="J9" s="36" t="n"/>
+      <c r="K9" s="36" t="n"/>
+      <c r="L9" s="19" t="n"/>
+      <c r="M9" s="19" t="n"/>
+      <c r="N9" s="19" t="n"/>
+    </row>
+    <row r="10">
+      <c r="G10" s="71" t="n"/>
+      <c r="I10" s="71" t="n"/>
+    </row>
+    <row r="11">
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis qn, (kg/m3)</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vmk (m3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B14" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D14" s="34" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="70" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="34" t="n"/>
+      <c r="I14" s="36" t="n"/>
+      <c r="J14" s="36" t="n"/>
+      <c r="K14" s="36" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="68" t="n"/>
+      <c r="N14" s="68" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="34" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="34" t="n"/>
+      <c r="I15" s="36" t="n"/>
+      <c r="J15" s="36" t="n"/>
+      <c r="K15" s="36" t="n"/>
+      <c r="L15" s="17" t="n"/>
+      <c r="M15" s="17" t="n"/>
+      <c r="N15" s="17" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="n"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="17" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="34" t="n"/>
+      <c r="I16" s="36" t="n"/>
+      <c r="J16" s="36" t="n"/>
+      <c r="K16" s="36" t="n"/>
+      <c r="L16" s="17" t="n"/>
+      <c r="M16" s="17" t="n"/>
+      <c r="N16" s="17" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="n"/>
+      <c r="B17" s="19" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="34" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="34" t="n"/>
+      <c r="I17" s="36" t="n"/>
+      <c r="J17" s="36" t="n"/>
+      <c r="K17" s="36" t="n"/>
+      <c r="L17" s="19" t="n"/>
+      <c r="M17" s="19" t="n"/>
+      <c r="N17" s="19" t="n"/>
+    </row>
+    <row r="18">
+      <c r="G18" s="71" t="n"/>
+      <c r="I18" s="71" t="n"/>
+    </row>
+    <row r="19">
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis qn, (kg/m3)</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vmk (m3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B22" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D22" s="34" t="n"/>
+      <c r="E22" s="36" t="n"/>
+      <c r="F22" s="70" t="n"/>
+      <c r="G22" s="36" t="n"/>
+      <c r="H22" s="34" t="n"/>
+      <c r="I22" s="36" t="n"/>
+      <c r="J22" s="36" t="n"/>
+      <c r="K22" s="36" t="n"/>
+      <c r="L22" s="70" t="n"/>
+      <c r="M22" s="68" t="n"/>
+      <c r="N22" s="68" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="n"/>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="34" t="n"/>
+      <c r="E23" s="36" t="n"/>
+      <c r="F23" s="17" t="n"/>
+      <c r="G23" s="36" t="n"/>
+      <c r="H23" s="34" t="n"/>
+      <c r="I23" s="36" t="n"/>
+      <c r="J23" s="36" t="n"/>
+      <c r="K23" s="36" t="n"/>
+      <c r="L23" s="17" t="n"/>
+      <c r="M23" s="17" t="n"/>
+      <c r="N23" s="17" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="34" t="n"/>
+      <c r="E24" s="36" t="n"/>
+      <c r="F24" s="17" t="n"/>
+      <c r="G24" s="36" t="n"/>
+      <c r="H24" s="34" t="n"/>
+      <c r="I24" s="36" t="n"/>
+      <c r="J24" s="36" t="n"/>
+      <c r="K24" s="36" t="n"/>
+      <c r="L24" s="17" t="n"/>
+      <c r="M24" s="17" t="n"/>
+      <c r="N24" s="17" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="n"/>
+      <c r="B25" s="19" t="n"/>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="34" t="n"/>
+      <c r="E25" s="36" t="n"/>
+      <c r="F25" s="19" t="n"/>
+      <c r="G25" s="36" t="n"/>
+      <c r="H25" s="34" t="n"/>
+      <c r="I25" s="36" t="n"/>
+      <c r="J25" s="36" t="n"/>
+      <c r="K25" s="36" t="n"/>
+      <c r="L25" s="19" t="n"/>
+      <c r="M25" s="19" t="n"/>
+      <c r="N25" s="19" t="n"/>
+    </row>
+    <row r="26">
+      <c r="G26" s="71" t="n"/>
+      <c r="I26" s="71" t="n"/>
+    </row>
+    <row r="27">
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis qn, (kg/m3)</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vmk (m3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B30" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D30" s="34" t="n"/>
+      <c r="E30" s="36" t="n"/>
+      <c r="F30" s="70" t="n"/>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="34" t="n"/>
+      <c r="I30" s="36" t="n"/>
+      <c r="J30" s="36" t="n"/>
+      <c r="K30" s="36" t="n"/>
+      <c r="L30" s="70" t="n"/>
+      <c r="M30" s="68" t="n"/>
+      <c r="N30" s="68" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="n"/>
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="34" t="n"/>
+      <c r="E31" s="36" t="n"/>
+      <c r="F31" s="17" t="n"/>
+      <c r="G31" s="36" t="n"/>
+      <c r="H31" s="34" t="n"/>
+      <c r="I31" s="36" t="n"/>
+      <c r="J31" s="36" t="n"/>
+      <c r="K31" s="36" t="n"/>
+      <c r="L31" s="17" t="n"/>
+      <c r="M31" s="17" t="n"/>
+      <c r="N31" s="17" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="n"/>
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="34" t="n"/>
+      <c r="E32" s="36" t="n"/>
+      <c r="F32" s="17" t="n"/>
+      <c r="G32" s="36" t="n"/>
+      <c r="H32" s="34" t="n"/>
+      <c r="I32" s="36" t="n"/>
+      <c r="J32" s="36" t="n"/>
+      <c r="K32" s="36" t="n"/>
+      <c r="L32" s="17" t="n"/>
+      <c r="M32" s="17" t="n"/>
+      <c r="N32" s="17" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="n"/>
+      <c r="B33" s="19" t="n"/>
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="34" t="n"/>
+      <c r="E33" s="36" t="n"/>
+      <c r="F33" s="19" t="n"/>
+      <c r="G33" s="36" t="n"/>
+      <c r="H33" s="34" t="n"/>
+      <c r="I33" s="36" t="n"/>
+      <c r="J33" s="36" t="n"/>
+      <c r="K33" s="36" t="n"/>
+      <c r="L33" s="19" t="n"/>
+      <c r="M33" s="19" t="n"/>
+      <c r="N33" s="19" t="n"/>
+    </row>
+    <row r="34">
+      <c r="G34" s="71" t="n"/>
+      <c r="I34" s="71" t="n"/>
+    </row>
+    <row r="35">
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis qn, (kg/m3)</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vmk (m3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B38" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D38" s="34" t="n"/>
+      <c r="E38" s="36" t="n"/>
+      <c r="F38" s="70" t="n"/>
+      <c r="G38" s="36" t="n"/>
+      <c r="H38" s="34" t="n"/>
+      <c r="I38" s="36" t="n"/>
+      <c r="J38" s="36" t="n"/>
+      <c r="K38" s="36" t="n"/>
+      <c r="L38" s="70" t="n"/>
+      <c r="M38" s="68" t="n"/>
+      <c r="N38" s="68" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="n"/>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="34" t="n"/>
+      <c r="E39" s="36" t="n"/>
+      <c r="F39" s="17" t="n"/>
+      <c r="G39" s="36" t="n"/>
+      <c r="H39" s="34" t="n"/>
+      <c r="I39" s="36" t="n"/>
+      <c r="J39" s="36" t="n"/>
+      <c r="K39" s="36" t="n"/>
+      <c r="L39" s="17" t="n"/>
+      <c r="M39" s="17" t="n"/>
+      <c r="N39" s="17" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="n"/>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="18" t="n"/>
+      <c r="D40" s="34" t="n"/>
+      <c r="E40" s="36" t="n"/>
+      <c r="F40" s="17" t="n"/>
+      <c r="G40" s="36" t="n"/>
+      <c r="H40" s="34" t="n"/>
+      <c r="I40" s="36" t="n"/>
+      <c r="J40" s="36" t="n"/>
+      <c r="K40" s="36" t="n"/>
+      <c r="L40" s="17" t="n"/>
+      <c r="M40" s="17" t="n"/>
+      <c r="N40" s="17" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="n"/>
+      <c r="B41" s="19" t="n"/>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="34" t="n"/>
+      <c r="E41" s="36" t="n"/>
+      <c r="F41" s="19" t="n"/>
+      <c r="G41" s="36" t="n"/>
+      <c r="H41" s="34" t="n"/>
+      <c r="I41" s="36" t="n"/>
+      <c r="J41" s="36" t="n"/>
+      <c r="K41" s="36" t="n"/>
+      <c r="L41" s="19" t="n"/>
+      <c r="M41" s="19" t="n"/>
+      <c r="N41" s="19" t="n"/>
+    </row>
+    <row r="42">
+      <c r="G42" s="71" t="n"/>
+      <c r="I42" s="71" t="n"/>
+    </row>
+    <row r="43">
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis qn, (kg/m3)</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vmk (m3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B46" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D46" s="34" t="n"/>
+      <c r="E46" s="36" t="n"/>
+      <c r="F46" s="70" t="n"/>
+      <c r="G46" s="36" t="n"/>
+      <c r="H46" s="34" t="n"/>
+      <c r="I46" s="36" t="n"/>
+      <c r="J46" s="36" t="n"/>
+      <c r="K46" s="36" t="n"/>
+      <c r="L46" s="70" t="n"/>
+      <c r="M46" s="68" t="n"/>
+      <c r="N46" s="68" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="17" t="n"/>
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="18" t="n"/>
+      <c r="D47" s="34" t="n"/>
+      <c r="E47" s="36" t="n"/>
+      <c r="F47" s="17" t="n"/>
+      <c r="G47" s="36" t="n"/>
+      <c r="H47" s="34" t="n"/>
+      <c r="I47" s="36" t="n"/>
+      <c r="J47" s="36" t="n"/>
+      <c r="K47" s="36" t="n"/>
+      <c r="L47" s="17" t="n"/>
+      <c r="M47" s="17" t="n"/>
+      <c r="N47" s="17" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="17" t="n"/>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="18" t="n"/>
+      <c r="D48" s="34" t="n"/>
+      <c r="E48" s="36" t="n"/>
+      <c r="F48" s="17" t="n"/>
+      <c r="G48" s="36" t="n"/>
+      <c r="H48" s="34" t="n"/>
+      <c r="I48" s="36" t="n"/>
+      <c r="J48" s="36" t="n"/>
+      <c r="K48" s="36" t="n"/>
+      <c r="L48" s="17" t="n"/>
+      <c r="M48" s="17" t="n"/>
+      <c r="N48" s="17" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="n"/>
+      <c r="B49" s="19" t="n"/>
+      <c r="C49" s="20" t="n"/>
+      <c r="D49" s="34" t="n"/>
+      <c r="E49" s="36" t="n"/>
+      <c r="F49" s="19" t="n"/>
+      <c r="G49" s="36" t="n"/>
+      <c r="H49" s="34" t="n"/>
+      <c r="I49" s="36" t="n"/>
+      <c r="J49" s="36" t="n"/>
+      <c r="K49" s="36" t="n"/>
+      <c r="L49" s="19" t="n"/>
+      <c r="M49" s="19" t="n"/>
+      <c r="N49" s="19" t="n"/>
+    </row>
+    <row r="50">
+      <c r="G50" s="71" t="n"/>
+      <c r="I50" s="71" t="n"/>
+    </row>
+    <row r="51">
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis qn, (kg/m3)</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vmk (m3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B54" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C54" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D54" s="34" t="n"/>
+      <c r="E54" s="36" t="n"/>
+      <c r="F54" s="70" t="n"/>
+      <c r="G54" s="36" t="n"/>
+      <c r="H54" s="34" t="n"/>
+      <c r="I54" s="36" t="n"/>
+      <c r="J54" s="36" t="n"/>
+      <c r="K54" s="36" t="n"/>
+      <c r="L54" s="70" t="n"/>
+      <c r="M54" s="68" t="n"/>
+      <c r="N54" s="68" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="n"/>
+      <c r="B55" s="17" t="n"/>
+      <c r="C55" s="18" t="n"/>
+      <c r="D55" s="34" t="n"/>
+      <c r="E55" s="36" t="n"/>
+      <c r="F55" s="17" t="n"/>
+      <c r="G55" s="36" t="n"/>
+      <c r="H55" s="34" t="n"/>
+      <c r="I55" s="36" t="n"/>
+      <c r="J55" s="36" t="n"/>
+      <c r="K55" s="36" t="n"/>
+      <c r="L55" s="17" t="n"/>
+      <c r="M55" s="17" t="n"/>
+      <c r="N55" s="17" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="n"/>
+      <c r="B56" s="17" t="n"/>
+      <c r="C56" s="18" t="n"/>
+      <c r="D56" s="34" t="n"/>
+      <c r="E56" s="36" t="n"/>
+      <c r="F56" s="17" t="n"/>
+      <c r="G56" s="36" t="n"/>
+      <c r="H56" s="34" t="n"/>
+      <c r="I56" s="36" t="n"/>
+      <c r="J56" s="36" t="n"/>
+      <c r="K56" s="36" t="n"/>
+      <c r="L56" s="17" t="n"/>
+      <c r="M56" s="17" t="n"/>
+      <c r="N56" s="17" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="19" t="n"/>
+      <c r="B57" s="19" t="n"/>
+      <c r="C57" s="20" t="n"/>
+      <c r="D57" s="34" t="n"/>
+      <c r="E57" s="36" t="n"/>
+      <c r="F57" s="19" t="n"/>
+      <c r="G57" s="36" t="n"/>
+      <c r="H57" s="34" t="n"/>
+      <c r="I57" s="36" t="n"/>
+      <c r="J57" s="36" t="n"/>
+      <c r="K57" s="36" t="n"/>
+      <c r="L57" s="19" t="n"/>
+      <c r="M57" s="19" t="n"/>
+      <c r="N57" s="19" t="n"/>
+    </row>
+    <row r="58">
+      <c r="G58" s="71" t="n"/>
+      <c r="I58" s="71" t="n"/>
+    </row>
+    <row r="59">
+      <c r="G59" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis qn, (kg/m3)</t>
+        </is>
+      </c>
+      <c r="I59" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vmk (m3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B62" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C62" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D62" s="34" t="n"/>
+      <c r="E62" s="36" t="n"/>
+      <c r="F62" s="70" t="n"/>
+      <c r="G62" s="36" t="n"/>
+      <c r="H62" s="34" t="n"/>
+      <c r="I62" s="36" t="n"/>
+      <c r="J62" s="36" t="n"/>
+      <c r="K62" s="36" t="n"/>
+      <c r="L62" s="70" t="n"/>
+      <c r="M62" s="68" t="n"/>
+      <c r="N62" s="68" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="n"/>
+      <c r="B63" s="17" t="n"/>
+      <c r="C63" s="18" t="n"/>
+      <c r="D63" s="34" t="n"/>
+      <c r="E63" s="36" t="n"/>
+      <c r="F63" s="17" t="n"/>
+      <c r="G63" s="36" t="n"/>
+      <c r="H63" s="34" t="n"/>
+      <c r="I63" s="36" t="n"/>
+      <c r="J63" s="36" t="n"/>
+      <c r="K63" s="36" t="n"/>
+      <c r="L63" s="17" t="n"/>
+      <c r="M63" s="17" t="n"/>
+      <c r="N63" s="17" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="n"/>
+      <c r="B64" s="17" t="n"/>
+      <c r="C64" s="18" t="n"/>
+      <c r="D64" s="34" t="n"/>
+      <c r="E64" s="36" t="n"/>
+      <c r="F64" s="17" t="n"/>
+      <c r="G64" s="36" t="n"/>
+      <c r="H64" s="34" t="n"/>
+      <c r="I64" s="36" t="n"/>
+      <c r="J64" s="36" t="n"/>
+      <c r="K64" s="36" t="n"/>
+      <c r="L64" s="17" t="n"/>
+      <c r="M64" s="17" t="n"/>
+      <c r="N64" s="17" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="n"/>
+      <c r="B65" s="19" t="n"/>
+      <c r="C65" s="20" t="n"/>
+      <c r="D65" s="34" t="n"/>
+      <c r="E65" s="36" t="n"/>
+      <c r="F65" s="19" t="n"/>
+      <c r="G65" s="36" t="n"/>
+      <c r="H65" s="34" t="n"/>
+      <c r="I65" s="36" t="n"/>
+      <c r="J65" s="36" t="n"/>
+      <c r="K65" s="36" t="n"/>
+      <c r="L65" s="19" t="n"/>
+      <c r="M65" s="19" t="n"/>
+      <c r="N65" s="19" t="n"/>
+    </row>
+    <row r="66">
+      <c r="G66" s="71" t="n"/>
+      <c r="I66" s="71" t="n"/>
+    </row>
+    <row r="67">
+      <c r="G67" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis qn, (kg/m3)</t>
+        </is>
+      </c>
+      <c r="I67" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vmk (m3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B70" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C70" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D70" s="34" t="n"/>
+      <c r="E70" s="36" t="n"/>
+      <c r="F70" s="70" t="n"/>
+      <c r="G70" s="36" t="n"/>
+      <c r="H70" s="34" t="n"/>
+      <c r="I70" s="36" t="n"/>
+      <c r="J70" s="36" t="n"/>
+      <c r="K70" s="36" t="n"/>
+      <c r="L70" s="70" t="n"/>
+      <c r="M70" s="68" t="n"/>
+      <c r="N70" s="68" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="17" t="n"/>
+      <c r="B71" s="17" t="n"/>
+      <c r="C71" s="18" t="n"/>
+      <c r="D71" s="34" t="n"/>
+      <c r="E71" s="36" t="n"/>
+      <c r="F71" s="17" t="n"/>
+      <c r="G71" s="36" t="n"/>
+      <c r="H71" s="34" t="n"/>
+      <c r="I71" s="36" t="n"/>
+      <c r="J71" s="36" t="n"/>
+      <c r="K71" s="36" t="n"/>
+      <c r="L71" s="17" t="n"/>
+      <c r="M71" s="17" t="n"/>
+      <c r="N71" s="17" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="17" t="n"/>
+      <c r="B72" s="17" t="n"/>
+      <c r="C72" s="18" t="n"/>
+      <c r="D72" s="34" t="n"/>
+      <c r="E72" s="36" t="n"/>
+      <c r="F72" s="17" t="n"/>
+      <c r="G72" s="36" t="n"/>
+      <c r="H72" s="34" t="n"/>
+      <c r="I72" s="36" t="n"/>
+      <c r="J72" s="36" t="n"/>
+      <c r="K72" s="36" t="n"/>
+      <c r="L72" s="17" t="n"/>
+      <c r="M72" s="17" t="n"/>
+      <c r="N72" s="17" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="19" t="n"/>
+      <c r="B73" s="19" t="n"/>
+      <c r="C73" s="20" t="n"/>
+      <c r="D73" s="34" t="n"/>
+      <c r="E73" s="36" t="n"/>
+      <c r="F73" s="19" t="n"/>
+      <c r="G73" s="36" t="n"/>
+      <c r="H73" s="34" t="n"/>
+      <c r="I73" s="36" t="n"/>
+      <c r="J73" s="36" t="n"/>
+      <c r="K73" s="36" t="n"/>
+      <c r="L73" s="19" t="n"/>
+      <c r="M73" s="19" t="n"/>
+      <c r="N73" s="19" t="n"/>
+    </row>
+    <row r="74">
+      <c r="G74" s="71" t="n"/>
+      <c r="I74" s="71" t="n"/>
+    </row>
+    <row r="75">
+      <c r="G75" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis qn, (kg/m3)</t>
+        </is>
+      </c>
+      <c r="I75" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vmk (m3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B78" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C78" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D78" s="34" t="n"/>
+      <c r="E78" s="36" t="n"/>
+      <c r="F78" s="70" t="n"/>
+      <c r="G78" s="36" t="n"/>
+      <c r="H78" s="34" t="n"/>
+      <c r="I78" s="36" t="n"/>
+      <c r="J78" s="36" t="n"/>
+      <c r="K78" s="36" t="n"/>
+      <c r="L78" s="70" t="n"/>
+      <c r="M78" s="68" t="n"/>
+      <c r="N78" s="68" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="17" t="n"/>
+      <c r="B79" s="17" t="n"/>
+      <c r="C79" s="18" t="n"/>
+      <c r="D79" s="34" t="n"/>
+      <c r="E79" s="36" t="n"/>
+      <c r="F79" s="17" t="n"/>
+      <c r="G79" s="36" t="n"/>
+      <c r="H79" s="34" t="n"/>
+      <c r="I79" s="36" t="n"/>
+      <c r="J79" s="36" t="n"/>
+      <c r="K79" s="36" t="n"/>
+      <c r="L79" s="17" t="n"/>
+      <c r="M79" s="17" t="n"/>
+      <c r="N79" s="17" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="17" t="n"/>
+      <c r="B80" s="17" t="n"/>
+      <c r="C80" s="18" t="n"/>
+      <c r="D80" s="34" t="n"/>
+      <c r="E80" s="36" t="n"/>
+      <c r="F80" s="17" t="n"/>
+      <c r="G80" s="36" t="n"/>
+      <c r="H80" s="34" t="n"/>
+      <c r="I80" s="36" t="n"/>
+      <c r="J80" s="36" t="n"/>
+      <c r="K80" s="36" t="n"/>
+      <c r="L80" s="17" t="n"/>
+      <c r="M80" s="17" t="n"/>
+      <c r="N80" s="17" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="19" t="n"/>
+      <c r="B81" s="19" t="n"/>
+      <c r="C81" s="20" t="n"/>
+      <c r="D81" s="34" t="n"/>
+      <c r="E81" s="36" t="n"/>
+      <c r="F81" s="19" t="n"/>
+      <c r="G81" s="36" t="n"/>
+      <c r="H81" s="34" t="n"/>
+      <c r="I81" s="36" t="n"/>
+      <c r="J81" s="36" t="n"/>
+      <c r="K81" s="36" t="n"/>
+      <c r="L81" s="19" t="n"/>
+      <c r="M81" s="19" t="n"/>
+      <c r="N81" s="19" t="n"/>
+    </row>
+    <row r="82">
+      <c r="G82" s="71" t="n"/>
+      <c r="I82" s="71" t="n"/>
+    </row>
+    <row r="83">
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis qn, (kg/m3)</t>
+        </is>
+      </c>
+      <c r="I83" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vmk (m3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B86" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C86" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D86" s="34" t="n"/>
+      <c r="E86" s="36" t="n"/>
+      <c r="F86" s="70" t="n"/>
+      <c r="G86" s="36" t="n"/>
+      <c r="H86" s="34" t="n"/>
+      <c r="I86" s="36" t="n"/>
+      <c r="J86" s="36" t="n"/>
+      <c r="K86" s="36" t="n"/>
+      <c r="L86" s="70" t="n"/>
+      <c r="M86" s="68" t="n"/>
+      <c r="N86" s="68" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="17" t="n"/>
+      <c r="B87" s="17" t="n"/>
+      <c r="C87" s="18" t="n"/>
+      <c r="D87" s="34" t="n"/>
+      <c r="E87" s="36" t="n"/>
+      <c r="F87" s="17" t="n"/>
+      <c r="G87" s="36" t="n"/>
+      <c r="H87" s="34" t="n"/>
+      <c r="I87" s="36" t="n"/>
+      <c r="J87" s="36" t="n"/>
+      <c r="K87" s="36" t="n"/>
+      <c r="L87" s="17" t="n"/>
+      <c r="M87" s="17" t="n"/>
+      <c r="N87" s="17" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="17" t="n"/>
+      <c r="B88" s="17" t="n"/>
+      <c r="C88" s="18" t="n"/>
+      <c r="D88" s="34" t="n"/>
+      <c r="E88" s="36" t="n"/>
+      <c r="F88" s="17" t="n"/>
+      <c r="G88" s="36" t="n"/>
+      <c r="H88" s="34" t="n"/>
+      <c r="I88" s="36" t="n"/>
+      <c r="J88" s="36" t="n"/>
+      <c r="K88" s="36" t="n"/>
+      <c r="L88" s="17" t="n"/>
+      <c r="M88" s="17" t="n"/>
+      <c r="N88" s="17" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="19" t="n"/>
+      <c r="B89" s="19" t="n"/>
+      <c r="C89" s="20" t="n"/>
+      <c r="D89" s="34" t="n"/>
+      <c r="E89" s="36" t="n"/>
+      <c r="F89" s="19" t="n"/>
+      <c r="G89" s="36" t="n"/>
+      <c r="H89" s="34" t="n"/>
+      <c r="I89" s="36" t="n"/>
+      <c r="J89" s="36" t="n"/>
+      <c r="K89" s="36" t="n"/>
+      <c r="L89" s="19" t="n"/>
+      <c r="M89" s="19" t="n"/>
+      <c r="N89" s="19" t="n"/>
+    </row>
+    <row r="90">
+      <c r="G90" s="71" t="n"/>
+      <c r="I90" s="71" t="n"/>
+    </row>
+    <row r="91">
+      <c r="G91" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis qn, (kg/m3)</t>
+        </is>
+      </c>
+      <c r="I91" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vmk (m3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B94" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C94" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D94" s="34" t="n"/>
+      <c r="E94" s="36" t="n"/>
+      <c r="F94" s="70" t="n"/>
+      <c r="G94" s="36" t="n"/>
+      <c r="H94" s="34" t="n"/>
+      <c r="I94" s="36" t="n"/>
+      <c r="J94" s="36" t="n"/>
+      <c r="K94" s="36" t="n"/>
+      <c r="L94" s="70" t="n"/>
+      <c r="M94" s="68" t="n"/>
+      <c r="N94" s="68" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="17" t="n"/>
+      <c r="B95" s="17" t="n"/>
+      <c r="C95" s="18" t="n"/>
+      <c r="D95" s="34" t="n"/>
+      <c r="E95" s="36" t="n"/>
+      <c r="F95" s="17" t="n"/>
+      <c r="G95" s="36" t="n"/>
+      <c r="H95" s="34" t="n"/>
+      <c r="I95" s="36" t="n"/>
+      <c r="J95" s="36" t="n"/>
+      <c r="K95" s="36" t="n"/>
+      <c r="L95" s="17" t="n"/>
+      <c r="M95" s="17" t="n"/>
+      <c r="N95" s="17" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="17" t="n"/>
+      <c r="B96" s="17" t="n"/>
+      <c r="C96" s="18" t="n"/>
+      <c r="D96" s="34" t="n"/>
+      <c r="E96" s="36" t="n"/>
+      <c r="F96" s="17" t="n"/>
+      <c r="G96" s="36" t="n"/>
+      <c r="H96" s="34" t="n"/>
+      <c r="I96" s="36" t="n"/>
+      <c r="J96" s="36" t="n"/>
+      <c r="K96" s="36" t="n"/>
+      <c r="L96" s="17" t="n"/>
+      <c r="M96" s="17" t="n"/>
+      <c r="N96" s="17" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="19" t="n"/>
+      <c r="B97" s="19" t="n"/>
+      <c r="C97" s="20" t="n"/>
+      <c r="D97" s="34" t="n"/>
+      <c r="E97" s="36" t="n"/>
+      <c r="F97" s="19" t="n"/>
+      <c r="G97" s="36" t="n"/>
+      <c r="H97" s="34" t="n"/>
+      <c r="I97" s="36" t="n"/>
+      <c r="J97" s="36" t="n"/>
+      <c r="K97" s="36" t="n"/>
+      <c r="L97" s="19" t="n"/>
+      <c r="M97" s="19" t="n"/>
+      <c r="N97" s="19" t="n"/>
+    </row>
+    <row r="98">
+      <c r="G98" s="71" t="n"/>
+      <c r="I98" s="71" t="n"/>
+    </row>
+    <row r="99">
+      <c r="G99" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis qn, (kg/m3)</t>
+        </is>
+      </c>
+      <c r="I99" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vmk (m3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B102" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C102" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D102" s="34" t="n"/>
+      <c r="E102" s="36" t="n"/>
+      <c r="F102" s="70" t="n"/>
+      <c r="G102" s="36" t="n"/>
+      <c r="H102" s="34" t="n"/>
+      <c r="I102" s="36" t="n"/>
+      <c r="J102" s="36" t="n"/>
+      <c r="K102" s="36" t="n"/>
+      <c r="L102" s="70" t="n"/>
+      <c r="M102" s="68" t="n"/>
+      <c r="N102" s="68" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="17" t="n"/>
+      <c r="B103" s="17" t="n"/>
+      <c r="C103" s="18" t="n"/>
+      <c r="D103" s="34" t="n"/>
+      <c r="E103" s="36" t="n"/>
+      <c r="F103" s="17" t="n"/>
+      <c r="G103" s="36" t="n"/>
+      <c r="H103" s="34" t="n"/>
+      <c r="I103" s="36" t="n"/>
+      <c r="J103" s="36" t="n"/>
+      <c r="K103" s="36" t="n"/>
+      <c r="L103" s="17" t="n"/>
+      <c r="M103" s="17" t="n"/>
+      <c r="N103" s="17" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="17" t="n"/>
+      <c r="B104" s="17" t="n"/>
+      <c r="C104" s="18" t="n"/>
+      <c r="D104" s="34" t="n"/>
+      <c r="E104" s="36" t="n"/>
+      <c r="F104" s="17" t="n"/>
+      <c r="G104" s="36" t="n"/>
+      <c r="H104" s="34" t="n"/>
+      <c r="I104" s="36" t="n"/>
+      <c r="J104" s="36" t="n"/>
+      <c r="K104" s="36" t="n"/>
+      <c r="L104" s="17" t="n"/>
+      <c r="M104" s="17" t="n"/>
+      <c r="N104" s="17" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="19" t="n"/>
+      <c r="B105" s="19" t="n"/>
+      <c r="C105" s="20" t="n"/>
+      <c r="D105" s="34" t="n"/>
+      <c r="E105" s="36" t="n"/>
+      <c r="F105" s="19" t="n"/>
+      <c r="G105" s="36" t="n"/>
+      <c r="H105" s="34" t="n"/>
+      <c r="I105" s="36" t="n"/>
+      <c r="J105" s="36" t="n"/>
+      <c r="K105" s="36" t="n"/>
+      <c r="L105" s="19" t="n"/>
+      <c r="M105" s="19" t="n"/>
+      <c r="N105" s="19" t="n"/>
+    </row>
+    <row r="106">
+      <c r="G106" s="71" t="n"/>
+      <c r="I106" s="71" t="n"/>
+    </row>
+    <row r="107">
+      <c r="G107" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis qn, (kg/m3)</t>
+        </is>
+      </c>
+      <c r="I107" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vmk (m3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B110" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C110" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D110" s="34" t="n"/>
+      <c r="E110" s="36" t="n"/>
+      <c r="F110" s="70" t="n"/>
+      <c r="G110" s="36" t="n"/>
+      <c r="H110" s="34" t="n"/>
+      <c r="I110" s="36" t="n"/>
+      <c r="J110" s="36" t="n"/>
+      <c r="K110" s="36" t="n"/>
+      <c r="L110" s="70" t="n"/>
+      <c r="M110" s="68" t="n"/>
+      <c r="N110" s="68" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="17" t="n"/>
+      <c r="B111" s="17" t="n"/>
+      <c r="C111" s="18" t="n"/>
+      <c r="D111" s="34" t="n"/>
+      <c r="E111" s="36" t="n"/>
+      <c r="F111" s="17" t="n"/>
+      <c r="G111" s="36" t="n"/>
+      <c r="H111" s="34" t="n"/>
+      <c r="I111" s="36" t="n"/>
+      <c r="J111" s="36" t="n"/>
+      <c r="K111" s="36" t="n"/>
+      <c r="L111" s="17" t="n"/>
+      <c r="M111" s="17" t="n"/>
+      <c r="N111" s="17" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="17" t="n"/>
+      <c r="B112" s="17" t="n"/>
+      <c r="C112" s="18" t="n"/>
+      <c r="D112" s="34" t="n"/>
+      <c r="E112" s="36" t="n"/>
+      <c r="F112" s="17" t="n"/>
+      <c r="G112" s="36" t="n"/>
+      <c r="H112" s="34" t="n"/>
+      <c r="I112" s="36" t="n"/>
+      <c r="J112" s="36" t="n"/>
+      <c r="K112" s="36" t="n"/>
+      <c r="L112" s="17" t="n"/>
+      <c r="M112" s="17" t="n"/>
+      <c r="N112" s="17" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="19" t="n"/>
+      <c r="B113" s="19" t="n"/>
+      <c r="C113" s="20" t="n"/>
+      <c r="D113" s="34" t="n"/>
+      <c r="E113" s="36" t="n"/>
+      <c r="F113" s="19" t="n"/>
+      <c r="G113" s="36" t="n"/>
+      <c r="H113" s="34" t="n"/>
+      <c r="I113" s="36" t="n"/>
+      <c r="J113" s="36" t="n"/>
+      <c r="K113" s="36" t="n"/>
+      <c r="L113" s="19" t="n"/>
+      <c r="M113" s="19" t="n"/>
+      <c r="N113" s="19" t="n"/>
+    </row>
+    <row r="114">
+      <c r="G114" s="71" t="n"/>
+      <c r="I114" s="71" t="n"/>
+    </row>
+    <row r="115">
+      <c r="G115" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis qn, (kg/m3)</t>
+        </is>
+      </c>
+      <c r="I115" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vmk (m3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="54" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B118" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C118" s="55" t="inlineStr">
+        <is>
+          <t>Ekopartneris</t>
+        </is>
+      </c>
+      <c r="D118" s="34" t="n"/>
+      <c r="E118" s="36" t="n"/>
+      <c r="F118" s="70" t="n"/>
+      <c r="G118" s="36" t="n"/>
+      <c r="H118" s="34" t="n"/>
+      <c r="I118" s="36" t="n"/>
+      <c r="J118" s="36" t="n"/>
+      <c r="K118" s="36" t="n"/>
+      <c r="L118" s="70" t="n"/>
+      <c r="M118" s="68" t="n"/>
+      <c r="N118" s="68" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="17" t="n"/>
+      <c r="B119" s="17" t="n"/>
+      <c r="C119" s="18" t="n"/>
+      <c r="D119" s="34" t="n"/>
+      <c r="E119" s="36" t="n"/>
+      <c r="F119" s="17" t="n"/>
+      <c r="G119" s="36" t="n"/>
+      <c r="H119" s="34" t="n"/>
+      <c r="I119" s="36" t="n"/>
+      <c r="J119" s="36" t="n"/>
+      <c r="K119" s="36" t="n"/>
+      <c r="L119" s="17" t="n"/>
+      <c r="M119" s="17" t="n"/>
+      <c r="N119" s="17" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="17" t="n"/>
+      <c r="B120" s="17" t="n"/>
+      <c r="C120" s="18" t="n"/>
+      <c r="D120" s="34" t="n"/>
+      <c r="E120" s="36" t="n"/>
+      <c r="F120" s="17" t="n"/>
+      <c r="G120" s="36" t="n"/>
+      <c r="H120" s="34" t="n"/>
+      <c r="I120" s="36" t="n"/>
+      <c r="J120" s="36" t="n"/>
+      <c r="K120" s="36" t="n"/>
+      <c r="L120" s="17" t="n"/>
+      <c r="M120" s="17" t="n"/>
+      <c r="N120" s="17" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="19" t="n"/>
+      <c r="B121" s="19" t="n"/>
+      <c r="C121" s="20" t="n"/>
+      <c r="D121" s="34" t="n"/>
+      <c r="E121" s="36" t="n"/>
+      <c r="F121" s="19" t="n"/>
+      <c r="G121" s="36" t="n"/>
+      <c r="H121" s="34" t="n"/>
+      <c r="I121" s="36" t="n"/>
+      <c r="J121" s="36" t="n"/>
+      <c r="K121" s="36" t="n"/>
+      <c r="L121" s="19" t="n"/>
+      <c r="M121" s="19" t="n"/>
+      <c r="N121" s="19" t="n"/>
+    </row>
+    <row r="122">
+      <c r="F122" s="72" t="n"/>
+      <c r="G122" s="71" t="n"/>
+      <c r="I122" s="71" t="n"/>
+      <c r="L122" s="71" t="n"/>
+    </row>
+    <row r="123">
+      <c r="F123" s="12" t="inlineStr">
+        <is>
+          <t>Viso suma Vmn(sum), Nm3.</t>
+        </is>
+      </c>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkis qn, (kg/m3)</t>
+        </is>
+      </c>
+      <c r="I123" s="12" t="inlineStr">
+        <is>
+          <t>Suma Vmk (m3)</t>
+        </is>
+      </c>
+      <c r="L123" s="12" t="inlineStr">
+        <is>
+          <t>Izokinetiškumo vidurkių vidurkis</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="G125" s="71" t="n"/>
+      <c r="I125" s="73" t="n"/>
+    </row>
+    <row r="126">
+      <c r="G126" s="12" t="inlineStr">
+        <is>
+          <t>Vidurkių vidurkis qn, (kg/m3)</t>
+        </is>
+      </c>
+      <c r="I126" s="12" t="inlineStr">
+        <is>
+          <t>Viso suma Vmk(sum), m3.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="16">
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="C70:C73"/>
+    <mergeCell ref="C102:C105"/>
+    <mergeCell ref="C118:C121"/>
+    <mergeCell ref="C78:C81"/>
+    <mergeCell ref="C94:C97"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="C30:C33"/>
     <mergeCell ref="C6:C9"/>
-    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="C54:C57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4390,12 +6018,12 @@
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="70" t="inlineStr">
+      <c r="A6" s="74" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="B6" s="70" t="n">
+      <c r="B6" s="74" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="55" t="inlineStr">
@@ -4403,21 +6031,21 @@
           <t>Ekopartneris</t>
         </is>
       </c>
-      <c r="D6" s="71" t="n"/>
-      <c r="E6" s="71" t="n"/>
-      <c r="F6" s="71" t="n"/>
-      <c r="G6" s="71" t="n"/>
-      <c r="H6" s="72" t="n"/>
-      <c r="I6" s="71" t="n"/>
-      <c r="J6" s="71" t="n"/>
-      <c r="K6" s="72" t="n"/>
-      <c r="L6" s="72" t="n"/>
-      <c r="M6" s="73" t="n"/>
-      <c r="N6" s="74" t="n"/>
-      <c r="O6" s="75" t="n">
-        <v>3</v>
-      </c>
-      <c r="P6" s="76" t="inlineStr">
+      <c r="D6" s="75" t="n"/>
+      <c r="E6" s="75" t="n"/>
+      <c r="F6" s="75" t="n"/>
+      <c r="G6" s="75" t="n"/>
+      <c r="H6" s="76" t="n"/>
+      <c r="I6" s="75" t="n"/>
+      <c r="J6" s="75" t="n"/>
+      <c r="K6" s="76" t="n"/>
+      <c r="L6" s="76" t="n"/>
+      <c r="M6" s="77" t="n"/>
+      <c r="N6" s="78" t="n"/>
+      <c r="O6" s="79" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" s="80" t="inlineStr">
         <is>
           <t>5 linijos, 1 filtras</t>
         </is>
@@ -4427,19 +6055,19 @@
       <c r="A7" s="21" t="n"/>
       <c r="B7" s="21" t="n"/>
       <c r="C7" s="18" t="n"/>
-      <c r="D7" s="71" t="n"/>
-      <c r="E7" s="71" t="n"/>
-      <c r="F7" s="71" t="n"/>
-      <c r="G7" s="71" t="n"/>
-      <c r="H7" s="72" t="n"/>
-      <c r="I7" s="71" t="n"/>
-      <c r="J7" s="71" t="n"/>
-      <c r="K7" s="72" t="n"/>
-      <c r="L7" s="72" t="n"/>
-      <c r="M7" s="79" t="n"/>
-      <c r="N7" s="77" t="n"/>
+      <c r="D7" s="75" t="n"/>
+      <c r="E7" s="75" t="n"/>
+      <c r="F7" s="75" t="n"/>
+      <c r="G7" s="75" t="n"/>
+      <c r="H7" s="76" t="n"/>
+      <c r="I7" s="75" t="n"/>
+      <c r="J7" s="75" t="n"/>
+      <c r="K7" s="76" t="n"/>
+      <c r="L7" s="76" t="n"/>
+      <c r="M7" s="83" t="n"/>
+      <c r="N7" s="81" t="n"/>
       <c r="O7" s="44" t="n"/>
-      <c r="P7" s="76" t="inlineStr">
+      <c r="P7" s="80" t="inlineStr">
         <is>
           <t>5 linijos, 2 filtras</t>
         </is>
@@ -4449,19 +6077,19 @@
       <c r="A8" s="22" t="n"/>
       <c r="B8" s="22" t="n"/>
       <c r="C8" s="20" t="n"/>
-      <c r="D8" s="71" t="n"/>
-      <c r="E8" s="71" t="n"/>
-      <c r="F8" s="71" t="n"/>
-      <c r="G8" s="71" t="n"/>
-      <c r="H8" s="72" t="n"/>
-      <c r="I8" s="71" t="n"/>
-      <c r="J8" s="71" t="n"/>
-      <c r="K8" s="72" t="n"/>
-      <c r="L8" s="72" t="n"/>
-      <c r="M8" s="80" t="n"/>
-      <c r="N8" s="78" t="n"/>
+      <c r="D8" s="75" t="n"/>
+      <c r="E8" s="75" t="n"/>
+      <c r="F8" s="75" t="n"/>
+      <c r="G8" s="75" t="n"/>
+      <c r="H8" s="76" t="n"/>
+      <c r="I8" s="75" t="n"/>
+      <c r="J8" s="75" t="n"/>
+      <c r="K8" s="76" t="n"/>
+      <c r="L8" s="76" t="n"/>
+      <c r="M8" s="84" t="n"/>
+      <c r="N8" s="82" t="n"/>
       <c r="O8" s="44" t="n"/>
-      <c r="P8" s="76" t="inlineStr">
+      <c r="P8" s="80" t="inlineStr">
         <is>
           <t>5 linijos, 3 filtras</t>
         </is>
@@ -4624,18 +6252,18 @@
       <c r="C6" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="n"/>
+      <c r="D6" s="68" t="n"/>
       <c r="E6" s="37" t="n"/>
       <c r="F6" s="37" t="n"/>
       <c r="G6" s="37" t="n"/>
-      <c r="H6" s="69" t="n"/>
+      <c r="H6" s="68" t="n"/>
       <c r="I6" s="59" t="n"/>
       <c r="J6" s="37" t="n"/>
       <c r="K6" s="37" t="n"/>
       <c r="L6" s="37" t="n"/>
       <c r="M6" s="36" t="n"/>
       <c r="N6" s="59" t="n"/>
-      <c r="O6" s="81" t="inlineStr">
+      <c r="O6" s="85" t="inlineStr">
         <is>
           <t>5 linijos, 3 filtrai</t>
         </is>
@@ -4698,7 +6326,7 @@
       <c r="L9" s="37" t="n"/>
       <c r="M9" s="36" t="n"/>
       <c r="N9" s="17" t="n"/>
-      <c r="O9" s="82" t="inlineStr">
+      <c r="O9" s="86" t="inlineStr">
         <is>
           <t>Tuščiasis ėminys (mt)</t>
         </is>
@@ -4740,7 +6368,7 @@
       <c r="L11" s="37" t="n"/>
       <c r="M11" s="36" t="n"/>
       <c r="N11" s="17" t="n"/>
-      <c r="O11" s="82" t="inlineStr">
+      <c r="O11" s="86" t="inlineStr">
         <is>
           <t>Išplautos nuosėdos (mn)</t>
         </is>
@@ -4765,7 +6393,7 @@
       <c r="L12" s="37" t="n"/>
       <c r="M12" s="36" t="n"/>
       <c r="N12" s="17" t="n"/>
-      <c r="O12" s="82" t="inlineStr">
+      <c r="O12" s="86" t="inlineStr">
         <is>
           <t>Išvalytos ėminių sistemos tuščiasis ėminys (mIt)</t>
         </is>
@@ -4790,7 +6418,7 @@
       <c r="L13" s="37" t="n"/>
       <c r="M13" s="36" t="n"/>
       <c r="N13" s="17" t="n"/>
-      <c r="O13" s="82" t="inlineStr">
+      <c r="O13" s="86" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt1)</t>
         </is>
@@ -4815,7 +6443,7 @@
       <c r="L14" s="37" t="n"/>
       <c r="M14" s="36" t="n"/>
       <c r="N14" s="17" t="n"/>
-      <c r="O14" s="82" t="inlineStr">
+      <c r="O14" s="86" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt2)</t>
         </is>
@@ -4840,7 +6468,7 @@
       <c r="L15" s="37" t="n"/>
       <c r="M15" s="36" t="n"/>
       <c r="N15" s="17" t="n"/>
-      <c r="O15" s="82" t="inlineStr">
+      <c r="O15" s="86" t="inlineStr">
         <is>
           <t>Tušti indai svorio kontrolei (mIt3)</t>
         </is>
@@ -4861,7 +6489,7 @@
       <c r="L16" s="13" t="n"/>
       <c r="M16" s="36" t="n"/>
       <c r="N16" s="19" t="n"/>
-      <c r="O16" s="82" t="inlineStr">
+      <c r="O16" s="86" t="inlineStr">
         <is>
           <t>Tuščių indų ir išvalytos ėminių sistemos tuščiojo ėminio svorio pokytis (mItp)</t>
         </is>
